--- a/data/disruptors_supplementary_data_tables_s1-s5.xlsx
+++ b/data/disruptors_supplementary_data_tables_s1-s5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester.sharepoint.com/sites/Team_caad90aa-a47f-449b-818d-a866be7fd445/Shared Documents/General/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester.sharepoint.com/sites/Team_caad90aa-a47f-449b-818d-a866be7fd445/Shared Documents/General/disruptors/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{2185ED28-394C-4B15-AA86-7120D6AF9B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5381AD78-053C-451A-B278-87ABBE5D2D44}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{2185ED28-394C-4B15-AA86-7120D6AF9B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B291BDA3-B4DE-4C3D-B971-74A74A02A106}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3870" windowWidth="29040" windowHeight="15840" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
+    <workbookView xWindow="-28920" yWindow="-2895" windowWidth="29040" windowHeight="15840" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="table_s5_biosphere_changes" sheetId="12" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">references!$A$1:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">references!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">table_s1_transient!$A$2:$J$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">table_s2_persistent!$A$2:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">table_s3_events!$A$1:$K$36</definedName>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="639">
   <si>
     <t>Explanation of sheets</t>
   </si>
@@ -80,123 +80,18 @@
     <t>references</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>short_ref</t>
   </si>
   <si>
     <t>full_ref</t>
   </si>
   <si>
-    <t>Richardson et al 2023</t>
-  </si>
-  <si>
-    <t>Richardson, K., Steffen, W., et al. 2023. Earth beyond six of nine planetary boundaries. Science Advances, 9, eadh2458, https://doi.org/10.1126/sciadv.adh2458.</t>
-  </si>
-  <si>
     <t>Ocean acidification</t>
   </si>
   <si>
     <t>count</t>
   </si>
   <si>
-    <t>Forster, P.M., Smith, C.J., et al. 2023. Indicators of Global Climate Change 2022: annual update of large-scale indicators of the state of the climate system and human influence. Earth System Science Data, 15, 2295–2327, https://doi.org/10.5194/essd-15-2295-2023.</t>
-  </si>
-  <si>
-    <t>Forster et al 2023</t>
-  </si>
-  <si>
-    <t>Ceballos, G., Ehrlich, P.R., Barnosky, A.D., García, A., Pringle, R.M. and Palmer, T.M. 2015. Accelerated modern human–induced species losses: Entering the sixth mass extinction. Science Advances, 1, e1400253, https://doi.org/10.1126/sciadv.1400253.</t>
-  </si>
-  <si>
-    <t>Ceballos et al 2015</t>
-  </si>
-  <si>
-    <t>Cowie, R.H., Bouchet, P. and Fontaine, B. 2022. The Sixth Mass Extinction: fact, fiction or speculation? Biological Reviews, 97, 640–663, https://doi.org/10.1111/brv.12816.</t>
-  </si>
-  <si>
-    <t>Cowie et al 2022</t>
-  </si>
-  <si>
-    <t>Rounsevell, M.D.A., Harfoot, M., Harrison, P.A., Newbold, T., Gregory, R.D. and Mace, G.M. 2020. A biodiversity target based on species extinctions. Science, 368, 1193–1195, https://doi.org/10.1126/science.aba6592.</t>
-  </si>
-  <si>
-    <t>Rounsevell et al 2020</t>
-  </si>
-  <si>
-    <t>NASA Earth Observation</t>
-  </si>
-  <si>
-    <t>NASA Earth Observation, AURA Ozone data: https://neo.gsfc.nasa.gov/archive/geotiff.float/AURA_OZONE_M/</t>
-  </si>
-  <si>
-    <t>Jiang, L.-Q., Feely, R.A., Carter, B.R., Greeley, D.J., Gledhill, D.K. and Arzayus, K.M. 2015. Climatological distribution of aragonite saturation state in the global oceans. Global Biogeochemical Cycles, 29, 1656–1673, https://doi.org/10.1002/2015GB005198.</t>
-  </si>
-  <si>
-    <t>Jiang et al 2015</t>
-  </si>
-  <si>
-    <t>Carpenter &amp; Bennett 2011</t>
-  </si>
-  <si>
-    <t>Carpenter, S.R. and Bennett, E.M. 2011. Reconsideration of the planetary boundary for phosphorus. Environmental Research Letters, 6, 014009, https://doi.org/10.1088/1748-9326/6/1/014009.</t>
-  </si>
-  <si>
-    <t>Lu &amp; Tian 2017</t>
-  </si>
-  <si>
-    <t>Lu, C. and Tian, H. 2017. Global nitrogen and phosphorus fertilizer use for agriculture production in the past half century: shifted hot spots and nutrient imbalance. Earth System Science Data, 9, 181–192, https://doi.org/10.5194/essd-9-181-2017.</t>
-  </si>
-  <si>
-    <t>FAO 2022</t>
-  </si>
-  <si>
-    <t>FAO 2022. FAOSTAT—FAO database for food and agriculture: http://www.fao.org/faostat/</t>
-  </si>
-  <si>
-    <t>EU Copernicus Climate Change Service. Land cover classification gridded maps from 1992 to present derived from satellite observations. ICDR Land Cover 2016-2020, https://cds.climate.copernicus.eu/datasets/satellite-land-cover?tab=overview</t>
-  </si>
-  <si>
-    <t>EU Copernicus Climate Change Service</t>
-  </si>
-  <si>
-    <t>Ramankutty, N. and Foley, J.A. 1998. Characterizing patterns of global land use: An analysis of global croplands data. Global Biogeochemical Cycles, 12, 667–685, https://doi.org/10.1029/98GB02512.</t>
-  </si>
-  <si>
-    <t>Ramakutty &amp; Foley 1998</t>
-  </si>
-  <si>
-    <t>Porkka, M., Virkki, V., et al. 2022. Global water cycle shifts far beyond pre-industrial conditions – planetary boundary for freshwater change transgressed, EarthArXiv; https://doi.org/10.1038/s44221-024-00208-7.</t>
-  </si>
-  <si>
-    <t>Porkka et al 2022</t>
-  </si>
-  <si>
-    <t>Chin, M., Diehl, T., et al. 2014. Multi-decadal aerosol variations from 1980 to 2009: a perspective from observations and a global model. Atmospheric Chemistry and Physics, 14, 3657–3690, https://doi.org/10.5194/acp-14-3657-2014.</t>
-  </si>
-  <si>
-    <t>Chin et al 2014</t>
-  </si>
-  <si>
-    <t>Vogel, A., Alessa, G., Scheele, R., Weber, L., Dubovik, O., North, P. and Fiedler, S. 2022. Uncertainty in Aerosol Optical Depth From Modern Aerosol-Climate Models, Reanalyses, and Satellite Products. Journal of Geophysical Research: Atmospheres, 127, e2021JD035483, https://doi.org/10.1029/2021JD035483.</t>
-  </si>
-  <si>
-    <t>Vogel et al 2022</t>
-  </si>
-  <si>
-    <t>Zanis et al 2020</t>
-  </si>
-  <si>
-    <t>Zanis, P., Akritidis, D., et al. 2020. Fast responses on pre-industrial climate from present-day aerosols in a CMIP6 multi-model study. Atmospheric Chemistry and Physics, 20, 8381–8404, https://doi.org/10.5194/acp-20-8381-2020.</t>
-  </si>
-  <si>
-    <t>Sun, Y. 2024. Dynamics of nutrient cycles in the Permian–Triassic oceans. Earth-Science Reviews, 258, 104914, https://doi.org/10.1016/j.earscirev.2024.104914.</t>
-  </si>
-  <si>
-    <t>Sun 2024</t>
-  </si>
-  <si>
     <t>Cretaceous-Palaeogene boundary</t>
   </si>
   <si>
@@ -209,18 +104,6 @@
     <t>Cambrian agronomic revolution</t>
   </si>
   <si>
-    <t>Müller, J., Sun, Y., Yang, F., Fantasia, A. and Joachimski, M. 2022. Phosphorus Cycle and Primary Productivity Changes in the Tethys Ocean During the Permian-Triassic Transition: Starving Marine Ecosystems. Frontiers in Earth Science, 10, https://doi.org/10.3389/feart.2022.832308.</t>
-  </si>
-  <si>
-    <t>Muller et al 2022</t>
-  </si>
-  <si>
-    <t>Clarkson, M.O., Kasemann, S.A., et al. 2015. Ocean acidification and the Permo-Triassic mass extinction. Science, 348, 229–232, https://doi.org/10.1126/science.aaa0193.</t>
-  </si>
-  <si>
-    <t>Clarkson et al 2015</t>
-  </si>
-  <si>
     <t>transient</t>
   </si>
   <si>
@@ -704,9 +587,6 @@
     <t>Stanley 2016</t>
   </si>
   <si>
-    <t>McGhee et al 2015</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chen J, Wang X, Isson T, Gibert Z, Montañez IP, Shen S. 2025 Serpukhovian mass extinction linked to interglacial warming and marine anoxia. GOLDSCHMIDT. </t>
   </si>
   <si>
@@ -797,12 +677,6 @@
     <t>genus</t>
   </si>
   <si>
-    <t>Clyde et al 2016</t>
-  </si>
-  <si>
-    <t>Clyde WC, Ramezani J, Johnson KR, Bowring SA, Jones MM. 2016 Direct high-precision U–Pb geochronology of the end-Cretaceous extinction and calibration of Paleocene astronomical timescales. Earth and Planetary Science Letters 452, 272–280. (doi:10.1016/j.epsl.2016.07.041)</t>
-  </si>
-  <si>
     <t>Bambach RK. 2006 Phanerozoic Biodiversity Mass Extinctions. Annual Review of Earth and Planetary Sciences 34, 127–155. (doi:10.1146/annurev.earth.33.092203.122654)</t>
   </si>
   <si>
@@ -812,12 +686,6 @@
     <t>Gangl et al 2019</t>
   </si>
   <si>
-    <t>Charbonnier G, Boulila S, Spangenberg JE, Adatte T, Föllmi KB, Laskar J. 2018 Obliquity pacing of the hydrological cycle during the Oceanic Anoxic Event 2. Earth and Planetary Science Letters 499, 266–277. (doi:10.1016/j.epsl.2018.07.029)</t>
-  </si>
-  <si>
-    <t>Charbonnier et al 2018</t>
-  </si>
-  <si>
     <t>GTS 2020 estimate of ~500 kyr (Gale et al 2020); astrochronological estimates suggest &gt;930 kyr for the whole event and ~30 kyr for the onset (Gangl et al 2019)</t>
   </si>
   <si>
@@ -830,12 +698,6 @@
     <t>GTS 2020 estimate of ~1.1 Myr (Gale et al 2020); radiometric constraints agree giving 1.116 +0.087/-0.093 Myr with an onset duration of ~0.115 Myr (Li et al 2024)</t>
   </si>
   <si>
-    <t>Reershemius T, Planavsky NJ. 2021 What controls the duration and intensity of ocean anoxic events in the Paleozoic and the Mesozoic? Earth-Science Reviews 221, 103787. (doi:10.1016/j.earscirev.2021.103787)</t>
-  </si>
-  <si>
-    <t>Reershemius &amp; Planavsky 2021</t>
-  </si>
-  <si>
     <t>Boulila et al 2019</t>
   </si>
   <si>
@@ -890,12 +752,6 @@
     <t>decline in all osetichthyan groups across Ladinian-Carnian boundary ranges from 51 to 62 %</t>
   </si>
   <si>
-    <t>Bernardi M, Gianolla P, Petti FM, Mietto P, Benton MJ. 2018 Dinosaur diversification linked with the Carnian Pluvial Episode. Nat Commun 9, 1499. (doi:10.1038/s41467-018-03996-1)</t>
-  </si>
-  <si>
-    <t>Bernardi et al 2018</t>
-  </si>
-  <si>
     <t>Miller et al 2017</t>
   </si>
   <si>
@@ -905,12 +761,6 @@
     <t>astrochronology calibrates five short-lived CIEs to a total duration of 1.09 Myr (Miller et al 2017); other astrochronology agrees that the interval spans two to three 405 kyr cycles with a total duration of 0.8 to 1.2 Myr (Zhang et al 2015)</t>
   </si>
   <si>
-    <t>Zhang Y, Li M, Ogg JG, Montgomery P, Huang C, Chen Z-Q, Shi Z, Enos P, Lehrmann DJ. 2015 Cycle-calibrated magnetostratigraphy of middle Carnian from South China: Implications for Late Triassic time scale and termination of the Yangtze Platform. Palaeogeography, Palaeoclimatology, Palaeoecology 436, 135–166. (doi:10.1016/j.palaeo.2015.05.033)</t>
-  </si>
-  <si>
-    <t>Zhang et al 2015</t>
-  </si>
-  <si>
     <t>Goudemand N, Romano C, Leu M, Bucher H, Trotter JA, Williams IS. 2019 Dynamic interplay between climate and marine biodiversity upheavals during the early Triassic Smithian -Spathian biotic crisis. Earth-Science Reviews 195, 169–178. (doi:10.1016/j.earscirev.2019.01.013)</t>
   </si>
   <si>
@@ -953,12 +803,6 @@
     <t>Capel et al 2023</t>
   </si>
   <si>
-    <t>Singh et al 2025</t>
-  </si>
-  <si>
-    <t>Singh P, Ferré J, Thrasher B, Monarrez PM, Al-Ramadan K, Cantrell DL, Lehrmann DJ, Morsilli M, Payne JL. 2025 Macroevolutionary coupling of marine biomass and biodiversity across the Phanerozoic. Current Biology (doi:10.1016/j.cub.2025.06.006)</t>
-  </si>
-  <si>
     <t>Xu Z et al. 2025 Early Triassic super-greenhouse climate driven by vegetation collapse. Nat Commun 16, 5400. (doi:10.1038/s41467-025-60396-y)</t>
   </si>
   <si>
@@ -1010,12 +854,6 @@
     <t>birds</t>
   </si>
   <si>
-    <t>Schuettpelz E, Rouhan G, Pryer KM, Rothfels CJ, Prado J, Sundue MA, Windham MD, Moran RC, Smith AR. 2018 Are there too many fern genera? TAXON 67, 473–480. (doi:10.12705/673.1)</t>
-  </si>
-  <si>
-    <t>Schuettpelz et al 2018</t>
-  </si>
-  <si>
     <t>vertebrates</t>
   </si>
   <si>
@@ -1085,12 +923,6 @@
     <t>Myrow PM, Ramezani J, Hanson AE, Bowring SA, Racki G, Rakociński M. 2014 High-precision U–Pb age and duration of the latest Devonian (Famennian) Hangenberg event, and its implications. Terra Nova 26, 222–229. (doi:10.1111/ter.12090)</t>
   </si>
   <si>
-    <t>Kaiser et al 2016</t>
-  </si>
-  <si>
-    <t>Kaiser SI, Aretz M, Becker RT. 2016 The global Hangenberg Crisis (Devonian–Carboniferous transition): review of a first-order mass extinction. In Devonian Climate, Sea Level and Evolutionary Events (eds RT Becker, P Königshof, CE Brett), p. 0. Geological Society of London. (doi:10.1144/SP423.9)</t>
-  </si>
-  <si>
     <t>radiometric constraints suggest ~50 to 100 kyr for deposition of the Hangenberg Shale (Myrow et al 2014) with the whole interval perhaps up to 300 kyr</t>
   </si>
   <si>
@@ -1157,9 +989,6 @@
     <t xml:space="preserve">Archean-Proterozoic boundary </t>
   </si>
   <si>
-    <t>Great Oxidation (Oxygenation) Event, oxygenation of the atmosphere and hydrosphere, oxidation of surface rocks and minerals (geosphere), impact on global climate and cryosphere (cooling and snowball glaciation)</t>
-  </si>
-  <si>
     <t>Negative: lethal to anaerobic ecologies, likely large scale extinction and short term biomass loss</t>
   </si>
   <si>
@@ -1280,9 +1109,6 @@
     <t>Donoghue PCJ, Harrison CJ, Paps J, Schneider H. 2021 The evolutionary emergence of land plants. Current Biology 31, R1281–R1298. (doi:10.1016/j.cub.2021.07.038)</t>
   </si>
   <si>
-    <t>initial colonisation in late Cambrian or Early Ordovician (Morrie et al 2018; Donoghue et al 2021); main revolution began in the late Silurian ~430 Ma with an initial peak of genus and species diversity in the Early Devonian ~400 Ma and a largely established terrestrial plant biosphere by the Late Devonian ~360 Ma (Capel et al 2023)</t>
-  </si>
-  <si>
     <t>Morris JL et al. 2018 The timescale of early land plant evolution. Proceedings of the National Academy of Sciences 115, E2274–E2283. (doi:10.1073/pnas.1719588115)</t>
   </si>
   <si>
@@ -1337,18 +1163,6 @@
     <t>highly uncertain magnitude and duration; less than 5 Myr</t>
   </si>
   <si>
-    <t>Gibson et al 2018</t>
-  </si>
-  <si>
-    <t>Gibson TM et al. 2018 Precise age of Bangiomorpha pubescens dates the origin of eukaryotic photosynthesis. Geology 46, 135–138. (doi:10.1130/G39829.1)</t>
-  </si>
-  <si>
-    <t>Miao et al 2024</t>
-  </si>
-  <si>
-    <t>Miao L, Yin Z, Knoll AH, Qu Y, Zhu M. 2024 1.63-billion-year-old multicellular eukaryotes from the Chuanlinggou Formation in North China. Science Advances 10, eadk3208. (doi:10.1126/sciadv.adk3208)</t>
-  </si>
-  <si>
     <t>Late Ordovician Mass Extinction</t>
   </si>
   <si>
@@ -1581,12 +1395,6 @@
   </si>
   <si>
     <t>following projections of vertebrate genera extinctions assuming the extinction of endangered monospecific genera (Ceballos &amp; Ehrlich 2023 table 3)</t>
-  </si>
-  <si>
-    <t>Thomas 2015</t>
-  </si>
-  <si>
-    <t>Thomas CD. 2015 Rapid acceleration of plant speciation during the Anthropocene. Trends in Ecology &amp; Evolution 30, 448–455. (doi:10.1016/j.tree.2015.05.009)</t>
   </si>
   <si>
     <t>assume halting and reversing biosphere degredation by 2100 in an integrated action portfolio (IAP) scenario (Leclere et al 2020) and supporting new symbioses at a rate of at least 10 speciation events per million species years (Thomas 2015)</t>
@@ -1860,9 +1668,6 @@
     <t xml:space="preserve">[c] The EOT is included in Kiessling et al. (2025) with no warming, no deoxygenation, and no ocean acidification. The biotic event is assigned with “medium” confidence to a climate change cause, which was “likely cooling”. </t>
   </si>
   <si>
-    <t>Uncertain; possibly ~1 Myr following Melchin et al 2020</t>
-  </si>
-  <si>
     <t>Uncertain; possibly ~1 Myr (following Melchin et al. 2020)</t>
   </si>
   <si>
@@ -1870,9 +1675,6 @@
   </si>
   <si>
     <t>1 to 20 % loss of species</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable (intense fires and month to decadal-scale cooling; Rae et al. 2021) </t>
   </si>
   <si>
     <t>Seconds to millennia for K-Pg boundary extinction; maximum impact duration &lt;20 to 30 years following modelling work (Brugger et al 2017; Chiarenza et al 2020; Morgan et al 2022), but note the wide temporal range of impact on the biosphere during this event</t>
@@ -2073,6 +1875,213 @@
       <t xml:space="preserve"> concentration of 70% of bird biomass in chickens, and 98% of mammal biomass in humans and farmed animals</t>
     </r>
   </si>
+  <si>
+    <t>Great Oxidation (Oxygenation) Episode (Event) [GOE], oxygenation of the atmosphere and hydrosphere, oxidation of surface rocks and minerals (geosphere), impact on global climate and cryosphere (cooling and snowball glaciation)</t>
+  </si>
+  <si>
+    <t>minimum duration of human impacts on decadal scale; minimum duration 150 years by definition; maximum duration up to 50 kyr human impact; extended to 3100 CE</t>
+  </si>
+  <si>
+    <t>uncertain; perhaps ~1 to 2 Myr; diachronous main extinction pulse</t>
+  </si>
+  <si>
+    <t>uncertain; possibly ~1 Myr following Melchin et al 2020</t>
+  </si>
+  <si>
+    <t>uncertain; possibly 2 Myr in total; the first excursion may be very short</t>
+  </si>
+  <si>
+    <t>uncertain; possibly ~1 to 1.5 Myr with a protracted recovery phase?</t>
+  </si>
+  <si>
+    <t>initial colonisation in late Cambrian or Early Ordovician (Morris et al 2018; Donoghue et al 2021); main revolution began in the late Silurian ~430 Ma with an initial peak of genus and species diversity in the Early Devonian ~400 Ma and a largely established terrestrial plant biosphere by the Late Devonian ~360 Ma (Capel et al 2023)</t>
+  </si>
+  <si>
+    <t>Kiessling et al 2025</t>
+  </si>
+  <si>
+    <t>Kwon et al 2022</t>
+  </si>
+  <si>
+    <t>Hutchinson et al 2021</t>
+  </si>
+  <si>
+    <t>Pearson et al 2008</t>
+  </si>
+  <si>
+    <t>Westerhold et al 2020</t>
+  </si>
+  <si>
+    <t>McInerney &amp; Wing 2011</t>
+  </si>
+  <si>
+    <t>Gale et al 2020</t>
+  </si>
+  <si>
+    <t>Jenkyns et al 2018</t>
+  </si>
+  <si>
+    <t>Hesselbo et al 2020</t>
+  </si>
+  <si>
+    <t>Ogg et al 2020</t>
+  </si>
+  <si>
+    <t>Shen et al 2019</t>
+  </si>
+  <si>
+    <t>Bond et al 2019</t>
+  </si>
+  <si>
+    <t>McGhee et al 2013</t>
+  </si>
+  <si>
+    <t>Hu et al 2022</t>
+  </si>
+  <si>
+    <t>Montanez &amp; Poulsen 2013</t>
+  </si>
+  <si>
+    <t>Kabanov et al 2023</t>
+  </si>
+  <si>
+    <t>Melchin et al 2020</t>
+  </si>
+  <si>
+    <t>Harper 2024</t>
+  </si>
+  <si>
+    <t>Gradstein et al 2020</t>
+  </si>
+  <si>
+    <t>Judd et al 2024</t>
+  </si>
+  <si>
+    <t>Zhuravlev &amp; Wood 1996</t>
+  </si>
+  <si>
+    <t>Zhuravlev &amp; Wood 2018</t>
+  </si>
+  <si>
+    <t>Ruhl et al 2010</t>
+  </si>
+  <si>
+    <t>Wong Hearing et al 2025</t>
+  </si>
+  <si>
+    <t>Bond DPG, Wignall PB, Grasby SE. 2019 The Capitanian (Guadalupian, Middle Permian) mass extinction in NW Pangea (Borup Fiord, Arctic Canada): A global crisis driven by volcanism and anoxia. GSA Bulletin 132, 931–942. (doi:10.1130/B35281.1)</t>
+  </si>
+  <si>
+    <t>Foster GL, Hull P, Lunt DJ, Zachos JC. 2018 Placing our current ‘hyperthermal’ in the context of rapid climate change in our geological past. Philos Trans A Math Phys Eng Sci 376, 20170086. (doi:10.1098/rsta.2017.0086)</t>
+  </si>
+  <si>
+    <t>Gale AS, Mutterlose J, Batenburg S, Gradstein FM, Agterberg FP, Ogg JG, Petrizzo MR. 2020 Chapter 27 - The Cretaceous Period. In Geologic Time Scale 2020 (eds FM Gradstein, JG Ogg, MD Schmitz, GM Ogg), pp. 1023–1086. Elsevier. (doi:10.1016/B978-0-12-824360-2.00027-9)</t>
+  </si>
+  <si>
+    <t>Gradstein FM, Ogg JD, Schmitz MD, Ogg GM. 2020 Geologic Time Scale 2020. 1st edn. Elsevier. See https://www.elsevier.com/books/geologic-time-scale-2020/gradstein/978-0-12-824360-2.</t>
+  </si>
+  <si>
+    <t>Harper DAT. 2024 Late Ordovician Mass Extinction: Earth, fire and ice. Natl Sci Rev 11, nwad319. (doi:10.1093/nsr/nwad319)</t>
+  </si>
+  <si>
+    <t>Hesselbo SP, Ogg JG, Ruhl M, Hinnov LA, Huang CJ. 2020 Chapter 26 - The Jurassic Period. In Geologic Time Scale 2020 (eds FM Gradstein, JG Ogg, MD Schmitz, GM Ogg), pp. 955–1021. Elsevier. (doi:10.1016/B978-0-12-824360-2.00026-7)</t>
+  </si>
+  <si>
+    <t>Hu D, Li M, Zhang X, Wang X, Farquhar J, Xu Y, Sun L, Shen Y. 2022 Multiple S-isotope constraints on environmental changes during the Serpukhovian mass extinction. Earth and Planetary Science Letters 594, 117719. (doi:10.1016/j.epsl.2022.117719)</t>
+  </si>
+  <si>
+    <t>Huang C, Joachimski MM, Gong Y. 2018 Did climate changes trigger the Late Devonian Kellwasser Crisis? Evidence from a high-resolution conodont δ18OPO4 record from South China. Earth and Planetary Science Letters 495, 174–184. (doi:10.1016/j.epsl.2018.05.016)</t>
+  </si>
+  <si>
+    <t>Huang et al 2018</t>
+  </si>
+  <si>
+    <t>Hutchinson DK et al. 2021 The Eocene–Oligocene transition: a review of marine and terrestrial proxy data, models and model–data comparisons. Climate of the Past 17, 269–315. (doi:10.5194/cp-17-269-2021)</t>
+  </si>
+  <si>
+    <t>Jenkyns HC. 2018 Transient cooling episodes during Cretaceous Oceanic Anoxic Events with special reference to OAE 1a (Early Aptian). Philosophical Transactions of the Royal Society A: Mathematical, Physical and Engineering Sciences 376, 20170073. (doi:10.1098/rsta.2017.0073)</t>
+  </si>
+  <si>
+    <t>Judd EJ, Tierney JE, Lunt DJ, Montañez IP, Huber BT, Wing SL, Valdes PJ. 2024 A 485-million-year history of Earth’s surface temperature. Science 385, eadk3705. (doi:10.1126/science.adk3705)</t>
+  </si>
+  <si>
+    <t>Kabanov P, Hauck TE, Gouwy SA, Grasby SE, van der Boon A. 2023 Oceanic anoxic events, photic-zone euxinia, and controversy of sea-level fluctuations during the Middle-Late Devonian. Earth-Science Reviews 241, 104415. (doi:10.1016/j.earscirev.2023.104415)</t>
+  </si>
+  <si>
+    <t>Keller G. 1986 Stepwise mass extinctions and impact events: Late Eocene to early Oligocene. Marine Micropaleontology 10, 267–293. (doi:10.1016/0377-8398(86)90032-0)</t>
+  </si>
+  <si>
+    <t>Kiessling W, Reddin CJ, Dowding EM, Dimitrijević D, Raja NB, Kocsis ÁT. 2025 Marine biological responses to abrupt climate change in deep time. Paleobiology 51, 97–111. (doi:10.1017/pab.2024.20)</t>
+  </si>
+  <si>
+    <t>Kwon EY, Timmermann A, Tipple BJ, Schmittner A. 2022 Projected reversal of oceanic stable carbon isotope ratio depth gradient with continued anthropogenic carbon emissions. Commun Earth Environ 3, 62. (doi:10.1038/s43247-022-00388-8)</t>
+  </si>
+  <si>
+    <t>McGhee GR, Clapham ME, Sheehan PM, Bottjer DJ, Droser ML. 2013 A new ecological-severity ranking of major Phanerozoic biodiversity crises. Palaeogeography, Palaeoclimatology, Palaeoecology 370, 260–270. (doi:10.1016/j.palaeo.2012.12.019)</t>
+  </si>
+  <si>
+    <t>McInerney FA, Wing SL. 2011 The Paleocene-Eocene Thermal Maximum: A Perturbation of Carbon Cycle, Climate, and Biosphere with Implications for the Future. Annual Review of Earth and Planetary Sciences 39, 489–516. (doi:10.1146/annurev-earth-040610-133431)</t>
+  </si>
+  <si>
+    <t>Melchin MJ, Sadler PM, Cramer BD. 2020 Chapter 21 - The Silurian Period. In Geologic Time Scale 2020 (eds FM Gradstein, JG Ogg, MD Schmitz, GM Ogg), pp. 695–732. Elsevier. (doi:10.1016/B978-0-12-824360-2.00021-8)</t>
+  </si>
+  <si>
+    <t>Montañez IP, Poulsen CJ. 2013 The Late Paleozoic Ice Age: An Evolving Paradigm. Annual Review of Earth and Planetary Sciences 41, 629–656. (doi:10.1146/annurev.earth.031208.100118)</t>
+  </si>
+  <si>
+    <t>Ogg JG, Chen Z-Q, Orchard MJ, Jiang HS. 2020 Chapter 25 - The Triassic Period. In Geologic Time Scale 2020 (eds FM Gradstein, JG Ogg, MD Schmitz, GM Ogg), pp. 903–953. Elsevier. (doi:10.1016/B978-0-12-824360-2.00025-5)</t>
+  </si>
+  <si>
+    <t>Pearson PN, McMillan IK, Wade BS, Jones TD, Coxall HK, Bown PR, Lear CH. 2008 Extinction and environmental change across the Eocene-Oligocene boundary in Tanzania. Geology 36, 179–182. (doi:10.1130/G24308A.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable (intense fires and month to decadal-scale cooling; Vellekoop et al 2014; Gulick et al 2019) </t>
+  </si>
+  <si>
+    <t>Gulick et al 2019</t>
+  </si>
+  <si>
+    <t>Gulick SPS et al. 2019 The first day of the Cenozoic. Proceedings of the National Academy of Sciences 116, 19342–19351. (doi:10.1073/pnas.1909479116)</t>
+  </si>
+  <si>
+    <t>Vellekoop J, Sluijs A, Smit J, Schouten S, Weijers JWH, Sinninghe Damsté JS, Brinkhuis H. 2014 Rapid short-term cooling following the Chicxulub impact at the Cretaceous–Paleogene boundary. Proceedings of the National Academy of Sciences 111, 7537–7541. (doi:10.1073/pnas.1319253111)</t>
+  </si>
+  <si>
+    <t>Vellekoop et al 2014</t>
+  </si>
+  <si>
+    <t>Ruhl M, Deenen MHL, Abels HA, Bonis NR, Krijgsman W, Kürschner WM. 2010 Astronomical constraints on the duration of the early Jurassic Hettangian stage and recovery rates following the end-Triassic mass extinction (St Audrie’s Bay/East Quantoxhead, UK). Earth and Planetary Science Letters 295, 262–276. (doi:10.1016/j.epsl.2010.04.008)</t>
+  </si>
+  <si>
+    <t>Shen Z, Monnet C, Cascales-Miñana B, Gong Y, Dong X, Kroeck DM, Servais T. 2019 Diversity dynamics of Devonian terrestrial palynofloras from China: regional and global significance. Earth-Science Reviews , 102967. (doi:10.1016/j.earscirev.2019.102967)</t>
+  </si>
+  <si>
+    <t>Speijer RP, Scheibner C, Stassen P, Morsi A-MM. 2012 Response of marine ecosystems to deep-time global warming: a synthesis of biotic patterns across the Paleocene-Eocene Thermal Maximum (PETM). Austrian Journal of Earth Sciences 105, 6–16.</t>
+  </si>
+  <si>
+    <t>Stanley SM. 2016 Estimates of the magnitudes of major marine mass extinctions in earth history. Proceedings of the National Academy of Sciences 113, E6325–E6334. (doi:10.1073/pnas.1613094113)</t>
+  </si>
+  <si>
+    <t>Weppe R, Condamine FL, Guinot G, Maugoust J, Orliac MJ. 2023 Drivers of the artiodactyl turnover in insular western Europe at the Eocene–Oligocene Transition. Proceedings of the National Academy of Sciences 120, e2309945120. (doi:10.1073/pnas.2309945120)</t>
+  </si>
+  <si>
+    <t>Westerhold T et al. 2020 An astronomically dated record of Earth’s climate and its predictability over the last 66 million years. Science 369, 1383–1387. (doi:10.1126/science.aba6853)</t>
+  </si>
+  <si>
+    <t>van Woesik et al 2012</t>
+  </si>
+  <si>
+    <t>van Woesik R, Franklin EC, O’Leary J, McClanahan TR, Klaus JS, Budd AF. 2012 Hosts of the Plio-Pleistocene past reflect modern-day coral vulnerability. Proc Biol Sci 279, 2448–2456. (doi:10.1098/rspb.2011.2621)</t>
+  </si>
+  <si>
+    <t>Wong Hearing TW, Tindal BH, Vandyk TM, Na L, Pohl A, Liu AG, Harvey THP, Williams M. 2025 Ediacaran coupling of climate and biosphere dynamics. (doi:10.31223/X5S42P)</t>
+  </si>
+  <si>
+    <t>Zhuravlev AY, Wood RA. 1996 Anoxia as the cause of the mid-Early Cambrian (Botomian) extinction event. Geology 24, 311–314. (doi:10.1130/0091-7613(1996)024&amp;lt;0311:AATCOT&amp;gt;2.3.CO;2)</t>
+  </si>
+  <si>
+    <t>Zhuravlev AY, Wood RA. 2018 The two phases of the Cambrian Explosion. Scientific Reports 8, 16656. (doi:10.1038/s41598-018-34962-y)</t>
+  </si>
 </sst>
 </file>
 
@@ -2081,7 +2090,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2120,22 +2129,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2163,7 +2157,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2189,6 +2183,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -2224,14 +2227,8 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2245,42 +2242,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2291,18 +2264,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2384,13 +2400,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2712,7 +2721,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>553</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -2725,47 +2734,47 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>554</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>555</v>
+        <v>491</v>
       </c>
       <c r="B5" t="s">
-        <v>560</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>556</v>
+        <v>492</v>
       </c>
       <c r="B6" t="s">
-        <v>561</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>557</v>
+        <v>493</v>
       </c>
       <c r="B7" t="s">
-        <v>562</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>558</v>
+        <v>494</v>
       </c>
       <c r="B8" t="s">
-        <v>563</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>559</v>
+        <v>495</v>
       </c>
       <c r="B9" t="s">
-        <v>564</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -2779,1012 +2788,752 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7423E71A-C3BA-4E9A-8679-88DDD26ECF27}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>261</v>
       </c>
       <c r="B2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>485</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>377</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>372</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>414</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>8</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>9</v>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>367</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>10</v>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>588</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>11</v>
+        <v>601</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>208</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>12</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>459</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>13</v>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>234</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>14</v>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>403</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>15</v>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>242</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>16</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>437</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>17</v>
+        <v>436</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>172</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>18</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>465</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>19</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>383</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>20</v>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>287</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>21</v>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>219</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>22</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>284</v>
       </c>
       <c r="B23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>23</v>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>480</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>24</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>343</v>
       </c>
       <c r="B25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C25" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>25</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>274</v>
       </c>
       <c r="B26" t="s">
-        <v>219</v>
-      </c>
-      <c r="C26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>26</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>224</v>
-      </c>
-      <c r="C27" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>27</v>
+        <v>602</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>583</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>28</v>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>203</v>
       </c>
       <c r="B29" t="s">
-        <v>241</v>
-      </c>
-      <c r="C29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>29</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>230</v>
       </c>
       <c r="B30" t="s">
-        <v>245</v>
-      </c>
-      <c r="C30" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>30</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>595</v>
       </c>
       <c r="B31" t="s">
-        <v>247</v>
-      </c>
-      <c r="C31" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>31</v>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>624</v>
       </c>
       <c r="B32" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>594</v>
+      </c>
+      <c r="B34" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>420</v>
+      </c>
+      <c r="B35" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>585</v>
+      </c>
+      <c r="B36" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>590</v>
+      </c>
+      <c r="B37" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>609</v>
+      </c>
+      <c r="B39" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>579</v>
+      </c>
+      <c r="B40" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>584</v>
+      </c>
+      <c r="B42" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>596</v>
+      </c>
+      <c r="B43" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>592</v>
+      </c>
+      <c r="B44" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>577</v>
+      </c>
+      <c r="B46" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>578</v>
+      </c>
+      <c r="B47" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>396</v>
+      </c>
+      <c r="B48" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>415</v>
+      </c>
+      <c r="B49" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>464</v>
+      </c>
+      <c r="B51" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>589</v>
+      </c>
+      <c r="B53" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>582</v>
+      </c>
+      <c r="B54" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>593</v>
+      </c>
+      <c r="B55" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>357</v>
+      </c>
+      <c r="B57" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>591</v>
+      </c>
+      <c r="B58" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>466</v>
+      </c>
+      <c r="B59" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>346</v>
+      </c>
+      <c r="B60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>281</v>
+      </c>
+      <c r="B61" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>266</v>
+      </c>
+      <c r="B62" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>586</v>
+      </c>
+      <c r="B63" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>248</v>
+      </c>
+      <c r="B64" t="s">
         <v>249</v>
       </c>
-      <c r="C32" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>253</v>
-      </c>
-      <c r="C33" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>254</v>
-      </c>
-      <c r="C34" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>258</v>
-      </c>
-      <c r="C35" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>261</v>
-      </c>
-      <c r="C36" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>263</v>
-      </c>
-      <c r="C37" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>265</v>
-      </c>
-      <c r="C38" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>270</v>
-      </c>
-      <c r="C39" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>273</v>
-      </c>
-      <c r="C40" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>274</v>
-      </c>
-      <c r="C41" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>278</v>
-      </c>
-      <c r="C42" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>280</v>
-      </c>
-      <c r="C43" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>282</v>
-      </c>
-      <c r="C44" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>284</v>
-      </c>
-      <c r="C45" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>286</v>
-      </c>
-      <c r="C46" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C47" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>292</v>
-      </c>
-      <c r="C48" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>293</v>
-      </c>
-      <c r="C49" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>296</v>
-      </c>
-      <c r="C50" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>300</v>
-      </c>
-      <c r="C51" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>302</v>
-      </c>
-      <c r="C52" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>313</v>
-      </c>
-      <c r="C53" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>320</v>
-      </c>
-      <c r="C54" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>322</v>
-      </c>
-      <c r="C55" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>326</v>
-      </c>
-      <c r="C56" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>328</v>
-      </c>
-      <c r="C57" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
-        <v>335</v>
-      </c>
-      <c r="C58" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="s">
-        <v>337</v>
-      </c>
-      <c r="C59" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>340</v>
-      </c>
-      <c r="C60" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
-        <v>343</v>
-      </c>
-      <c r="C61" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>404</v>
-      </c>
-      <c r="C62" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>400</v>
-      </c>
-      <c r="C63" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>415</v>
-      </c>
-      <c r="C64" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>64</v>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>580</v>
       </c>
       <c r="B65" t="s">
-        <v>421</v>
-      </c>
-      <c r="C65" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>65</v>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>184</v>
       </c>
       <c r="B66" t="s">
-        <v>423</v>
-      </c>
-      <c r="C66" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>66</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>433</v>
       </c>
       <c r="B67" t="s">
-        <v>429</v>
-      </c>
-      <c r="C67" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>67</v>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>432</v>
       </c>
       <c r="B68" t="s">
         <v>434</v>
       </c>
-      <c r="C68" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>68</v>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>462</v>
       </c>
       <c r="B69" t="s">
-        <v>439</v>
-      </c>
-      <c r="C69" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>69</v>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>224</v>
       </c>
       <c r="B70" t="s">
-        <v>445</v>
-      </c>
-      <c r="C70" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>70</v>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>599</v>
       </c>
       <c r="B71" t="s">
-        <v>458</v>
-      </c>
-      <c r="C71" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>399</v>
+      </c>
+      <c r="B72" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>212</v>
+      </c>
+      <c r="B73" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>456</v>
+      </c>
+      <c r="B74" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>461</v>
-      </c>
-      <c r="C72" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>465</v>
-      </c>
-      <c r="C73" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>470</v>
-      </c>
-      <c r="C74" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>74</v>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>476</v>
       </c>
       <c r="B75" t="s">
-        <v>476</v>
-      </c>
-      <c r="C75" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>75</v>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>587</v>
       </c>
       <c r="B76" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+      <c r="B77" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>170</v>
+      </c>
+      <c r="B78" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>408</v>
+      </c>
+      <c r="B79" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>627</v>
+      </c>
+      <c r="B80" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B81" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>581</v>
+      </c>
+      <c r="B82" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>250</v>
+      </c>
+      <c r="B83" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>179</v>
+      </c>
+      <c r="B84" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>634</v>
+      </c>
+      <c r="B85" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>600</v>
+      </c>
+      <c r="B86" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>478</v>
+      </c>
+      <c r="B89" t="s">
         <v>477</v>
       </c>
-      <c r="C76" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>482</v>
-      </c>
-      <c r="C77" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>494</v>
-      </c>
-      <c r="C78" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>495</v>
-      </c>
-      <c r="C79" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>499</v>
-      </c>
-      <c r="C80" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>503</v>
-      </c>
-      <c r="C81" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>520</v>
-      </c>
-      <c r="C82" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>523</v>
-      </c>
-      <c r="C83" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>526</v>
-      </c>
-      <c r="C84" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>528</v>
-      </c>
-      <c r="C85" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>529</v>
-      </c>
-      <c r="C86" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>530</v>
-      </c>
-      <c r="C87" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>540</v>
-      </c>
-      <c r="C88" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>542</v>
-      </c>
-      <c r="C89" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>89</v>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>597</v>
       </c>
       <c r="B90" t="s">
-        <v>544</v>
-      </c>
-      <c r="C90" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>90</v>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>598</v>
       </c>
       <c r="B91" t="s">
-        <v>549</v>
-      </c>
-      <c r="C91" t="s">
-        <v>548</v>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>268</v>
+      </c>
+      <c r="B92" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C3" xr:uid="{7423E71A-C3BA-4E9A-8679-88DDD26ECF27}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C77">
+  <autoFilter ref="A1:B3" xr:uid="{7423E71A-C3BA-4E9A-8679-88DDD26ECF27}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B180">
       <sortCondition ref="A1:A3"/>
     </sortState>
   </autoFilter>
@@ -3797,894 +3546,915 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.7265625" style="24" customWidth="1"/>
-    <col min="2" max="2" width="14.6328125" style="24" customWidth="1"/>
-    <col min="3" max="3" width="37.90625" style="24" customWidth="1"/>
-    <col min="4" max="4" width="23" style="24" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" style="24" customWidth="1"/>
-    <col min="6" max="6" width="21.54296875" style="24" customWidth="1"/>
-    <col min="7" max="7" width="22.7265625" style="24" customWidth="1"/>
-    <col min="8" max="8" width="23.453125" style="24" customWidth="1"/>
-    <col min="9" max="9" width="41.1796875" style="24" customWidth="1"/>
-    <col min="10" max="10" width="31.08984375" style="24" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="24"/>
+    <col min="1" max="1" width="35.7265625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="37.90625" style="41" customWidth="1"/>
+    <col min="4" max="4" width="45.6328125" style="41" customWidth="1"/>
+    <col min="5" max="5" width="17.6328125" style="41" customWidth="1"/>
+    <col min="6" max="6" width="32.08984375" style="41" customWidth="1"/>
+    <col min="7" max="7" width="22.7265625" style="41" customWidth="1"/>
+    <col min="8" max="8" width="23.453125" style="41" customWidth="1"/>
+    <col min="9" max="9" width="41.1796875" style="41" customWidth="1"/>
+    <col min="10" max="10" width="36.7265625" style="41" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="24" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>618</v>
-      </c>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="53" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="2" spans="1:10" s="7" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
-        <v>609</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>544</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>545</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="24" t="s">
+        <v>512</v>
+      </c>
+      <c r="B3" s="26">
+        <v>0</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="B4" s="26">
+        <v>34</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="B5" s="26">
+        <v>56</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="24" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="26">
+        <v>66</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>526</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>623</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="B7" s="26">
+        <v>94</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="24" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="24" t="s">
         <v>513</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="B9" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="B10" s="26">
+        <v>201</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="F10" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="24" t="s">
+        <v>547</v>
+      </c>
+      <c r="B12" s="26">
+        <v>248</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="B13" s="26">
+        <v>252</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
+        <v>536</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>568</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="24" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="26">
+        <v>325</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="B16" s="26">
+        <v>360</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="24" t="s">
         <v>514</v>
       </c>
-      <c r="F2" s="29" t="s">
-        <v>610</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>611</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="B3" s="30">
-        <v>0</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="J3" s="25" t="s">
+      <c r="B17" s="24">
+        <v>371</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="24" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="25" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>575</v>
-      </c>
-      <c r="B4" s="30">
-        <v>34</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>589</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="25" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
-        <v>574</v>
-      </c>
-      <c r="B5" s="30">
-        <v>56</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="25" t="s">
+      <c r="I17" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="24" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A18" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="B18" s="26">
+        <v>381</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="B19" s="26">
+        <v>386</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B20" s="26">
+        <v>423.5</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="J20" s="24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A21" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="B21" s="26">
+        <v>428</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A22" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="B22" s="26">
+        <v>433</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="24" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A23" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="B23" s="26">
+        <v>445</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="26">
+        <v>495</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="24" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="25" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="30">
-        <v>66</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>592</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>591</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
-        <v>572</v>
-      </c>
-      <c r="B7" s="30">
-        <v>94</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>593</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="25" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
-        <v>573</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>515</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>516</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="30">
-        <v>201</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>597</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I11" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11" s="25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
-        <v>613</v>
-      </c>
-      <c r="B12" s="30">
-        <v>248</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I12" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
-        <v>598</v>
-      </c>
-      <c r="B13" s="30">
-        <v>252</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="25" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
-        <v>602</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>634</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>601</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="25" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="B15" s="30">
-        <v>325</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>603</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>605</v>
-      </c>
-      <c r="B16" s="30">
-        <v>360</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>606</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>607</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="J16" s="25" t="s">
+      <c r="H25" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="27" t="s">
+        <v>549</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="27" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
-        <v>578</v>
-      </c>
-      <c r="B17" s="25">
-        <v>371</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="25" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
-        <v>579</v>
-      </c>
-      <c r="B18" s="30">
-        <v>381</v>
-      </c>
-      <c r="C18" s="25" t="s">
+      <c r="G26" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
-        <v>608</v>
-      </c>
-      <c r="B19" s="30">
-        <v>386</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="J19" s="25" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>580</v>
-      </c>
-      <c r="B20" s="30">
-        <v>423.5</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>588</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="B21" s="30">
-        <v>428</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="25" t="s">
-        <v>582</v>
-      </c>
-      <c r="B22" s="30">
-        <v>433</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="25" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A23" s="25" t="s">
-        <v>583</v>
-      </c>
-      <c r="B23" s="30">
-        <v>445</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>546</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A24" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="B24" s="30">
-        <v>495</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="25" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="25" t="s">
-        <v>614</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="H25" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I25" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" s="25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A26" s="31" t="s">
-        <v>615</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="G26" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="I26" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="J26" s="31" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
-        <v>584</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-    </row>
-    <row r="28" spans="1:10" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="28" t="s">
-        <v>585</v>
-      </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-    </row>
-    <row r="29" spans="1:10" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
-        <v>586</v>
-      </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-    </row>
-    <row r="30" spans="1:10" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="28" t="s">
-        <v>617</v>
-      </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-    </row>
-    <row r="31" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="34" t="s">
-        <v>616</v>
-      </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="27"/>
-    </row>
-    <row r="32" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="28"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="43" t="s">
+        <v>520</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="44" t="s">
+        <v>521</v>
+      </c>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="44" t="s">
+        <v>522</v>
+      </c>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="44" t="s">
+        <v>551</v>
+      </c>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+    </row>
+    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="45" t="s">
+        <v>550</v>
+      </c>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="42"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4695,249 +4465,249 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.7265625" style="35" customWidth="1"/>
-    <col min="2" max="2" width="20" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.7265625" style="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.453125" style="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.6328125" style="35" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="35"/>
+    <col min="1" max="1" width="31.7265625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="20" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="29" customWidth="1"/>
+    <col min="5" max="5" width="52.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.6328125" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>631</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="47" t="s">
-        <v>612</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>345</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>346</v>
-      </c>
-      <c r="D2" s="47" t="s">
-        <v>622</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>347</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>349</v>
+      <c r="A2" s="35" t="s">
+        <v>546</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>556</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="87" x14ac:dyDescent="0.35">
-      <c r="A3" s="38" t="s">
-        <v>633</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>383</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>385</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>386</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>387</v>
+      <c r="A3" s="31" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
-        <v>632</v>
-      </c>
-      <c r="B4" s="44">
+      <c r="A4" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="B4" s="47">
         <v>0.3</v>
       </c>
-      <c r="C4" s="45" t="s">
-        <v>380</v>
-      </c>
-      <c r="D4" s="44">
+      <c r="C4" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="52">
         <v>0.05</v>
       </c>
-      <c r="E4" s="46" t="s">
-        <v>381</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>635</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>382</v>
+      <c r="E4" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="42">
+      <c r="A5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="48">
         <v>140</v>
       </c>
-      <c r="C5" s="37" t="s">
-        <v>377</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>629</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>378</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>379</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>630</v>
+      <c r="C5" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" s="51" t="s">
+        <v>563</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="A6" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>518</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>373</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>628</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>374</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>375</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>376</v>
+      <c r="A6" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>454</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>562</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>627</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>626</v>
-      </c>
-      <c r="D7" s="39">
+      <c r="A7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>561</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="D7" s="51">
         <v>40</v>
       </c>
-      <c r="E7" s="36" t="s">
-        <v>369</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>370</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>371</v>
+      <c r="E7" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="118" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>625</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>388</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>366</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>367</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>368</v>
+      <c r="A8" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>559</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="87" x14ac:dyDescent="0.35">
-      <c r="A9" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>512</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>624</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>361</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>362</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>363</v>
+      <c r="A9" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>448</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>558</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>570</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="36" t="s">
-        <v>354</v>
-      </c>
-      <c r="B10" s="37">
+      <c r="A10" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="46">
         <v>3800</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>356</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>357</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>358</v>
+      <c r="C10" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>557</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="87" x14ac:dyDescent="0.35">
-      <c r="A11" s="48" t="s">
-        <v>350</v>
+      <c r="A11" s="36" t="s">
+        <v>294</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>351</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>619</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>620</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>352</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>353</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>621</v>
+        <v>295</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>553</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>554</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="F11" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -4953,68 +4723,68 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.7265625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15.08984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.90625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="69.08984375" style="4" customWidth="1"/>
     <col min="12" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>474</v>
+        <v>412</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>391</v>
+        <v>334</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>392</v>
+        <v>335</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>393</v>
+        <v>336</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>394</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>567</v>
+        <v>503</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>570</v>
+        <v>506</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>571</v>
+        <v>507</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G2" s="10">
         <v>-1.1000000000000001E-3</v>
@@ -5029,23 +4799,23 @@
         <v>3300</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>395</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G3" s="10">
         <v>-1.1000000000000001E-3</v>
@@ -5060,23 +4830,23 @@
         <v>3300</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>395</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>568</v>
+        <v>504</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>569</v>
+        <v>505</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>571</v>
+        <v>507</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G4" s="10">
         <v>-1E-4</v>
@@ -5091,23 +4861,23 @@
         <v>300</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>395</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>428</v>
+        <v>366</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G5" s="10">
         <v>-1E-4</v>
@@ -5122,23 +4892,23 @@
         <v>300</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>395</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G6" s="11">
         <v>0</v>
@@ -5153,23 +4923,23 @@
         <v>200</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>438</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>480</v>
+        <v>418</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G7" s="11">
         <v>2.6</v>
@@ -5184,21 +4954,21 @@
         <v>500000</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>493</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G8" s="11">
         <v>34</v>
@@ -5213,23 +4983,23 @@
         <v>100000</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11">
         <v>56</v>
@@ -5244,27 +5014,27 @@
         <v>150000</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="G10" s="11">
         <v>66</v>
@@ -5279,21 +5049,21 @@
         <v>30</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>534</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>537</v>
+        <v>473</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G11" s="11">
         <v>94</v>
@@ -5308,21 +5078,21 @@
         <v>500000</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>538</v>
+        <v>474</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G12" s="11">
         <v>120</v>
@@ -5337,23 +5107,23 @@
         <v>500000</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>398</v>
+        <v>341</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>399</v>
+        <v>342</v>
       </c>
       <c r="G13" s="10">
         <v>140</v>
@@ -5368,23 +5138,23 @@
         <v>75000000</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>519</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>419</v>
+        <v>361</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G14" s="11">
         <v>143.1</v>
@@ -5399,21 +5169,21 @@
         <v>1000000</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>420</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G15" s="11">
         <v>183</v>
@@ -5428,24 +5198,24 @@
         <v>500000</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="G16" s="11">
         <v>201</v>
@@ -5460,21 +5230,21 @@
         <v>85000</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>405</v>
+        <v>347</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="G17" s="11">
         <v>234</v>
@@ -5489,21 +5259,21 @@
         <v>1090000</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G18" s="11">
         <v>248</v>
@@ -5518,27 +5288,27 @@
         <v>1000000</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>281</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>536</v>
+        <v>472</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="G19" s="11">
         <v>252</v>
@@ -5553,21 +5323,21 @@
         <v>60000</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>535</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>406</v>
+        <v>348</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="G20" s="11">
         <v>262</v>
@@ -5582,21 +5352,21 @@
         <v>1500000</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G21" s="11">
         <v>325</v>
@@ -5611,21 +5381,21 @@
         <v>4000000</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>334</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="G22" s="11">
         <v>360</v>
@@ -5640,25 +5410,25 @@
         <v>100000</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>339</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G23" s="11">
         <v>371</v>
@@ -5673,21 +5443,21 @@
         <v>100000</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G24" s="23">
         <v>381</v>
@@ -5702,21 +5472,21 @@
         <v>1500000</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>140</v>
+        <v>572</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="G25" s="23">
         <v>386</v>
@@ -5731,21 +5501,21 @@
         <v>100000</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>436</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G26" s="23">
         <v>423.5</v>
@@ -5760,21 +5530,21 @@
         <v>500000</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="G27" s="23">
         <v>428</v>
@@ -5789,21 +5559,21 @@
         <v>1000000</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>155</v>
+        <v>574</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>410</v>
+        <v>352</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="G28" s="23">
         <v>433</v>
@@ -5818,27 +5588,27 @@
         <v>1000000</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>159</v>
+        <v>575</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>425</v>
+        <v>363</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G29" s="23">
         <v>445</v>
@@ -5853,23 +5623,23 @@
         <v>500000</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>543</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>390</v>
+        <v>333</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>426</v>
+        <v>364</v>
       </c>
       <c r="G30" s="10">
         <v>475</v>
@@ -5884,21 +5654,21 @@
         <v>60000000</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>402</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="G31" s="11">
         <v>495</v>
@@ -5913,21 +5683,21 @@
         <v>2600000</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G32" s="11">
         <v>507</v>
@@ -5942,21 +5712,21 @@
         <v>500000</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G33" s="11">
         <v>513</v>
@@ -5971,23 +5741,23 @@
         <v>1000000</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>413</v>
+        <v>355</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>399</v>
+        <v>342</v>
       </c>
       <c r="G34" s="10">
         <v>545</v>
@@ -6002,21 +5772,21 @@
         <v>40000000</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>517</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>414</v>
+        <v>356</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="G35" s="11">
         <v>2220</v>
@@ -6031,23 +5801,23 @@
         <v>100000000</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>417</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>547</v>
+        <v>483</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="G36" s="10">
         <v>2400</v>
@@ -6062,7 +5832,7 @@
         <v>500000000</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>418</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -6092,28 +5862,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="52" t="s">
-        <v>509</v>
-      </c>
-      <c r="B1" s="52" t="s">
-        <v>510</v>
-      </c>
-      <c r="C1" s="53" t="s">
-        <v>391</v>
-      </c>
-      <c r="D1" s="53" t="s">
-        <v>392</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>393</v>
+      <c r="A1" s="39" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>446</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>507</v>
+        <v>443</v>
       </c>
       <c r="C2" s="21">
         <f>AVERAGEIF(table_s3_events!$E$2:$E$36, $A$2, table_s3_events!$H$2:$H$36)</f>
@@ -6130,10 +5900,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>508</v>
+        <v>444</v>
       </c>
       <c r="C3" s="21" cm="1">
         <f t="array" ref="C3">MEDIAN(IF(table_s3_events!$E$2:$E$36 = $A$3, table_s3_events!$H$2:$H$36))</f>
@@ -6150,10 +5920,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>511</v>
+        <v>447</v>
       </c>
       <c r="C4" s="21" cm="1">
         <f t="array" ref="C4">_xlfn.STDEV.P(IF(table_s3_events!$E$2:$E$36=$A$4, table_s3_events!$H$2:$H$36))</f>
@@ -6170,10 +5940,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>551</v>
+        <v>487</v>
       </c>
       <c r="C5" s="21" cm="1">
         <f t="array" ref="C5">MAX(IF(table_s3_events!$E$2:$E$36=$A$5, table_s3_events!$H$2:$H$36))</f>
@@ -6190,10 +5960,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>552</v>
+        <v>488</v>
       </c>
       <c r="C6" s="21" cm="1">
         <f t="array" ref="C6">MIN(IF(table_s3_events!$E$2:$E$36=$A$4, table_s3_events!$H$2:$H$36))</f>
@@ -6209,31 +5979,31 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="51" cm="1">
+      <c r="A7" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="38" cm="1">
         <f t="array" ref="C7">COUNT(IF(table_s3_events!$E$2:$E$36=$A$7, table_s3_events!$H$2:$H$36))</f>
         <v>5</v>
       </c>
-      <c r="D7" s="51" cm="1">
+      <c r="D7" s="38" cm="1">
         <f t="array" ref="D7">COUNT(IF(table_s3_events!$E$2:$E$36=$A$7, table_s3_events!$I$2:$I$36))</f>
         <v>5</v>
       </c>
-      <c r="E7" s="51" cm="1">
+      <c r="E7" s="38" cm="1">
         <f t="array" ref="E7">COUNT(IF(table_s3_events!$E$2:$E$36=$A$7, table_s3_events!$J$2:$J$36))</f>
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>507</v>
+        <v>443</v>
       </c>
       <c r="C8" s="21">
         <f>AVERAGEIF(table_s3_events!$E$2:$E$36, $A$8, table_s3_events!H2:H36)</f>
@@ -6250,10 +6020,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>508</v>
+        <v>444</v>
       </c>
       <c r="C9" s="21" cm="1">
         <f t="array" ref="C9">MEDIAN(IF(table_s3_events!$E$2:$E$36 = $A$9, table_s3_events!$J$2:$J$36))</f>
@@ -6270,10 +6040,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>511</v>
+        <v>447</v>
       </c>
       <c r="C10" s="21" cm="1">
         <f t="array" ref="C10">_xlfn.STDEV.P(IF(table_s3_events!$E$2:$E$36=$A$10, table_s3_events!H2:H36))</f>
@@ -6290,10 +6060,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>551</v>
+        <v>487</v>
       </c>
       <c r="C11" s="21" cm="1">
         <f t="array" ref="C11">MAX(IF(table_s3_events!$E$2:$E$36=$A$11, table_s3_events!$H$2:$H$36))</f>
@@ -6310,10 +6080,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>552</v>
+        <v>488</v>
       </c>
       <c r="C12" s="21" cm="1">
         <f t="array" ref="C12">MIN(IF(table_s3_events!$E$2:$E$36=$A$12, table_s3_events!$H$2:$H$36))</f>
@@ -6329,21 +6099,21 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="51" cm="1">
+      <c r="A13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="38" cm="1">
         <f t="array" ref="C13">COUNT(IF(table_s3_events!$E$2:$E$36=$A$13, table_s3_events!$H$2:$H$36))</f>
         <v>25</v>
       </c>
-      <c r="D13" s="51" cm="1">
+      <c r="D13" s="38" cm="1">
         <f t="array" ref="D13">COUNT(IF(table_s3_events!$E$2:$E$36=$A$13, table_s3_events!$I$2:$I$36))</f>
         <v>25</v>
       </c>
-      <c r="E13" s="51" cm="1">
+      <c r="E13" s="38" cm="1">
         <f t="array" ref="E13">COUNT(IF(table_s3_events!$E$2:$E$36=$A$13, table_s3_events!$J$2:$J$36))</f>
         <v>25</v>
       </c>
@@ -6372,9 +6142,10 @@
     <col min="11" max="11" width="15" style="18" customWidth="1"/>
     <col min="12" max="12" width="30.08984375" style="12" customWidth="1"/>
     <col min="13" max="13" width="13.26953125" style="12" customWidth="1"/>
-    <col min="14" max="14" width="19.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="8.7265625" style="12"/>
+    <col min="16" max="16" width="64.36328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.7265625" style="12"/>
     <col min="18" max="18" width="14.54296875" style="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.6328125" style="12" customWidth="1"/>
     <col min="20" max="16384" width="8.7265625" style="12"/>
@@ -6382,50 +6153,50 @@
   <sheetData>
     <row r="1" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="I1" s="14" t="str">
         <f>_xlfn.XLOOKUP(A1, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>event_duration_est_yr</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>506</v>
+        <v>442</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>479</v>
+        <v>417</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>451</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -6434,23 +6205,23 @@
         <v>2100 persistent - sustainable stewardship</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>569</v>
+        <v>505</v>
       </c>
       <c r="C2" s="12" t="str">
         <f>_xlfn.XLOOKUP($B2, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>sustainable stewardship</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>458</v>
+        <v>396</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H2" s="12">
         <v>0</v>
@@ -6468,16 +6239,16 @@
         <v>0</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>459</v>
+        <v>397</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>452</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -6486,23 +6257,23 @@
         <v>2100 persistent - sustainable stewardship</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>569</v>
+        <v>505</v>
       </c>
       <c r="C3" s="12" t="str">
         <f>_xlfn.XLOOKUP($B3, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>sustainable stewardship</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>458</v>
+        <v>396</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H3" s="12">
         <v>0</v>
@@ -6520,16 +6291,16 @@
         <v>0</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>459</v>
+        <v>397</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>453</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -6538,23 +6309,23 @@
         <v>3100 persistent - sustainable stewardship</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>570</v>
+        <v>506</v>
       </c>
       <c r="C4" s="12" t="str">
         <f>_xlfn.XLOOKUP($B4, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>sustainable stewardship</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H4" s="12">
         <v>2</v>
@@ -6572,16 +6343,16 @@
         <v>606.06060606060612</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>452</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -6590,23 +6361,23 @@
         <v>3100 persistent - sustainable stewardship</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>570</v>
+        <v>506</v>
       </c>
       <c r="C5" s="12" t="str">
         <f>_xlfn.XLOOKUP($B5, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>sustainable stewardship</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H5" s="12">
         <v>5</v>
@@ -6624,16 +6395,16 @@
         <v>1515.1515151515152</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>453</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
@@ -6642,23 +6413,23 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C6" s="12" t="str">
         <f>_xlfn.XLOOKUP($B6, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H6" s="12">
         <v>-32</v>
@@ -6676,13 +6447,13 @@
         <v>-106666.66666666667</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>454</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
@@ -6691,23 +6462,23 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C7" s="12" t="str">
         <f>_xlfn.XLOOKUP($B7, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H7" s="12">
         <v>-27</v>
@@ -6725,16 +6496,16 @@
         <v>-90000.000000000015</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>473</v>
+        <v>411</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>455</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
@@ -6743,23 +6514,23 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C8" s="12" t="str">
         <f>_xlfn.XLOOKUP($B8, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H8" s="12">
         <v>-17.600000000000001</v>
@@ -6777,10 +6548,10 @@
         <v>-58666.666666666679</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>471</v>
+        <v>409</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
@@ -6789,23 +6560,23 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C9" s="12" t="str">
         <f>_xlfn.XLOOKUP($B9, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H9" s="12">
         <v>-14</v>
@@ -6823,7 +6594,7 @@
         <v>-46666.666666666672</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>314</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -6832,23 +6603,23 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C10" s="12" t="str">
         <f>_xlfn.XLOOKUP($B10, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H10" s="12">
         <v>-13</v>
@@ -6866,10 +6637,10 @@
         <v>-43333.333333333336</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>472</v>
+        <v>410</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
@@ -6878,23 +6649,23 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C11" s="12" t="str">
         <f>_xlfn.XLOOKUP($B11, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>499</v>
+        <v>437</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H11" s="12">
         <v>-7.8</v>
@@ -6912,10 +6683,10 @@
         <v>-26000</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>502</v>
+        <v>440</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -6924,23 +6695,23 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C12" s="12" t="str">
         <f>_xlfn.XLOOKUP($B12, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>458</v>
+        <v>396</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H12" s="12">
         <v>-3.8</v>
@@ -6958,10 +6729,10 @@
         <v>-12666.666666666668</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>525</v>
+        <v>461</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -6970,23 +6741,23 @@
         <v>3100 transient - business as usual</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>_xlfn.XLOOKUP($B13, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>549</v>
+        <v>485</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H13" s="12">
         <v>-28</v>
@@ -7004,10 +6775,10 @@
         <v>-8484.8484848484841</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>550</v>
+        <v>486</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
@@ -7016,23 +6787,23 @@
         <v>3100 transient - business as usual</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="C14" s="12" t="str">
         <f>_xlfn.XLOOKUP($B14, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H14" s="12">
         <v>-10</v>
@@ -7050,10 +6821,10 @@
         <v>-3030.3030303030305</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>565</v>
+        <v>501</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -7062,23 +6833,23 @@
         <v>3100 transient - business as usual</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="C15" s="12" t="str">
         <f>_xlfn.XLOOKUP($B15, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>business as usual</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H15" s="12">
         <v>-5</v>
@@ -7096,10 +6867,10 @@
         <v>-1515.1515151515152</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>566</v>
+        <v>502</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>306</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
@@ -7108,23 +6879,23 @@
         <v>Recent past</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C16" s="12" t="str">
         <f>_xlfn.XLOOKUP($B16, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H16" s="12">
         <v>-83</v>
@@ -7142,10 +6913,10 @@
         <v>-415000</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -7154,23 +6925,23 @@
         <v>Recent past</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C17" s="12" t="str">
         <f>_xlfn.XLOOKUP($B17, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>441</v>
+        <v>379</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H17" s="12">
         <v>-50</v>
@@ -7188,7 +6959,7 @@
         <v>-250000</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -7197,23 +6968,23 @@
         <v>Recent past</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C18" s="12" t="str">
         <f>_xlfn.XLOOKUP($B18, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>300</v>
+        <v>248</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H18" s="12">
         <v>-30</v>
@@ -7231,10 +7002,10 @@
         <v>-150000</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>319</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -7243,23 +7014,23 @@
         <v>Recent past</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C19" s="12" t="str">
         <f>_xlfn.XLOOKUP($B19, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H19" s="12">
         <v>-1.61</v>
@@ -7277,10 +7048,10 @@
         <v>-8050</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>441</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -7289,23 +7060,23 @@
         <v>Recent past</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C20" s="12" t="str">
         <f>_xlfn.XLOOKUP($B20, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H20" s="12">
         <v>-1.54</v>
@@ -7323,10 +7094,10 @@
         <v>-7700</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>487</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -7335,23 +7106,23 @@
         <v>Recent past</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C21" s="12" t="str">
         <f>_xlfn.XLOOKUP($B21, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H21" s="12">
         <v>-0.88</v>
@@ -7369,10 +7140,10 @@
         <v>-4400</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>488</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -7381,23 +7152,23 @@
         <v>Recent past</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C22" s="12" t="str">
         <f>_xlfn.XLOOKUP($B22, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H22" s="12">
         <v>-0.57999999999999996</v>
@@ -7415,10 +7186,10 @@
         <v>-2899.9999999999995</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>489</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -7427,23 +7198,23 @@
         <v>Recent past</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C23" s="12" t="str">
         <f>_xlfn.XLOOKUP($B23, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>461</v>
+        <v>399</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H23" s="12">
         <v>-0.5</v>
@@ -7461,7 +7232,7 @@
         <v>-2500</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>500</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -7470,23 +7241,23 @@
         <v>Recent past</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C24" s="12" t="str">
         <f>_xlfn.XLOOKUP($B24, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H24" s="12">
         <v>-0.45</v>
@@ -7504,7 +7275,7 @@
         <v>-2250</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>307</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -7513,23 +7284,23 @@
         <v>Recent past</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C25" s="12" t="str">
         <f>_xlfn.XLOOKUP($B25, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>306</v>
+        <v>254</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H25" s="12">
         <v>-0.17</v>
@@ -7547,7 +7318,7 @@
         <v>-850</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>308</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -7556,23 +7327,23 @@
         <v>Recent past</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C26" s="12" t="str">
         <f>_xlfn.XLOOKUP($B26, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>461</v>
+        <v>399</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H26" s="12">
         <v>-0.01</v>
@@ -7596,23 +7367,23 @@
         <v>Recent past</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="C27" s="12" t="str">
         <f>_xlfn.XLOOKUP($B27, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>humans so far</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>499</v>
+        <v>437</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>500</v>
+        <v>438</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H27" s="12">
         <v>-1</v>
@@ -7630,7 +7401,7 @@
         <v>-5000</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>501</v>
+        <v>439</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
@@ -7639,23 +7410,23 @@
         <v>Angiosperm Revolution</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="C28" s="12" t="str">
         <f>_xlfn.XLOOKUP($B28, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H28" s="12">
         <v>150</v>
@@ -7673,7 +7444,7 @@
         <v>2</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -7682,23 +7453,23 @@
         <v>Angiosperm Revolution</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="C29" s="12" t="str">
         <f>_xlfn.XLOOKUP($B29, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H29" s="12">
         <v>161</v>
@@ -7716,7 +7487,7 @@
         <v>2.1466666666666665</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
@@ -7725,23 +7496,23 @@
         <v>Cambrian Agronomic Revolution</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>413</v>
+        <v>355</v>
       </c>
       <c r="C30" s="12" t="str">
         <f>_xlfn.XLOOKUP($B30, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H30" s="12">
         <v>243</v>
@@ -7759,7 +7530,7 @@
         <v>6.0750000000000002</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -7768,23 +7539,23 @@
         <v>Cambrian Agronomic Revolution</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>413</v>
+        <v>355</v>
       </c>
       <c r="C31" s="12" t="str">
         <f>_xlfn.XLOOKUP($B31, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H31" s="12">
         <v>1000</v>
@@ -7802,7 +7573,7 @@
         <v>25</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>317</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
@@ -7811,23 +7582,23 @@
         <v>Cambrian Agronomic Revolution</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>413</v>
+        <v>355</v>
       </c>
       <c r="C32" s="12" t="str">
         <f>_xlfn.XLOOKUP($B32, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H32" s="12">
         <v>1000</v>
@@ -7845,7 +7616,7 @@
         <v>25</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
@@ -7854,23 +7625,23 @@
         <v>Eukaryogenesis</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>414</v>
+        <v>356</v>
       </c>
       <c r="C33" s="12" t="str">
         <f>_xlfn.XLOOKUP($B33, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H33" s="12">
         <v>600</v>
@@ -7888,7 +7659,7 @@
         <v>6</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>433</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
@@ -7897,23 +7668,23 @@
         <v>Great Oxygenation Event</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C34" s="12" t="str">
         <f>_xlfn.XLOOKUP($B34, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H34" s="12">
         <v>458</v>
@@ -7931,7 +7702,7 @@
         <v>0.91600000000000004</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>447</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
@@ -7940,23 +7711,23 @@
         <v>Great Oxygenation Event</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C35" s="12" t="str">
         <f>_xlfn.XLOOKUP($B35, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H35" s="12">
         <v>188000</v>
@@ -7974,7 +7745,7 @@
         <v>376</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>446</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
@@ -7983,23 +7754,23 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C36" s="12" t="str">
         <f>_xlfn.XLOOKUP($B36, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>477</v>
+        <v>415</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H36" s="12">
         <v>35</v>
@@ -8017,7 +7788,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>478</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -8026,23 +7797,23 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C37" s="12" t="str">
         <f>_xlfn.XLOOKUP($B37, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>477</v>
+        <v>415</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H37" s="12">
         <v>80</v>
@@ -8060,7 +7831,7 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>478</v>
+        <v>416</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
@@ -8069,23 +7840,23 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C38" s="12" t="str">
         <f>_xlfn.XLOOKUP($B38, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H38" s="12">
         <v>147</v>
@@ -8103,7 +7874,7 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
@@ -8112,23 +7883,23 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C39" s="12" t="str">
         <f>_xlfn.XLOOKUP($B39, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H39" s="12">
         <v>900</v>
@@ -8146,7 +7917,7 @@
         <v>15</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
@@ -8155,23 +7926,23 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C40" s="12" t="str">
         <f>_xlfn.XLOOKUP($B40, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>465</v>
+        <v>403</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H40" s="12">
         <v>12000</v>
@@ -8189,7 +7960,7 @@
         <v>200</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>468</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
@@ -8198,23 +7969,23 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C41" s="12" t="str">
         <f>_xlfn.XLOOKUP($B41, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>persistent</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>292</v>
+        <v>242</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H41" s="12">
         <v>18000</v>
@@ -8232,7 +8003,7 @@
         <v>300</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>467</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
@@ -8241,23 +8012,23 @@
         <v>Carnian (Triassic)</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>405</v>
+        <v>347</v>
       </c>
       <c r="C42" s="12" t="str">
         <f>_xlfn.XLOOKUP($B42, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H42" s="12">
         <v>-62</v>
@@ -8275,7 +8046,7 @@
         <v>-56.880733944954123</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
@@ -8284,23 +8055,23 @@
         <v>Carnian (Triassic)</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>405</v>
+        <v>347</v>
       </c>
       <c r="C43" s="12" t="str">
         <f>_xlfn.XLOOKUP($B43, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H43" s="12">
         <v>-51</v>
@@ -8318,7 +8089,7 @@
         <v>-46.788990825688067</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
@@ -8327,23 +8098,23 @@
         <v>Carnian (Triassic)</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>405</v>
+        <v>347</v>
       </c>
       <c r="C44" s="12" t="str">
         <f>_xlfn.XLOOKUP($B44, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H44" s="12">
         <v>-33</v>
@@ -8361,7 +8132,7 @@
         <v>-30.275229357798164</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
@@ -8370,23 +8141,23 @@
         <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C45" s="12" t="str">
         <f>_xlfn.XLOOKUP($B45, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H45" s="12">
         <v>-40</v>
@@ -8410,23 +8181,23 @@
         <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C46" s="12" t="str">
         <f>_xlfn.XLOOKUP($B46, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H46" s="12">
         <v>-40</v>
@@ -8450,23 +8221,23 @@
         <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C47" s="12" t="str">
         <f>_xlfn.XLOOKUP($B47, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H47" s="12">
         <v>-39</v>
@@ -8490,23 +8261,23 @@
         <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C48" s="12" t="str">
         <f>_xlfn.XLOOKUP($B48, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>520</v>
+        <v>456</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H48" s="12">
         <v>-75</v>
@@ -8524,7 +8295,7 @@
         <v>-2500000</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>522</v>
+        <v>458</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -8533,23 +8304,23 @@
         <v>End-Guadalupian (Capitanian; Permian)</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>406</v>
+        <v>348</v>
       </c>
       <c r="C49" s="12" t="str">
         <f>_xlfn.XLOOKUP($B49, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H49" s="12">
         <v>-48</v>
@@ -8573,23 +8344,23 @@
         <v>End-Guadalupian (Capitanian; Permian)</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>406</v>
+        <v>348</v>
       </c>
       <c r="C50" s="12" t="str">
         <f>_xlfn.XLOOKUP($B50, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H50" s="12">
         <v>-34</v>
@@ -8613,23 +8384,23 @@
         <v>End-Guadalupian (Capitanian; Permian)</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>406</v>
+        <v>348</v>
       </c>
       <c r="C51" s="12" t="str">
         <f>_xlfn.XLOOKUP($B51, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H51" s="12">
         <v>-25</v>
@@ -8653,23 +8424,23 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C52" s="12" t="str">
         <f>_xlfn.XLOOKUP($B52, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H52" s="12">
         <v>-95</v>
@@ -8693,23 +8464,23 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C53" s="12" t="str">
         <f>_xlfn.XLOOKUP($B53, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H53" s="12">
         <v>-83</v>
@@ -8733,23 +8504,23 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C54" s="12" t="str">
         <f>_xlfn.XLOOKUP($B54, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>296</v>
+        <v>244</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H54" s="12">
         <v>-70</v>
@@ -8773,23 +8544,23 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C55" s="12" t="str">
         <f>_xlfn.XLOOKUP($B55, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H55" s="12">
         <v>-62</v>
@@ -8813,23 +8584,23 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C56" s="12" t="str">
         <f>_xlfn.XLOOKUP($B56, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H56" s="12">
         <v>-56</v>
@@ -8853,23 +8624,23 @@
         <v>End-Triassic</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C57" s="12" t="str">
         <f>_xlfn.XLOOKUP($B57, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H57" s="12">
         <v>-80</v>
@@ -8893,23 +8664,23 @@
         <v>End-Triassic</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C58" s="12" t="str">
         <f>_xlfn.XLOOKUP($B58, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H58" s="12">
         <v>-73</v>
@@ -8933,23 +8704,23 @@
         <v>End-Triassic</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C59" s="12" t="str">
         <f>_xlfn.XLOOKUP($B59, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H59" s="12">
         <v>-47</v>
@@ -8973,23 +8744,23 @@
         <v>Eocene-Oligocene transition</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="C60" s="12" t="str">
         <f>_xlfn.XLOOKUP($B60, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H60" s="12">
         <v>-77</v>
@@ -9013,23 +8784,23 @@
         <v>Eocene-Oligocene transition</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="C61" s="12" t="str">
         <f>_xlfn.XLOOKUP($B61, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H61" s="12">
         <v>-16</v>
@@ -9053,23 +8824,23 @@
         <v>Eocene-Oligocene transition</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="C62" s="12" t="str">
         <f>_xlfn.XLOOKUP($B62, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H62" s="12">
         <v>-15</v>
@@ -9093,23 +8864,23 @@
         <v>Frasnian-Famenian (Late Devonian)</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C63" s="12" t="str">
         <f>_xlfn.XLOOKUP($B63, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H63" s="12">
         <v>-40</v>
@@ -9133,23 +8904,23 @@
         <v>Frasnian-Famenian (Late Devonian)</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C64" s="12" t="str">
         <f>_xlfn.XLOOKUP($B64, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H64" s="12">
         <v>-35</v>
@@ -9173,23 +8944,23 @@
         <v>Frasnian-Famenian (Late Devonian)</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C65" s="12" t="str">
         <f>_xlfn.XLOOKUP($B65, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H65" s="12">
         <v>-18</v>
@@ -9213,23 +8984,23 @@
         <v>Hangenberg Event (end-Devonian)</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="C66" s="12" t="str">
         <f>_xlfn.XLOOKUP($B66, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H66" s="12">
         <v>-50</v>
@@ -9253,23 +9024,23 @@
         <v>Hangenberg Event (end-Devonian)</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="C67" s="12" t="str">
         <f>_xlfn.XLOOKUP($B67, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H67" s="12">
         <v>-31</v>
@@ -9293,23 +9064,23 @@
         <v>Ireviken Event (Sheinwoodian, Wenlock, Silurian)</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>410</v>
+        <v>352</v>
       </c>
       <c r="C68" s="12" t="str">
         <f>_xlfn.XLOOKUP($B68, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H68" s="12">
         <v>-22</v>
@@ -9333,23 +9104,23 @@
         <v>Jurassic-Cretaceous extinction (Tithonian)</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="C69" s="12" t="str">
         <f>_xlfn.XLOOKUP($B69, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H69" s="12">
         <v>-20</v>
@@ -9374,23 +9145,23 @@
         <v>Kačák Event (Eifelian, Middle Devonian)</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C70" s="12" t="str">
         <f>_xlfn.XLOOKUP($B70, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H70" s="12">
         <v>-32</v>
@@ -9415,22 +9186,22 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>540</v>
+        <v>476</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H71" s="12">
         <v>-85</v>
@@ -9455,22 +9226,22 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>540</v>
+        <v>476</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H72" s="12">
         <v>-49</v>
@@ -9496,23 +9267,23 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C73" s="12" t="str">
         <f>_xlfn.XLOOKUP($B73, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H73" s="12">
         <v>-57</v>
@@ -9537,23 +9308,23 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C74" s="12" t="str">
         <f>_xlfn.XLOOKUP($B74, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H74" s="12">
         <v>-52</v>
@@ -9579,23 +9350,23 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C75" s="12" t="str">
         <f>_xlfn.XLOOKUP($B75, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H75" s="12">
         <v>-46</v>
@@ -9619,23 +9390,23 @@
         <v>Lau Event (Ludfordian, Ludlow, Silurian)</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="C76" s="12" t="str">
         <f>_xlfn.XLOOKUP($B76, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H76" s="12">
         <v>-21</v>
@@ -9659,23 +9430,23 @@
         <v>Lau Event (Ludfordian, Ludlow, Silurian)</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="C77" s="12" t="str">
         <f>_xlfn.XLOOKUP($B77, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H77" s="12">
         <v>-9</v>
@@ -9699,23 +9470,23 @@
         <v>Mulde Event (Homerian, Wenlock, Silurian)</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="C78" s="12" t="str">
         <f>_xlfn.XLOOKUP($B78, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H78" s="12">
         <v>-25</v>
@@ -9739,23 +9510,23 @@
         <v>OAE1a (Aptian)</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="C79" s="12" t="str">
         <f>_xlfn.XLOOKUP($B79, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H79" s="12">
         <v>-22</v>
@@ -9779,23 +9550,23 @@
         <v>OAE2 (Cenomanian-Turonian)</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="C80" s="12" t="str">
         <f>_xlfn.XLOOKUP($B80, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H80" s="12">
         <v>-20</v>
@@ -9819,23 +9590,23 @@
         <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C81" s="12" t="str">
         <f>_xlfn.XLOOKUP($B81, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H81" s="12">
         <v>-65</v>
@@ -9859,23 +9630,23 @@
         <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C82" s="12" t="str">
         <f>_xlfn.XLOOKUP($B82, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H82" s="12">
         <v>-33</v>
@@ -9899,23 +9670,23 @@
         <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C83" s="12" t="str">
         <f>_xlfn.XLOOKUP($B83, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H83" s="12">
         <v>-20</v>
@@ -9939,23 +9710,23 @@
         <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C84" s="12" t="str">
         <f>_xlfn.XLOOKUP($B84, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H84" s="12">
         <v>-1</v>
@@ -9979,23 +9750,23 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="C85" s="12" t="str">
         <f>_xlfn.XLOOKUP($B85, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H85" s="12">
         <v>-0.5</v>
@@ -10013,7 +9784,7 @@
         <v>-1</v>
       </c>
       <c r="L85" s="12" t="s">
-        <v>485</v>
+        <v>423</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
@@ -10022,23 +9793,23 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="C86" s="12" t="str">
         <f>_xlfn.XLOOKUP($B86, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H86" s="12">
         <v>-11</v>
@@ -10056,7 +9827,7 @@
         <v>-22</v>
       </c>
       <c r="L86" s="12" t="s">
-        <v>486</v>
+        <v>424</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
@@ -10065,23 +9836,23 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="C87" s="12" t="str">
         <f>_xlfn.XLOOKUP($B87, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>487</v>
+        <v>425</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H87" s="12">
         <v>-36</v>
@@ -10099,7 +9870,7 @@
         <v>-72</v>
       </c>
       <c r="L87" s="12" t="s">
-        <v>491</v>
+        <v>429</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
@@ -10108,23 +9879,23 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="C88" s="12" t="str">
         <f>_xlfn.XLOOKUP($B88, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>488</v>
+        <v>426</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H88" s="12">
         <v>-49</v>
@@ -10142,7 +9913,7 @@
         <v>-98</v>
       </c>
       <c r="L88" s="12" t="s">
-        <v>492</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
@@ -10151,23 +9922,23 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="C89" s="12" t="str">
         <f>_xlfn.XLOOKUP($B89, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>489</v>
+        <v>427</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H89" s="12">
         <v>-42</v>
@@ -10185,7 +9956,7 @@
         <v>-84</v>
       </c>
       <c r="L89" s="12" t="s">
-        <v>490</v>
+        <v>428</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
@@ -10194,23 +9965,23 @@
         <v>Redlichiid-Olenellid trilobite Extinction Carbon isotope Excursion (ROECE; Cambrian Stage 4–Miaolingian boundary)</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="C90" s="12" t="str">
         <f>_xlfn.XLOOKUP($B90, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F90" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H90" s="12">
         <v>-50</v>
@@ -10228,7 +9999,7 @@
         <v>-100</v>
       </c>
       <c r="L90" s="12" t="s">
-        <v>431</v>
+        <v>369</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
@@ -10237,23 +10008,23 @@
         <v>Serpukhovian (late Mississippian; Carboniferous)</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="C91" s="12" t="str">
         <f>_xlfn.XLOOKUP($B91, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H91" s="12">
         <v>-39</v>
@@ -10277,23 +10048,23 @@
         <v>Serpukhovian (late Mississippian; Carboniferous)</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="C92" s="12" t="str">
         <f>_xlfn.XLOOKUP($B92, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H92" s="12">
         <v>-31</v>
@@ -10317,23 +10088,23 @@
         <v>Serpukhovian (late Mississippian; Carboniferous)</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="C93" s="12" t="str">
         <f>_xlfn.XLOOKUP($B93, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H93" s="12">
         <v>-14</v>
@@ -10357,23 +10128,23 @@
         <v>Sinsk Event / Archaeocyath Extinction Carbon isotope Excursion (AECE; Cambrian Stage 4)</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="C94" s="12" t="str">
         <f>_xlfn.XLOOKUP($B94, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H94" s="12">
         <v>-50</v>
@@ -10391,7 +10162,7 @@
         <v>-50</v>
       </c>
       <c r="L94" s="12" t="s">
-        <v>431</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
@@ -10400,23 +10171,23 @@
         <v>Sinsk Event / Archaeocyath Extinction Carbon isotope Excursion (AECE; Cambrian Stage 4)</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="C95" s="12" t="str">
         <f>_xlfn.XLOOKUP($B95, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H95" s="12">
         <v>-49</v>
@@ -10440,23 +10211,23 @@
         <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C96" s="12" t="str">
         <f>_xlfn.XLOOKUP($B96, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H96" s="12">
         <v>-65</v>
@@ -10480,23 +10251,23 @@
         <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C97" s="12" t="str">
         <f>_xlfn.XLOOKUP($B97, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H97" s="12">
         <v>-60</v>
@@ -10514,7 +10285,7 @@
         <v>-23.076923076923077</v>
       </c>
       <c r="L97" s="12" t="s">
-        <v>432</v>
+        <v>370</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
@@ -10523,23 +10294,23 @@
         <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C98" s="12" t="str">
         <f>_xlfn.XLOOKUP($B98, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H98" s="12">
         <v>-59</v>
@@ -10563,23 +10334,23 @@
         <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C99" s="12" t="str">
         <f>_xlfn.XLOOKUP($B99, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H99" s="12">
         <v>-58</v>
@@ -10603,23 +10374,23 @@
         <v>Taghanic Event (Giventian, Middle Devonian)</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="C100" s="12" t="str">
         <f>_xlfn.XLOOKUP($B100, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>210</v>
+        <v>589</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G100" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H100" s="12">
         <v>-36</v>
@@ -10643,23 +10414,23 @@
         <v>Taghanic Event (Giventian, Middle Devonian)</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="C101" s="12" t="str">
         <f>_xlfn.XLOOKUP($B101, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H101" s="12">
         <v>-29</v>
@@ -10683,23 +10454,23 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C102" s="12" t="str">
         <f>_xlfn.XLOOKUP($B102, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F102" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G102" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H102" s="12">
         <v>-25</v>
@@ -10723,23 +10494,23 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C103" s="12" t="str">
         <f>_xlfn.XLOOKUP($B103, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H103" s="12">
         <v>-22</v>
@@ -10763,23 +10534,23 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C104" s="12" t="str">
         <f>_xlfn.XLOOKUP($B104, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H104" s="12">
         <v>-20</v>
@@ -10803,23 +10574,23 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C105" s="12" t="str">
         <f>_xlfn.XLOOKUP($B105, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
         <v>transient</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="H105" s="12">
         <v>-15</v>
@@ -10844,52 +10615,9 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D17:D20 D63:D1048576 D1:D14 D22:D60">
-    <cfRule type="beginsWith" dxfId="11" priority="11" operator="beginsWith" text="guess">
-      <formula>LEFT(D1,LEN("guess"))="guess"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="10" priority="13" operator="beginsWith" text="estimate">
-      <formula>LEFT(D1,LEN("estimate"))="estimate"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D21">
-    <cfRule type="beginsWith" dxfId="9" priority="9" operator="beginsWith" text="guess">
-      <formula>LEFT(D21,LEN("guess"))="guess"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="8" priority="10" operator="beginsWith" text="estimate">
-      <formula>LEFT(D21,LEN("estimate"))="estimate"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16">
-    <cfRule type="beginsWith" dxfId="7" priority="7" operator="beginsWith" text="guess">
-      <formula>LEFT(D16,LEN("guess"))="guess"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="6" priority="8" operator="beginsWith" text="estimate">
-      <formula>LEFT(D16,LEN("estimate"))="estimate"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="beginsWith" dxfId="5" priority="5" operator="beginsWith" text="guess">
-      <formula>LEFT(D15,LEN("guess"))="guess"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="4" priority="6" operator="beginsWith" text="estimate">
-      <formula>LEFT(D15,LEN("estimate"))="estimate"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D62">
-    <cfRule type="beginsWith" dxfId="3" priority="3" operator="beginsWith" text="guess">
-      <formula>LEFT(D62,LEN("guess"))="guess"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="2" priority="4" operator="beginsWith" text="estimate">
-      <formula>LEFT(D62,LEN("estimate"))="estimate"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D61">
-    <cfRule type="beginsWith" dxfId="1" priority="1" operator="beginsWith" text="guess">
-      <formula>LEFT(D61,LEN("guess"))="guess"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="0" priority="2" operator="beginsWith" text="estimate">
-      <formula>LEFT(D61,LEN("estimate"))="estimate"</formula>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10916,7 +10644,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CCD39283-F4E1-4D52-B7DE-3097070FAE2B}">
           <x14:formula1>
-            <xm:f>references!$B:$B</xm:f>
+            <xm:f>references!$A:$A</xm:f>
           </x14:formula1>
           <xm:sqref>D1:D1048576</xm:sqref>
         </x14:dataValidation>
@@ -10927,26 +10655,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EE3B5FF1D6D93545B0A9BE76E04A5739" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b213452e5774ccb18cdbac914376359f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af" xmlns:ns3="d7940701-fd28-48c6-89b6-2769869457dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94bb0651eba29840b02d7d9879aff2b0" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
@@ -11141,32 +10849,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D4D638-0E0C-48CA-BE88-3BE2B56E957A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11183,4 +10886,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/disruptors_supplementary_data_tables_s1-s5.xlsx
+++ b/data/disruptors_supplementary_data_tables_s1-s5.xlsx
@@ -2274,15 +2274,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -2304,6 +2295,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2311,95 +2311,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3765,7 +3681,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="24" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="24" t="s">
         <v>509</v>
       </c>
@@ -4085,7 +4001,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="24" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="24" t="s">
         <v>515</v>
       </c>
@@ -4374,86 +4290,86 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="50" t="s">
         <v>520</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="51" t="s">
         <v>521</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="51" t="s">
         <v>522</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="51" t="s">
         <v>551</v>
       </c>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4513,7 +4429,7 @@
       <c r="C3" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="48" t="s">
         <v>327</v>
       </c>
       <c r="E3" s="30" t="s">
@@ -4530,13 +4446,13 @@
       <c r="A4" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="44">
         <v>0.3</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="49">
         <v>0.05</v>
       </c>
       <c r="E4" s="34" t="s">
@@ -4553,13 +4469,13 @@
       <c r="A5" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="48">
+      <c r="B5" s="45">
         <v>140</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="48" t="s">
         <v>563</v>
       </c>
       <c r="E5" s="30" t="s">
@@ -4576,7 +4492,7 @@
       <c r="A6" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="47" t="s">
         <v>454</v>
       </c>
       <c r="C6" s="30" t="s">
@@ -4599,13 +4515,13 @@
       <c r="A7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="47" t="s">
         <v>561</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="47" t="s">
         <v>560</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="48">
         <v>40</v>
       </c>
       <c r="E7" s="30" t="s">
@@ -4628,7 +4544,7 @@
       <c r="C8" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="48" t="s">
         <v>308</v>
       </c>
       <c r="E8" s="30" t="s">
@@ -4651,7 +4567,7 @@
       <c r="C9" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="48" t="s">
         <v>558</v>
       </c>
       <c r="E9" s="30" t="s">
@@ -4668,7 +4584,7 @@
       <c r="A10" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="43">
         <v>3800</v>
       </c>
       <c r="C10" s="30" t="s">
@@ -4691,7 +4607,7 @@
       <c r="A11" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="46" t="s">
         <v>295</v>
       </c>
       <c r="C11" s="36" t="s">
@@ -10655,6 +10571,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EE3B5FF1D6D93545B0A9BE76E04A5739" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b213452e5774ccb18cdbac914376359f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af" xmlns:ns3="d7940701-fd28-48c6-89b6-2769869457dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94bb0651eba29840b02d7d9879aff2b0" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
@@ -10849,27 +10785,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D4D638-0E0C-48CA-BE88-3BE2B56E957A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10886,29 +10827,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/disruptors_supplementary_data_tables_s1-s5.xlsx
+++ b/data/disruptors_supplementary_data_tables_s1-s5.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="168" documentId="8_{2185ED28-394C-4B15-AA86-7120D6AF9B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B291BDA3-B4DE-4C3D-B971-74A74A02A106}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2895" windowWidth="29040" windowHeight="15840" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" firstSheet="3" activeTab="6" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -2295,6 +2295,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2302,9 +2305,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3476,18 +3476,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="50" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
     </row>
     <row r="2" spans="1:10" s="7" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="25" t="s">
@@ -4290,86 +4290,86 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="51" t="s">
         <v>520</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="52" t="s">
         <v>521</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="52" t="s">
         <v>522</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="52" t="s">
         <v>551</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="53" t="s">
         <v>550</v>
       </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10571,26 +10571,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EE3B5FF1D6D93545B0A9BE76E04A5739" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b213452e5774ccb18cdbac914376359f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af" xmlns:ns3="d7940701-fd28-48c6-89b6-2769869457dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94bb0651eba29840b02d7d9879aff2b0" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
@@ -10785,32 +10765,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D4D638-0E0C-48CA-BE88-3BE2B56E957A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10827,4 +10802,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/disruptors_supplementary_data_tables_s1-s5.xlsx
+++ b/data/disruptors_supplementary_data_tables_s1-s5.xlsx
@@ -6543,11 +6543,11 @@
         <v>3300</v>
       </c>
       <c r="K2" s="7">
-        <f>IF(OR(F2="species", F2="genus"), (I2*10^4)/J2,"NA")</f>
+        <f t="shared" ref="K2:K33" si="0">IF(OR(F2="species", F2="genus"), (I2*10^4)/J2,"NA")</f>
         <v>6.0606060606060606</v>
       </c>
       <c r="L2" s="7">
-        <f>IF(H2="percent", I2/(J2/10^6), "NA")</f>
+        <f t="shared" ref="L2:L33" si="1">IF(H2="percent", I2/(J2/10^6), "NA")</f>
         <v>606.06060606060612</v>
       </c>
       <c r="M2" t="s">
@@ -6599,11 +6599,11 @@
         <v>3300</v>
       </c>
       <c r="K3" s="7">
-        <f>IF(OR(F3="species", F3="genus"), (I3*10^4)/J3,"NA")</f>
+        <f t="shared" si="0"/>
         <v>15.151515151515152</v>
       </c>
       <c r="L3" s="7">
-        <f>IF(H3="percent", I3/(J3/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>1515.1515151515152</v>
       </c>
       <c r="M3" t="s">
@@ -6655,11 +6655,11 @@
         <v>3300</v>
       </c>
       <c r="K4" s="7">
-        <f>IF(OR(F4="species", F4="genus"), (I4*10^4)/J4,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-84.848484848484844</v>
       </c>
       <c r="L4" s="7">
-        <f>IF(H4="percent", I4/(J4/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-8484.8484848484841</v>
       </c>
       <c r="M4" t="s">
@@ -6711,11 +6711,11 @@
         <v>3300</v>
       </c>
       <c r="K5" s="7">
-        <f>IF(OR(F5="species", F5="genus"), (I5*10^4)/J5,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-30.303030303030305</v>
       </c>
       <c r="L5" s="7">
-        <f>IF(H5="percent", I5/(J5/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-3030.3030303030305</v>
       </c>
       <c r="M5" t="s">
@@ -6767,11 +6767,11 @@
         <v>3300</v>
       </c>
       <c r="K6" s="7">
-        <f>IF(OR(F6="species", F6="genus"), (I6*10^4)/J6,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-15.151515151515152</v>
       </c>
       <c r="L6" s="7">
-        <f>IF(H6="percent", I6/(J6/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-1515.1515151515152</v>
       </c>
       <c r="M6" t="s">
@@ -6823,11 +6823,11 @@
         <v>300</v>
       </c>
       <c r="K7" s="7">
-        <f>IF(OR(F7="species", F7="genus"), (I7*10^4)/J7,"NA")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7" s="7">
-        <f>IF(H7="percent", I7/(J7/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7" t="s">
@@ -6879,11 +6879,11 @@
         <v>300</v>
       </c>
       <c r="K8" s="7">
-        <f>IF(OR(F8="species", F8="genus"), (I8*10^4)/J8,"NA")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L8" s="7">
-        <f>IF(H8="percent", I8/(J8/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M8" t="s">
@@ -6929,11 +6929,11 @@
         <v>300</v>
       </c>
       <c r="K9" s="7">
-        <f>IF(OR(F9="species", F9="genus"), (I9*10^4)/J9,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-1066.6666666666667</v>
       </c>
       <c r="L9" s="7">
-        <f>IF(H9="percent", I9/(J9/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-106666.66666666667</v>
       </c>
       <c r="O9" t="s">
@@ -6976,11 +6976,11 @@
         <v>300</v>
       </c>
       <c r="K10" s="7">
-        <f>IF(OR(F10="species", F10="genus"), (I10*10^4)/J10,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-900</v>
       </c>
       <c r="L10" s="7">
-        <f>IF(H10="percent", I10/(J10/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-90000.000000000015</v>
       </c>
       <c r="M10" t="s">
@@ -7026,11 +7026,11 @@
         <v>300</v>
       </c>
       <c r="K11" s="7">
-        <f>IF(OR(F11="species", F11="genus"), (I11*10^4)/J11,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-586.66666666666663</v>
       </c>
       <c r="L11" s="7">
-        <f>IF(H11="percent", I11/(J11/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-58666.666666666679</v>
       </c>
       <c r="M11" t="s">
@@ -7076,11 +7076,11 @@
         <v>300</v>
       </c>
       <c r="K12" s="7">
-        <f>IF(OR(F12="species", F12="genus"), (I12*10^4)/J12,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-466.66666666666669</v>
       </c>
       <c r="L12" s="7">
-        <f>IF(H12="percent", I12/(J12/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-46666.666666666672</v>
       </c>
       <c r="O12" t="s">
@@ -7123,11 +7123,11 @@
         <v>300</v>
       </c>
       <c r="K13" s="7">
-        <f>IF(OR(F13="species", F13="genus"), (I13*10^4)/J13,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-433.33333333333331</v>
       </c>
       <c r="L13" s="7">
-        <f>IF(H13="percent", I13/(J13/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-43333.333333333336</v>
       </c>
       <c r="M13" t="s">
@@ -7173,11 +7173,11 @@
         <v>300</v>
       </c>
       <c r="K14" s="7">
-        <f>IF(OR(F14="species", F14="genus"), (I14*10^4)/J14,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-260</v>
       </c>
       <c r="L14" s="7">
-        <f>IF(H14="percent", I14/(J14/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-26000</v>
       </c>
       <c r="M14" t="s">
@@ -7223,11 +7223,11 @@
         <v>300</v>
       </c>
       <c r="K15" s="7">
-        <f>IF(OR(F15="species", F15="genus"), (I15*10^4)/J15,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-126.66666666666667</v>
       </c>
       <c r="L15" s="7">
-        <f>IF(H15="percent", I15/(J15/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-12666.666666666668</v>
       </c>
       <c r="M15" t="s">
@@ -7273,11 +7273,11 @@
         <v>200</v>
       </c>
       <c r="K16" s="7" t="str">
-        <f>IF(OR(F16="species", F16="genus"), (I16*10^4)/J16,"NA")</f>
+        <f t="shared" si="0"/>
         <v>NA</v>
       </c>
       <c r="L16" s="7">
-        <f>IF(H16="percent", I16/(J16/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-415000</v>
       </c>
       <c r="M16" t="s">
@@ -7323,11 +7323,11 @@
         <v>200</v>
       </c>
       <c r="K17" s="7">
-        <f>IF(OR(F17="species", F17="genus"), (I17*10^4)/J17,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-2500</v>
       </c>
       <c r="L17" s="7">
-        <f>IF(H17="percent", I17/(J17/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-250000</v>
       </c>
       <c r="O17" t="s">
@@ -7370,11 +7370,11 @@
         <v>200</v>
       </c>
       <c r="K18" s="7" t="str">
-        <f>IF(OR(F18="species", F18="genus"), (I18*10^4)/J18,"NA")</f>
+        <f t="shared" si="0"/>
         <v>NA</v>
       </c>
       <c r="L18" s="7">
-        <f>IF(H18="percent", I18/(J18/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-150000</v>
       </c>
       <c r="M18" t="s">
@@ -7420,11 +7420,11 @@
         <v>200</v>
       </c>
       <c r="K19" s="7">
-        <f>IF(OR(F19="species", F19="genus"), (I19*10^4)/J19,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-80.500000000000014</v>
       </c>
       <c r="L19" s="7">
-        <f>IF(H19="percent", I19/(J19/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-8050</v>
       </c>
       <c r="M19" t="s">
@@ -7470,11 +7470,11 @@
         <v>200</v>
       </c>
       <c r="K20" s="7">
-        <f>IF(OR(F20="species", F20="genus"), (I20*10^4)/J20,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-77</v>
       </c>
       <c r="L20" s="7">
-        <f>IF(H20="percent", I20/(J20/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-7700</v>
       </c>
       <c r="M20" t="s">
@@ -7520,11 +7520,11 @@
         <v>200</v>
       </c>
       <c r="K21" s="7">
-        <f>IF(OR(F21="species", F21="genus"), (I21*10^4)/J21,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-44</v>
       </c>
       <c r="L21" s="7">
-        <f>IF(H21="percent", I21/(J21/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-4400</v>
       </c>
       <c r="M21" t="s">
@@ -7570,11 +7570,11 @@
         <v>200</v>
       </c>
       <c r="K22" s="7">
-        <f>IF(OR(F22="species", F22="genus"), (I22*10^4)/J22,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-29</v>
       </c>
       <c r="L22" s="7">
-        <f>IF(H22="percent", I22/(J22/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-2899.9999999999995</v>
       </c>
       <c r="M22" t="s">
@@ -7620,11 +7620,11 @@
         <v>200</v>
       </c>
       <c r="K23" s="7">
-        <f>IF(OR(F23="species", F23="genus"), (I23*10^4)/J23,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="L23" s="7">
-        <f>IF(H23="percent", I23/(J23/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-2500</v>
       </c>
       <c r="O23" t="s">
@@ -7667,11 +7667,11 @@
         <v>200</v>
       </c>
       <c r="K24" s="7">
-        <f>IF(OR(F24="species", F24="genus"), (I24*10^4)/J24,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-22.5</v>
       </c>
       <c r="L24" s="7">
-        <f>IF(H24="percent", I24/(J24/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-2250</v>
       </c>
       <c r="M24" t="s">
@@ -7714,11 +7714,11 @@
         <v>200</v>
       </c>
       <c r="K25" s="7">
-        <f>IF(OR(F25="species", F25="genus"), (I25*10^4)/J25,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-8.5000000000000018</v>
       </c>
       <c r="L25" s="7">
-        <f>IF(H25="percent", I25/(J25/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-850</v>
       </c>
       <c r="M25" t="s">
@@ -7761,11 +7761,11 @@
         <v>200</v>
       </c>
       <c r="K26" s="7">
-        <f>IF(OR(F26="species", F26="genus"), (I26*10^4)/J26,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
       <c r="L26" s="7">
-        <f>IF(H26="percent", I26/(J26/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-50</v>
       </c>
     </row>
@@ -7805,11 +7805,11 @@
         <v>200</v>
       </c>
       <c r="K27" s="7">
-        <f>IF(OR(F27="species", F27="genus"), (I27*10^4)/J27,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="L27" s="7">
-        <f>IF(H27="percent", I27/(J27/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-5000</v>
       </c>
       <c r="M27" t="s">
@@ -7852,11 +7852,11 @@
         <v>500000</v>
       </c>
       <c r="K28" s="7">
-        <f>IF(OR(F28="species", F28="genus"), (I28*10^4)/J28,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-0.01</v>
       </c>
       <c r="L28" s="7">
-        <f>IF(H28="percent", I28/(J28/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="M28" t="s">
@@ -7899,11 +7899,11 @@
         <v>500000</v>
       </c>
       <c r="K29" s="7">
-        <f>IF(OR(F29="species", F29="genus"), (I29*10^4)/J29,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-0.22</v>
       </c>
       <c r="L29" s="7">
-        <f>IF(H29="percent", I29/(J29/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-22</v>
       </c>
       <c r="M29" t="s">
@@ -7946,11 +7946,11 @@
         <v>500000</v>
       </c>
       <c r="K30" s="7">
-        <f>IF(OR(F30="species", F30="genus"), (I30*10^4)/J30,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-0.72</v>
       </c>
       <c r="L30" s="7">
-        <f>IF(H30="percent", I30/(J30/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-72</v>
       </c>
       <c r="M30" t="s">
@@ -7993,11 +7993,11 @@
         <v>500000</v>
       </c>
       <c r="K31" s="7">
-        <f>IF(OR(F31="species", F31="genus"), (I31*10^4)/J31,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-0.98</v>
       </c>
       <c r="L31" s="7">
-        <f>IF(H31="percent", I31/(J31/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-98</v>
       </c>
       <c r="M31" t="s">
@@ -8040,11 +8040,11 @@
         <v>500000</v>
       </c>
       <c r="K32" s="7">
-        <f>IF(OR(F32="species", F32="genus"), (I32*10^4)/J32,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-0.84</v>
       </c>
       <c r="L32" s="7">
-        <f>IF(H32="percent", I32/(J32/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-84</v>
       </c>
       <c r="M32" t="s">
@@ -8087,11 +8087,11 @@
         <v>100000</v>
       </c>
       <c r="K33" s="7">
-        <f>IF(OR(F33="species", F33="genus"), (I33*10^4)/J33,"NA")</f>
+        <f t="shared" si="0"/>
         <v>-7.7</v>
       </c>
       <c r="L33" s="7">
-        <f>IF(H33="percent", I33/(J33/10^6), "NA")</f>
+        <f t="shared" si="1"/>
         <v>-770</v>
       </c>
     </row>
@@ -8131,11 +8131,11 @@
         <v>100000</v>
       </c>
       <c r="K34" s="7">
-        <f>IF(OR(F34="species", F34="genus"), (I34*10^4)/J34,"NA")</f>
+        <f t="shared" ref="K34:K65" si="2">IF(OR(F34="species", F34="genus"), (I34*10^4)/J34,"NA")</f>
         <v>-1.6</v>
       </c>
       <c r="L34" s="7">
-        <f>IF(H34="percent", I34/(J34/10^6), "NA")</f>
+        <f t="shared" ref="L34:L65" si="3">IF(H34="percent", I34/(J34/10^6), "NA")</f>
         <v>-160</v>
       </c>
     </row>
@@ -8175,11 +8175,11 @@
         <v>100000</v>
       </c>
       <c r="K35" s="7">
-        <f>IF(OR(F35="species", F35="genus"), (I35*10^4)/J35,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-1.5</v>
       </c>
       <c r="L35" s="7">
-        <f>IF(H35="percent", I35/(J35/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-150</v>
       </c>
     </row>
@@ -8219,11 +8219,11 @@
         <v>150000</v>
       </c>
       <c r="K36" s="7">
-        <f>IF(OR(F36="species", F36="genus"), (I36*10^4)/J36,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-4.333333333333333</v>
       </c>
       <c r="L36" s="7">
-        <f>IF(H36="percent", I36/(J36/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-433.33333333333337</v>
       </c>
     </row>
@@ -8263,11 +8263,11 @@
         <v>150000</v>
       </c>
       <c r="K37" s="7">
-        <f>IF(OR(F37="species", F37="genus"), (I37*10^4)/J37,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-2.2000000000000002</v>
       </c>
       <c r="L37" s="7">
-        <f>IF(H37="percent", I37/(J37/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-220</v>
       </c>
     </row>
@@ -8307,11 +8307,11 @@
         <v>150000</v>
       </c>
       <c r="K38" s="7">
-        <f>IF(OR(F38="species", F38="genus"), (I38*10^4)/J38,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-1.3333333333333333</v>
       </c>
       <c r="L38" s="7">
-        <f>IF(H38="percent", I38/(J38/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-133.33333333333334</v>
       </c>
     </row>
@@ -8351,11 +8351,11 @@
         <v>150000</v>
       </c>
       <c r="K39" s="7">
-        <f>IF(OR(F39="species", F39="genus"), (I39*10^4)/J39,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-6.6666666666666666E-2</v>
       </c>
       <c r="L39" s="7">
-        <f>IF(H39="percent", I39/(J39/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-6.666666666666667</v>
       </c>
     </row>
@@ -8395,11 +8395,11 @@
         <v>30</v>
       </c>
       <c r="K40" s="7">
-        <f>IF(OR(F40="species", F40="genus"), (I40*10^4)/J40,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-13333.333333333334</v>
       </c>
       <c r="L40" s="7">
-        <f>IF(H40="percent", I40/(J40/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-1333333.3333333333</v>
       </c>
     </row>
@@ -8439,11 +8439,11 @@
         <v>30</v>
       </c>
       <c r="K41" s="7">
-        <f>IF(OR(F41="species", F41="genus"), (I41*10^4)/J41,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-13333.333333333334</v>
       </c>
       <c r="L41" s="7">
-        <f>IF(H41="percent", I41/(J41/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-1333333.3333333333</v>
       </c>
     </row>
@@ -8483,11 +8483,11 @@
         <v>30</v>
       </c>
       <c r="K42" s="7">
-        <f>IF(OR(F42="species", F42="genus"), (I42*10^4)/J42,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-13000</v>
       </c>
       <c r="L42" s="7">
-        <f>IF(H42="percent", I42/(J42/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-1300000</v>
       </c>
     </row>
@@ -8527,11 +8527,11 @@
         <v>30</v>
       </c>
       <c r="K43" s="7">
-        <f>IF(OR(F43="species", F43="genus"), (I43*10^4)/J43,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-25000</v>
       </c>
       <c r="L43" s="7">
-        <f>IF(H43="percent", I43/(J43/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-2500000</v>
       </c>
       <c r="M43" t="s">
@@ -8574,11 +8574,11 @@
         <v>500000</v>
       </c>
       <c r="K44" s="7">
-        <f>IF(OR(F44="species", F44="genus"), (I44*10^4)/J44,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.4</v>
       </c>
       <c r="L44" s="7">
-        <f>IF(H44="percent", I44/(J44/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-40</v>
       </c>
     </row>
@@ -8618,11 +8618,11 @@
         <v>500000</v>
       </c>
       <c r="K45" s="7">
-        <f>IF(OR(F45="species", F45="genus"), (I45*10^4)/J45,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.44</v>
       </c>
       <c r="L45" s="7">
-        <f>IF(H45="percent", I45/(J45/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-44</v>
       </c>
     </row>
@@ -8662,11 +8662,11 @@
         <v>75000000</v>
       </c>
       <c r="K46" s="7">
-        <f>IF(OR(F46="species", F46="genus"), (I46*10^4)/J46,"NA")</f>
+        <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
       <c r="L46" s="7">
-        <f>IF(H46="percent", I46/(J46/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="M46" t="s">
@@ -8709,11 +8709,11 @@
         <v>75000000</v>
       </c>
       <c r="K47" s="7" t="str">
-        <f>IF(OR(F47="species", F47="genus"), (I47*10^4)/J47,"NA")</f>
+        <f t="shared" si="2"/>
         <v>NA</v>
       </c>
       <c r="L47" s="7">
-        <f>IF(H47="percent", I47/(J47/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>2.1466666666666665</v>
       </c>
       <c r="M47" t="s">
@@ -8756,11 +8756,11 @@
         <v>1000000</v>
       </c>
       <c r="K48" s="7">
-        <f>IF(OR(F48="species", F48="genus"), (I48*10^4)/J48,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.2</v>
       </c>
       <c r="L48" s="7">
-        <f>IF(H48="percent", I48/(J48/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-20</v>
       </c>
     </row>
@@ -8800,11 +8800,11 @@
         <v>500000</v>
       </c>
       <c r="K49" s="7">
-        <f>IF(OR(F49="species", F49="genus"), (I49*10^4)/J49,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="L49" s="7">
-        <f>IF(H49="percent", I49/(J49/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-50</v>
       </c>
     </row>
@@ -8844,11 +8844,11 @@
         <v>500000</v>
       </c>
       <c r="K50" s="7">
-        <f>IF(OR(F50="species", F50="genus"), (I50*10^4)/J50,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.44</v>
       </c>
       <c r="L50" s="7">
-        <f>IF(H50="percent", I50/(J50/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-44</v>
       </c>
     </row>
@@ -8888,11 +8888,11 @@
         <v>500000</v>
       </c>
       <c r="K51" s="7">
-        <f>IF(OR(F51="species", F51="genus"), (I51*10^4)/J51,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.4</v>
       </c>
       <c r="L51" s="7">
-        <f>IF(H51="percent", I51/(J51/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-40</v>
       </c>
     </row>
@@ -8932,11 +8932,11 @@
         <v>500000</v>
       </c>
       <c r="K52" s="7">
-        <f>IF(OR(F52="species", F52="genus"), (I52*10^4)/J52,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.3</v>
       </c>
       <c r="L52" s="7">
-        <f>IF(H52="percent", I52/(J52/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-30</v>
       </c>
     </row>
@@ -8975,11 +8975,11 @@
         <v>500000</v>
       </c>
       <c r="K53" s="7">
-        <f>IF(OR(F53="species", F53="genus"), (I53*10^4)/J53,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.52</v>
       </c>
       <c r="L53" s="7">
-        <f>IF(H53="percent", I53/(J53/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-52</v>
       </c>
     </row>
@@ -9019,11 +9019,11 @@
         <v>85000</v>
       </c>
       <c r="K54" s="7">
-        <f>IF(OR(F54="species", F54="genus"), (I54*10^4)/J54,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-9.4117647058823533</v>
       </c>
       <c r="L54" s="7">
-        <f>IF(H54="percent", I54/(J54/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-941.17647058823525</v>
       </c>
     </row>
@@ -9063,11 +9063,11 @@
         <v>85000</v>
       </c>
       <c r="K55" s="7">
-        <f>IF(OR(F55="species", F55="genus"), (I55*10^4)/J55,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-8.5882352941176467</v>
       </c>
       <c r="L55" s="7">
-        <f>IF(H55="percent", I55/(J55/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-858.82352941176464</v>
       </c>
     </row>
@@ -9107,11 +9107,11 @@
         <v>85000</v>
       </c>
       <c r="K56" s="7">
-        <f>IF(OR(F56="species", F56="genus"), (I56*10^4)/J56,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-5.5294117647058822</v>
       </c>
       <c r="L56" s="7">
-        <f>IF(H56="percent", I56/(J56/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-552.94117647058818</v>
       </c>
     </row>
@@ -9151,11 +9151,11 @@
         <v>1090000</v>
       </c>
       <c r="K57" s="7">
-        <f>IF(OR(F57="species", F57="genus"), (I57*10^4)/J57,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.56880733944954132</v>
       </c>
       <c r="L57" s="7">
-        <f>IF(H57="percent", I57/(J57/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-56.880733944954123</v>
       </c>
       <c r="M57" t="s">
@@ -9198,11 +9198,11 @@
         <v>1090000</v>
       </c>
       <c r="K58" s="7">
-        <f>IF(OR(F58="species", F58="genus"), (I58*10^4)/J58,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.46788990825688076</v>
       </c>
       <c r="L58" s="7">
-        <f>IF(H58="percent", I58/(J58/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-46.788990825688067</v>
       </c>
       <c r="M58" t="s">
@@ -9245,11 +9245,11 @@
         <v>1090000</v>
       </c>
       <c r="K59" s="7">
-        <f>IF(OR(F59="species", F59="genus"), (I59*10^4)/J59,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.30275229357798167</v>
       </c>
       <c r="L59" s="7">
-        <f>IF(H59="percent", I59/(J59/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-30.275229357798164</v>
       </c>
       <c r="M59" t="s">
@@ -9292,11 +9292,11 @@
         <v>60000</v>
       </c>
       <c r="K60" s="7">
-        <f>IF(OR(F60="species", F60="genus"), (I60*10^4)/J60,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-15.833333333333334</v>
       </c>
       <c r="L60" s="7">
-        <f>IF(H60="percent", I60/(J60/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-1583.3333333333335</v>
       </c>
     </row>
@@ -9336,11 +9336,11 @@
         <v>60000</v>
       </c>
       <c r="K61" s="7">
-        <f>IF(OR(F61="species", F61="genus"), (I61*10^4)/J61,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-13.833333333333334</v>
       </c>
       <c r="L61" s="7">
-        <f>IF(H61="percent", I61/(J61/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-1383.3333333333335</v>
       </c>
     </row>
@@ -9380,11 +9380,11 @@
         <v>60000</v>
       </c>
       <c r="K62" s="7" t="str">
-        <f>IF(OR(F62="species", F62="genus"), (I62*10^4)/J62,"NA")</f>
+        <f t="shared" si="2"/>
         <v>NA</v>
       </c>
       <c r="L62" s="7">
-        <f>IF(H62="percent", I62/(J62/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-1166.6666666666667</v>
       </c>
     </row>
@@ -9424,11 +9424,11 @@
         <v>60000</v>
       </c>
       <c r="K63" s="7">
-        <f>IF(OR(F63="species", F63="genus"), (I63*10^4)/J63,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-10.333333333333334</v>
       </c>
       <c r="L63" s="7">
-        <f>IF(H63="percent", I63/(J63/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-1033.3333333333335</v>
       </c>
     </row>
@@ -9468,11 +9468,11 @@
         <v>60000</v>
       </c>
       <c r="K64" s="7">
-        <f>IF(OR(F64="species", F64="genus"), (I64*10^4)/J64,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-9.3333333333333339</v>
       </c>
       <c r="L64" s="7">
-        <f>IF(H64="percent", I64/(J64/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-933.33333333333337</v>
       </c>
     </row>
@@ -9512,11 +9512,11 @@
         <v>1500000</v>
       </c>
       <c r="K65" s="7">
-        <f>IF(OR(F65="species", F65="genus"), (I65*10^4)/J65,"NA")</f>
+        <f t="shared" si="2"/>
         <v>-0.32</v>
       </c>
       <c r="L65" s="7">
-        <f>IF(H65="percent", I65/(J65/10^6), "NA")</f>
+        <f t="shared" si="3"/>
         <v>-32</v>
       </c>
     </row>
@@ -9556,11 +9556,11 @@
         <v>1500000</v>
       </c>
       <c r="K66" s="7">
-        <f>IF(OR(F66="species", F66="genus"), (I66*10^4)/J66,"NA")</f>
+        <f t="shared" ref="K66:K97" si="4">IF(OR(F66="species", F66="genus"), (I66*10^4)/J66,"NA")</f>
         <v>-0.22666666666666666</v>
       </c>
       <c r="L66" s="7">
-        <f>IF(H66="percent", I66/(J66/10^6), "NA")</f>
+        <f t="shared" ref="L66:L97" si="5">IF(H66="percent", I66/(J66/10^6), "NA")</f>
         <v>-22.666666666666668</v>
       </c>
     </row>
@@ -9600,11 +9600,11 @@
         <v>1500000</v>
       </c>
       <c r="K67" s="7">
-        <f>IF(OR(F67="species", F67="genus"), (I67*10^4)/J67,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.16666666666666666</v>
       </c>
       <c r="L67" s="7">
-        <f>IF(H67="percent", I67/(J67/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-16.666666666666668</v>
       </c>
     </row>
@@ -9644,11 +9644,11 @@
         <v>4000000</v>
       </c>
       <c r="K68" s="7">
-        <f>IF(OR(F68="species", F68="genus"), (I68*10^4)/J68,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-9.7500000000000003E-2</v>
       </c>
       <c r="L68" s="7">
-        <f>IF(H68="percent", I68/(J68/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-9.75</v>
       </c>
     </row>
@@ -9688,11 +9688,11 @@
         <v>4000000</v>
       </c>
       <c r="K69" s="7">
-        <f>IF(OR(F69="species", F69="genus"), (I69*10^4)/J69,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-7.7499999999999999E-2</v>
       </c>
       <c r="L69" s="7">
-        <f>IF(H69="percent", I69/(J69/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-7.75</v>
       </c>
       <c r="Z69" s="8"/>
@@ -9733,11 +9733,11 @@
         <v>4000000</v>
       </c>
       <c r="K70" s="7">
-        <f>IF(OR(F70="species", F70="genus"), (I70*10^4)/J70,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-3.5000000000000003E-2</v>
       </c>
       <c r="L70" s="7">
-        <f>IF(H70="percent", I70/(J70/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-3.5</v>
       </c>
       <c r="Z70" s="8"/>
@@ -9778,11 +9778,11 @@
         <v>100000</v>
       </c>
       <c r="K71" s="7">
-        <f>IF(OR(F71="species", F71="genus"), (I71*10^4)/J71,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
       <c r="L71" s="7">
-        <f>IF(H71="percent", I71/(J71/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-500</v>
       </c>
       <c r="Z71" s="8"/>
@@ -9823,11 +9823,11 @@
         <v>100000</v>
       </c>
       <c r="K72" s="7">
-        <f>IF(OR(F72="species", F72="genus"), (I72*10^4)/J72,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-3.1</v>
       </c>
       <c r="L72" s="7">
-        <f>IF(H72="percent", I72/(J72/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-310</v>
       </c>
       <c r="Y72" s="8"/>
@@ -9869,11 +9869,11 @@
         <v>100000</v>
       </c>
       <c r="K73" s="7">
-        <f>IF(OR(F73="species", F73="genus"), (I73*10^4)/J73,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-4</v>
       </c>
       <c r="L73" s="7">
-        <f>IF(H73="percent", I73/(J73/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-400</v>
       </c>
       <c r="Z73" s="8"/>
@@ -9914,11 +9914,11 @@
         <v>100000</v>
       </c>
       <c r="K74" s="7">
-        <f>IF(OR(F74="species", F74="genus"), (I74*10^4)/J74,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-3.5</v>
       </c>
       <c r="L74" s="7">
-        <f>IF(H74="percent", I74/(J74/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-350</v>
       </c>
       <c r="Y74" s="8"/>
@@ -9960,11 +9960,11 @@
         <v>100000</v>
       </c>
       <c r="K75" s="7">
-        <f>IF(OR(F75="species", F75="genus"), (I75*10^4)/J75,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-1.8</v>
       </c>
       <c r="L75" s="7">
-        <f>IF(H75="percent", I75/(J75/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-180</v>
       </c>
     </row>
@@ -10004,11 +10004,11 @@
         <v>1500000</v>
       </c>
       <c r="K76" s="7">
-        <f>IF(OR(F76="species", F76="genus"), (I76*10^4)/J76,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.24</v>
       </c>
       <c r="L76" s="7">
-        <f>IF(H76="percent", I76/(J76/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-24</v>
       </c>
     </row>
@@ -10048,11 +10048,11 @@
         <v>1500000</v>
       </c>
       <c r="K77" s="7">
-        <f>IF(OR(F77="species", F77="genus"), (I77*10^4)/J77,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.19333333333333333</v>
       </c>
       <c r="L77" s="7">
-        <f>IF(H77="percent", I77/(J77/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-19.333333333333332</v>
       </c>
     </row>
@@ -10092,11 +10092,11 @@
         <v>100000</v>
       </c>
       <c r="K78" s="7">
-        <f>IF(OR(F78="species", F78="genus"), (I78*10^4)/J78,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-3.2</v>
       </c>
       <c r="L78" s="7">
-        <f>IF(H78="percent", I78/(J78/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-320</v>
       </c>
     </row>
@@ -10136,11 +10136,11 @@
         <v>500000</v>
       </c>
       <c r="K79" s="7">
-        <f>IF(OR(F79="species", F79="genus"), (I79*10^4)/J79,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.42</v>
       </c>
       <c r="L79" s="7">
-        <f>IF(H79="percent", I79/(J79/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-42</v>
       </c>
     </row>
@@ -10180,11 +10180,11 @@
         <v>500000</v>
       </c>
       <c r="K80" s="7">
-        <f>IF(OR(F80="species", F80="genus"), (I80*10^4)/J80,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.18</v>
       </c>
       <c r="L80" s="7">
-        <f>IF(H80="percent", I80/(J80/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-18</v>
       </c>
     </row>
@@ -10224,11 +10224,11 @@
         <v>1000000</v>
       </c>
       <c r="K81" s="7">
-        <f>IF(OR(F81="species", F81="genus"), (I81*10^4)/J81,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.25</v>
       </c>
       <c r="L81" s="7">
-        <f>IF(H81="percent", I81/(J81/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-25</v>
       </c>
     </row>
@@ -10268,11 +10268,11 @@
         <v>1000000</v>
       </c>
       <c r="K82" s="7">
-        <f>IF(OR(F82="species", F82="genus"), (I82*10^4)/J82,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.22</v>
       </c>
       <c r="L82" s="7">
-        <f>IF(H82="percent", I82/(J82/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-22</v>
       </c>
     </row>
@@ -10311,11 +10311,11 @@
         <v>500000</v>
       </c>
       <c r="K83" s="7">
-        <f>IF(OR(F83="species", F83="genus"), (I83*10^4)/J83,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-1.7</v>
       </c>
       <c r="L83" s="7">
-        <f>IF(H83="percent", I83/(J83/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-170</v>
       </c>
     </row>
@@ -10354,11 +10354,11 @@
         <v>500000</v>
       </c>
       <c r="K84" s="7">
-        <f>IF(OR(F84="species", F84="genus"), (I84*10^4)/J84,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.98</v>
       </c>
       <c r="L84" s="7">
-        <f>IF(H84="percent", I84/(J84/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-98</v>
       </c>
     </row>
@@ -10398,11 +10398,11 @@
         <v>500000</v>
       </c>
       <c r="K85" s="7">
-        <f>IF(OR(F85="species", F85="genus"), (I85*10^4)/J85,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-1.1399999999999999</v>
       </c>
       <c r="L85" s="7">
-        <f>IF(H85="percent", I85/(J85/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-114</v>
       </c>
     </row>
@@ -10442,11 +10442,11 @@
         <v>500000</v>
       </c>
       <c r="K86" s="7">
-        <f>IF(OR(F86="species", F86="genus"), (I86*10^4)/J86,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-1.04</v>
       </c>
       <c r="L86" s="7">
-        <f>IF(H86="percent", I86/(J86/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-104</v>
       </c>
     </row>
@@ -10486,11 +10486,11 @@
         <v>500000</v>
       </c>
       <c r="K87" s="7">
-        <f>IF(OR(F87="species", F87="genus"), (I87*10^4)/J87,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.92</v>
       </c>
       <c r="L87" s="7">
-        <f>IF(H87="percent", I87/(J87/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-92</v>
       </c>
     </row>
@@ -10530,11 +10530,11 @@
         <v>60000000</v>
       </c>
       <c r="K88" s="7" t="str">
-        <f>IF(OR(F88="species", F88="genus"), (I88*10^4)/J88,"NA")</f>
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
       <c r="L88" s="7">
-        <f>IF(H88="percent", I88/(J88/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>0.58333333333333337</v>
       </c>
       <c r="M88" t="s">
@@ -10577,11 +10577,11 @@
         <v>60000000</v>
       </c>
       <c r="K89" s="7" t="str">
-        <f>IF(OR(F89="species", F89="genus"), (I89*10^4)/J89,"NA")</f>
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
       <c r="L89" s="7">
-        <f>IF(H89="percent", I89/(J89/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="M89" t="s">
@@ -10624,11 +10624,11 @@
         <v>60000000</v>
       </c>
       <c r="K90" s="7" t="str">
-        <f>IF(OR(F90="species", F90="genus"), (I90*10^4)/J90,"NA")</f>
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
       <c r="L90" s="7">
-        <f>IF(H90="percent", I90/(J90/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>2.4500000000000002</v>
       </c>
       <c r="M90" t="s">
@@ -10671,11 +10671,11 @@
         <v>60000000</v>
       </c>
       <c r="K91" s="7" t="str">
-        <f>IF(OR(F91="species", F91="genus"), (I91*10^4)/J91,"NA")</f>
+        <f t="shared" si="4"/>
         <v>NA</v>
       </c>
       <c r="L91" s="7">
-        <f>IF(H91="percent", I91/(J91/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="M91" t="s">
@@ -10718,11 +10718,11 @@
         <v>60000000</v>
       </c>
       <c r="K92" s="7">
-        <f>IF(OR(F92="species", F92="genus"), (I92*10^4)/J92,"NA")</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="L92" s="7">
-        <f>IF(H92="percent", I92/(J92/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>200</v>
       </c>
       <c r="M92" t="s">
@@ -10765,11 +10765,11 @@
         <v>60000000</v>
       </c>
       <c r="K93" s="7">
-        <f>IF(OR(F93="species", F93="genus"), (I93*10^4)/J93,"NA")</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="L93" s="7">
-        <f>IF(H93="percent", I93/(J93/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="M93" t="s">
@@ -10811,11 +10811,11 @@
         <v>30000000</v>
       </c>
       <c r="K94" s="7">
-        <f>IF(OR(F94="species", F94="genus"), (I94*10^4)/J94,"NA")</f>
+        <f t="shared" si="4"/>
         <v>0.26666666666666666</v>
       </c>
       <c r="L94" s="7">
-        <f>IF(H94="percent", I94/(J94/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>26.666666666666668</v>
       </c>
       <c r="M94" t="s">
@@ -10858,11 +10858,11 @@
         <v>2600000</v>
       </c>
       <c r="K95" s="7">
-        <f>IF(OR(F95="species", F95="genus"), (I95*10^4)/J95,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.25</v>
       </c>
       <c r="L95" s="7">
-        <f>IF(H95="percent", I95/(J95/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-25</v>
       </c>
     </row>
@@ -10902,11 +10902,11 @@
         <v>2600000</v>
       </c>
       <c r="K96" s="7">
-        <f>IF(OR(F96="species", F96="genus"), (I96*10^4)/J96,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.23076923076923078</v>
       </c>
       <c r="L96" s="7">
-        <f>IF(H96="percent", I96/(J96/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-23.076923076923077</v>
       </c>
       <c r="M96" t="s">
@@ -10949,11 +10949,11 @@
         <v>2600000</v>
       </c>
       <c r="K97" s="7">
-        <f>IF(OR(F97="species", F97="genus"), (I97*10^4)/J97,"NA")</f>
+        <f t="shared" si="4"/>
         <v>-0.22692307692307692</v>
       </c>
       <c r="L97" s="7">
-        <f>IF(H97="percent", I97/(J97/10^6), "NA")</f>
+        <f t="shared" si="5"/>
         <v>-22.69230769230769</v>
       </c>
     </row>
@@ -10993,11 +10993,11 @@
         <v>2600000</v>
       </c>
       <c r="K98" s="7">
-        <f>IF(OR(F98="species", F98="genus"), (I98*10^4)/J98,"NA")</f>
+        <f t="shared" ref="K98:K129" si="6">IF(OR(F98="species", F98="genus"), (I98*10^4)/J98,"NA")</f>
         <v>-0.22307692307692309</v>
       </c>
       <c r="L98" s="7">
-        <f>IF(H98="percent", I98/(J98/10^6), "NA")</f>
+        <f t="shared" ref="L98:L107" si="7">IF(H98="percent", I98/(J98/10^6), "NA")</f>
         <v>-22.307692307692307</v>
       </c>
     </row>
@@ -11037,11 +11037,11 @@
         <v>500000</v>
       </c>
       <c r="K99" s="7">
-        <f>IF(OR(F99="species", F99="genus"), (I99*10^4)/J99,"NA")</f>
+        <f t="shared" si="6"/>
         <v>-1</v>
       </c>
       <c r="L99" s="7">
-        <f>IF(H99="percent", I99/(J99/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>-100</v>
       </c>
       <c r="M99" t="s">
@@ -11084,11 +11084,11 @@
         <v>1000000</v>
       </c>
       <c r="K100" s="7">
-        <f>IF(OR(F100="species", F100="genus"), (I100*10^4)/J100,"NA")</f>
+        <f t="shared" si="6"/>
         <v>-0.5</v>
       </c>
       <c r="L100" s="7">
-        <f>IF(H100="percent", I100/(J100/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>-50</v>
       </c>
       <c r="M100" t="s">
@@ -11131,11 +11131,11 @@
         <v>1000000</v>
       </c>
       <c r="K101" s="7">
-        <f>IF(OR(F101="species", F101="genus"), (I101*10^4)/J101,"NA")</f>
+        <f t="shared" si="6"/>
         <v>-0.49</v>
       </c>
       <c r="L101" s="7">
-        <f>IF(H101="percent", I101/(J101/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>-49</v>
       </c>
     </row>
@@ -11175,11 +11175,11 @@
         <v>40000000</v>
       </c>
       <c r="K102" s="7" t="str">
-        <f>IF(OR(F102="species", F102="genus"), (I102*10^4)/J102,"NA")</f>
+        <f t="shared" si="6"/>
         <v>NA</v>
       </c>
       <c r="L102" s="7">
-        <f>IF(H102="percent", I102/(J102/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>6.0750000000000002</v>
       </c>
       <c r="M102" t="s">
@@ -11222,11 +11222,11 @@
         <v>40000000</v>
       </c>
       <c r="K103" s="7">
-        <f>IF(OR(F103="species", F103="genus"), (I103*10^4)/J103,"NA")</f>
+        <f t="shared" si="6"/>
         <v>0.23649999999999999</v>
       </c>
       <c r="L103" s="7">
-        <f>IF(H103="percent", I103/(J103/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>23.65</v>
       </c>
       <c r="M103" t="s">
@@ -11269,11 +11269,11 @@
         <v>40000000</v>
       </c>
       <c r="K104" s="7">
-        <f>IF(OR(F104="species", F104="genus"), (I104*10^4)/J104,"NA")</f>
+        <f t="shared" si="6"/>
         <v>0.23749999999999999</v>
       </c>
       <c r="L104" s="7">
-        <f>IF(H104="percent", I104/(J104/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>23.75</v>
       </c>
       <c r="M104" t="s">
@@ -11316,11 +11316,11 @@
         <v>100000000</v>
       </c>
       <c r="K105" s="7" t="str">
-        <f>IF(OR(F105="species", F105="genus"), (I105*10^4)/J105,"NA")</f>
+        <f t="shared" si="6"/>
         <v>NA</v>
       </c>
       <c r="L105" s="7">
-        <f>IF(H105="percent", I105/(J105/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="M105" t="s">
@@ -11363,11 +11363,11 @@
         <v>500000000</v>
       </c>
       <c r="K106" s="7" t="str">
-        <f>IF(OR(F106="species", F106="genus"), (I106*10^4)/J106,"NA")</f>
+        <f t="shared" si="6"/>
         <v>NA</v>
       </c>
       <c r="L106" s="7">
-        <f>IF(H106="percent", I106/(J106/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>0.91600000000000004</v>
       </c>
       <c r="M106" t="s">
@@ -11410,11 +11410,11 @@
         <v>500000000</v>
       </c>
       <c r="K107" s="7" t="str">
-        <f>IF(OR(F107="species", F107="genus"), (I107*10^4)/J107,"NA")</f>
+        <f t="shared" si="6"/>
         <v>NA</v>
       </c>
       <c r="L107" s="7">
-        <f>IF(H107="percent", I107/(J107/10^6), "NA")</f>
+        <f t="shared" si="7"/>
         <v>376</v>
       </c>
       <c r="M107" t="s">
@@ -11468,14 +11468,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11674,27 +11672,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11719,9 +11710,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/disruptors_supplementary_data_tables_s1-s5.xlsx
+++ b/data/disruptors_supplementary_data_tables_s1-s5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester.sharepoint.com/sites/Team_caad90aa-a47f-449b-818d-a866be7fd445/Shared Documents/General/disruptors/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="14_{07CC9888-B577-4F29-BB79-BFAB3ACC8C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A116BA5-859F-4B0C-ACA3-FFDFE6D6AB2B}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="14_{07CC9888-B577-4F29-BB79-BFAB3ACC8C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFA6BB95-C7CD-444A-B6E1-FDAE491F3022}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2895" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
+    <workbookView xWindow="-28920" yWindow="-3870" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="710">
   <si>
     <r>
       <t>Supplementary Data tables for Wong Hearing et al.: "</t>
@@ -2175,9 +2175,6 @@
     <t>global plants</t>
   </si>
   <si>
-    <t>largely following data in Barnosky 2008</t>
-  </si>
-  <si>
     <t>global animals</t>
   </si>
   <si>
@@ -2305,6 +2302,9 @@
   </si>
   <si>
     <t>estimate of lost biomass of marine mammals and fish weighing more than 10 g over 20th century due to fishing and whaling (~2 Gt loss)</t>
+  </si>
+  <si>
+    <t>Quaternary megafaunal extinction duration and rate calculated over 50 ka to 3 ka following Bar-On et al (2018); data largely following data in Barnosky 2008</t>
   </si>
 </sst>
 </file>
@@ -2497,10 +2497,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3228,10 +3224,10 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B44" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
@@ -7298,8 +7294,7 @@
         <v>-83</v>
       </c>
       <c r="J16" s="2">
-        <f>_xlfn.XLOOKUP(A16, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>200</v>
+        <v>47000</v>
       </c>
       <c r="K16" s="7" t="str">
         <f t="shared" si="0"/>
@@ -7307,13 +7302,13 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" si="1"/>
-        <v>-415000</v>
+        <v>-1765.9574468085107</v>
       </c>
       <c r="M16" t="s">
+        <v>709</v>
+      </c>
+      <c r="O16" t="s">
         <v>666</v>
-      </c>
-      <c r="O16" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
@@ -7339,7 +7334,7 @@
         <v>637</v>
       </c>
       <c r="G17" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H17" t="s">
         <v>634</v>
@@ -7348,19 +7343,21 @@
         <v>-50</v>
       </c>
       <c r="J17" s="2">
-        <f>_xlfn.XLOOKUP(A17, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>200</v>
+        <v>47000</v>
       </c>
       <c r="K17" s="7">
         <f t="shared" si="0"/>
-        <v>-2500</v>
+        <v>-10.638297872340425</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="1"/>
-        <v>-250000</v>
+        <v>-1063.8297872340424</v>
+      </c>
+      <c r="M17" t="s">
+        <v>709</v>
       </c>
       <c r="O17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
@@ -7407,10 +7404,10 @@
         <v>-150000</v>
       </c>
       <c r="M18" t="s">
+        <v>669</v>
+      </c>
+      <c r="O18" t="s">
         <v>670</v>
-      </c>
-      <c r="O18" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
@@ -7430,13 +7427,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F19" t="s">
         <v>646</v>
       </c>
       <c r="G19" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H19" t="s">
         <v>634</v>
@@ -7457,10 +7454,10 @@
         <v>-300000</v>
       </c>
       <c r="M19" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="O19" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -7507,10 +7504,10 @@
         <v>-8050</v>
       </c>
       <c r="M20" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="O20" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -7536,7 +7533,7 @@
         <v>632</v>
       </c>
       <c r="G21" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H21" t="s">
         <v>634</v>
@@ -7557,10 +7554,10 @@
         <v>-7700</v>
       </c>
       <c r="M21" t="s">
+        <v>671</v>
+      </c>
+      <c r="O21" t="s">
         <v>672</v>
-      </c>
-      <c r="O21" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -7607,10 +7604,10 @@
         <v>-4400</v>
       </c>
       <c r="M22" t="s">
+        <v>673</v>
+      </c>
+      <c r="O22" t="s">
         <v>674</v>
-      </c>
-      <c r="O22" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -7636,7 +7633,7 @@
         <v>632</v>
       </c>
       <c r="G23" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H23" t="s">
         <v>634</v>
@@ -7657,10 +7654,10 @@
         <v>-2899.9999999999995</v>
       </c>
       <c r="M23" t="s">
+        <v>675</v>
+      </c>
+      <c r="O23" t="s">
         <v>676</v>
-      </c>
-      <c r="O23" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
@@ -7707,7 +7704,7 @@
         <v>-2500</v>
       </c>
       <c r="O24" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -7754,7 +7751,7 @@
         <v>-2250</v>
       </c>
       <c r="M25" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
@@ -7801,7 +7798,7 @@
         <v>-850</v>
       </c>
       <c r="M26" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
@@ -7871,7 +7868,7 @@
         <v>632</v>
       </c>
       <c r="G28" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H28" t="s">
         <v>634</v>
@@ -7892,7 +7889,7 @@
         <v>-5000</v>
       </c>
       <c r="M28" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
@@ -7939,7 +7936,7 @@
         <v>-1</v>
       </c>
       <c r="M29" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
@@ -7986,7 +7983,7 @@
         <v>-22</v>
       </c>
       <c r="M30" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
@@ -8012,7 +8009,7 @@
         <v>632</v>
       </c>
       <c r="G31" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H31" t="s">
         <v>634</v>
@@ -8033,7 +8030,7 @@
         <v>-72</v>
       </c>
       <c r="M31" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -8059,7 +8056,7 @@
         <v>637</v>
       </c>
       <c r="G32" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H32" t="s">
         <v>634</v>
@@ -8080,7 +8077,7 @@
         <v>-98</v>
       </c>
       <c r="M32" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -8106,7 +8103,7 @@
         <v>637</v>
       </c>
       <c r="G33" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H33" t="s">
         <v>634</v>
@@ -8127,7 +8124,7 @@
         <v>-84</v>
       </c>
       <c r="M33" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -8614,7 +8611,7 @@
         <v>-2500000</v>
       </c>
       <c r="M44" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
@@ -8749,7 +8746,7 @@
         <v>2</v>
       </c>
       <c r="M47" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
@@ -8796,7 +8793,7 @@
         <v>2.1466666666666665</v>
       </c>
       <c r="M48" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
@@ -9238,7 +9235,7 @@
         <v>-56.880733944954123</v>
       </c>
       <c r="M58" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
@@ -9285,7 +9282,7 @@
         <v>-46.788990825688067</v>
       </c>
       <c r="M59" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
@@ -9332,7 +9329,7 @@
         <v>-30.275229357798164</v>
       </c>
       <c r="M60" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
@@ -10617,7 +10614,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="M89" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.35">
@@ -10664,7 +10661,7 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="M90" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.35">
@@ -10711,7 +10708,7 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="M91" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.35">
@@ -10758,7 +10755,7 @@
         <v>15</v>
       </c>
       <c r="M92" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.35">
@@ -10805,7 +10802,7 @@
         <v>200</v>
       </c>
       <c r="M93" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.35">
@@ -10852,7 +10849,7 @@
         <v>300</v>
       </c>
       <c r="M94" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.35">
@@ -10898,7 +10895,7 @@
         <v>26.666666666666668</v>
       </c>
       <c r="M95" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.35">
@@ -10989,7 +10986,7 @@
         <v>-23.076923076923077</v>
       </c>
       <c r="M97" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
@@ -11124,7 +11121,7 @@
         <v>-100</v>
       </c>
       <c r="M100" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
@@ -11171,7 +11168,7 @@
         <v>-50</v>
       </c>
       <c r="M101" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.35">
@@ -11262,7 +11259,7 @@
         <v>6.0750000000000002</v>
       </c>
       <c r="M103" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
@@ -11288,7 +11285,7 @@
         <v>637</v>
       </c>
       <c r="G104" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H104" t="s">
         <v>634</v>
@@ -11309,7 +11306,7 @@
         <v>23.65</v>
       </c>
       <c r="M104" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
@@ -11335,7 +11332,7 @@
         <v>632</v>
       </c>
       <c r="G105" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H105" t="s">
         <v>634</v>
@@ -11356,7 +11353,7 @@
         <v>23.75</v>
       </c>
       <c r="M105" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
@@ -11403,7 +11400,7 @@
         <v>6</v>
       </c>
       <c r="M106" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
@@ -11450,7 +11447,7 @@
         <v>0.91600000000000004</v>
       </c>
       <c r="M107" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
@@ -11497,7 +11494,7 @@
         <v>376</v>
       </c>
       <c r="M108" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -11556,6 +11553,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EE3B5FF1D6D93545B0A9BE76E04A5739" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b213452e5774ccb18cdbac914376359f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af" xmlns:ns3="d7940701-fd28-48c6-89b6-2769869457dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94bb0651eba29840b02d7d9879aff2b0" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
@@ -11750,17 +11758,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
   <ds:schemaRefs>
@@ -11770,6 +11767,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
+    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D4D638-0E0C-48CA-BE88-3BE2B56E957A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11786,15 +11794,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F179CFA0-01D1-49C4-829E-9CD6990EDE07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
-    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/disruptors_supplementary_data_tables_s1-s5.xlsx
+++ b/data/disruptors_supplementary_data_tables_s1-s5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester.sharepoint.com/sites/Team_caad90aa-a47f-449b-818d-a866be7fd445/Shared Documents/General/disruptors/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="14_{07CC9888-B577-4F29-BB79-BFAB3ACC8C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFA6BB95-C7CD-444A-B6E1-FDAE491F3022}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="14_{07CC9888-B577-4F29-BB79-BFAB3ACC8C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{941278D0-68ED-46E6-B898-CB2DD77F5CD2}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3870" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" firstSheet="4" activeTab="6" xr2:uid="{3126E51C-B0E9-457E-98E2-44FE6544FF4A}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">table_s1_transient!$A$1:$J$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">table_s2_persistent!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">table_s3_events!$A$1:$K$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">table_s5_biosphere_changes!$A$1:$M$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">table_s5_biosphere_changes!$A$1:$M$105</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="715">
   <si>
     <r>
       <t>Supplementary Data tables for Wong Hearing et al.: "</t>
@@ -851,9 +851,6 @@
     <t>Recent past and contemporary (Quaternary)</t>
   </si>
   <si>
-    <t>1000s of years for the anthropogenic extinction episode; maximum impact in last ~200 years</t>
-  </si>
-  <si>
     <t>Human activity</t>
   </si>
   <si>
@@ -867,9 +864,6 @@
   </si>
   <si>
     <t>Uncertain; currently at least –1‰ in the surface ocean and –2‰ in the atmosphere (Kwon et al. 2022)</t>
-  </si>
-  <si>
-    <t>Potential mass extinction and significant decline in biomass; instability and loss of ecosystems and functional diversity; human appropriation of primary productivity and concentration of animal and plant biomass in a few species deemed useful for human (70% of bird biomass in chickens; 98% of mammal biomass in humans and farmed animals)</t>
   </si>
   <si>
     <t>Eocene-Oligocene transition (Palaeogene) [c]</t>
@@ -1860,9 +1854,6 @@
     <t>PTME</t>
   </si>
   <si>
-    <t>carbon cycle destabilisation and marine extinction occurred over ~60 ± 48 kyr (Burgess et al 2014; Hua et al 2023) though it may have been as short as ~31 ± 31 kyr (Shen et al 2018); terrestrial extinction phase may have lasted as long as ~1 Myr (Hua et al 2023)</t>
-  </si>
-  <si>
     <t>End-Guadalupian (Capitanian; Permian)</t>
   </si>
   <si>
@@ -2217,9 +2208,6 @@
     <t>extinction rate of all included plant genera with values from extinct genera as proportion of IUCN assessed genera</t>
   </si>
   <si>
-    <t>extinction rate from Ceballos &amp; Ehrlich 2023 calculated in Hatfield et al 2025 table 1</t>
-  </si>
-  <si>
     <t>extinction rate minimum of marine animals following Bambach 2006 cited in Hatfield et al 2025 table 1</t>
   </si>
   <si>
@@ -2301,10 +2289,37 @@
     <t>large fish and marine mammals</t>
   </si>
   <si>
-    <t>estimate of lost biomass of marine mammals and fish weighing more than 10 g over 20th century due to fishing and whaling (~2 Gt loss)</t>
-  </si>
-  <si>
-    <t>Quaternary megafaunal extinction duration and rate calculated over 50 ka to 3 ka following Bar-On et al (2018); data largely following data in Barnosky 2008</t>
+    <t>1000s of years for the total anthropogenic extinction episode (e.g. ~50 ka to 3 ka for Quaternary megafaunal extinction; Bar-On et al. 2018); maximum impact in last ~200 years</t>
+  </si>
+  <si>
+    <t>Potential mass extinction and significant decline in biomass on land and in the oceans; instability and loss of ecosystems and functional diversity; human appropriation of primary productivity and concentration of animal and plant biomass in a few species deemed useful for human (70% of bird biomass in chickens; 98% of mammal biomass in humans and farmed animals)</t>
+  </si>
+  <si>
+    <t>extinction rate from Ceballos &amp; Ehrlich 2023 calculated in Hatfield et al 2025 table 1; these data are also used for the Planetary Health Check 2025</t>
+  </si>
+  <si>
+    <t>Greenspoon et al 2025</t>
+  </si>
+  <si>
+    <t>terrestrial mammals</t>
+  </si>
+  <si>
+    <t>Greenspoon L, Ramot N, Moran U, Roll U, Phillips R, Noor E, Milo R. 2025 The global biomass of mammals since 1850. Nat Commun 16, 8338. (doi:10.1038/s41467-025-63888-z)</t>
+  </si>
+  <si>
+    <t>estimate of lost biomass of marine mammals and fish weighing more than 10 g over 20th century due to fishing and whaling (~2 Gt loss); see also Greenspoon et al 2025 who estimate marine mammal loss at ~70% since 1850</t>
+  </si>
+  <si>
+    <t>loss of wild terrestrial mammal biomass since 1850</t>
+  </si>
+  <si>
+    <t>carbon cycle destabilisation and marine extinction occurred over ~60 ± 48 kyr (Burgess et al 2014; Hua et al 2023) though it may have been as short as ~31 ± 31 kyr (Shen et al 2018); astronomical calibration in South China suggests an extinction episode duration of ~40 kyr (Li et al 2016); terrestrial extinction phase may have lasted as long as ~1 Myr (Hua et al 2023)</t>
+  </si>
+  <si>
+    <t>Li M, Ogg J, Zhang Y, Huang C, Hinnov L, Chen Z-Q, Zou Z. 2016 Astronomical tuning of the end-Permian extinction and the Early Triassic Epoch of South China and Germany. Earth and Planetary Science Letters 441, 10–25. (doi:10.1016/j.epsl.2016.02.017)</t>
+  </si>
+  <si>
+    <t>Li et al 2016</t>
   </si>
 </sst>
 </file>
@@ -2871,7 +2886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7423E71A-C3BA-4E9A-8679-88DDD26ECF27}">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
@@ -3184,609 +3199,625 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>707</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>709</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>706</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>705</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>702</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>701</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>714</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>713</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B68" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B71" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B87" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B88" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B89" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B90" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B92" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B93" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B94" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B95" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B96" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B97" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B98" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B99" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B100" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B101" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B102" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B103" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B104" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B105" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B106" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B107" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B108" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B109" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B110" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B111" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B112" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B113" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
+        <v>234</v>
+      </c>
+      <c r="B114" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>236</v>
+      </c>
+      <c r="B115" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>238</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B116" t="s">
         <v>239</v>
       </c>
     </row>
@@ -3796,8 +3827,8 @@
       <sortCondition ref="A1:A3"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B114">
-    <sortCondition ref="A3:A114"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B116">
+    <sortCondition ref="A3:A116"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3853,7 +3884,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="9" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>250</v>
       </c>
@@ -3861,769 +3892,769 @@
         <v>0.3</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>257</v>
+        <v>705</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B3" s="10">
         <v>34</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="H3" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="I3" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>263</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B4" s="10">
         <v>56</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="H4" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>271</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="9" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B5" s="10">
         <v>66</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="H5" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>279</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B6" s="10">
         <v>94</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I6" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="E7" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>290</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="E8" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I8" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="J8" s="9" t="s">
         <v>296</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B9" s="10">
         <v>201</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G9" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I9" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="J9" s="9" t="s">
         <v>303</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B11" s="10">
         <v>248</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I11" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="J11" s="9" t="s">
         <v>317</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B12" s="10">
         <v>252</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="G12" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="I12" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H12" s="9" t="s">
+      <c r="J12" s="9" t="s">
         <v>324</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="E13" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="I13" s="24" t="s">
         <v>332</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="J13" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>334</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="9" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B14" s="10">
         <v>325</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="G14" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="J14" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B15" s="10">
         <v>360</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="G15" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I15" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>346</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B16" s="9">
         <v>371</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="G16" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I16" s="24" t="s">
         <v>351</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="J16" s="9" t="s">
         <v>352</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B17" s="10">
         <v>381</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="G17" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I17" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="J17" s="9" t="s">
         <v>358</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B18" s="10">
         <v>386</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E18" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H18" s="9" t="s">
+      <c r="J18" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B19" s="10">
         <v>423.5</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="G19" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>369</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B20" s="10">
         <v>428</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>373</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B21" s="10">
         <v>433</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B22" s="10">
         <v>445</v>
       </c>
       <c r="C22" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="G22" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I22" s="24" t="s">
         <v>382</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="J22" s="9" t="s">
         <v>383</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>384</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B23" s="10">
         <v>495</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="G23" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I23" s="24" t="s">
         <v>388</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="J23" s="9" t="s">
         <v>389</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="9" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="D24" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="G24" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="I24" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="J24" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="I25" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="J25" s="11" t="s">
         <v>400</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="I25" s="25" t="s">
-        <v>401</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="28" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -4637,7 +4668,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
@@ -4651,7 +4682,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B28" s="29"/>
       <c r="C28" s="29"/>
@@ -4665,7 +4696,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="29" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -4679,7 +4710,7 @@
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="27" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -4725,316 +4756,316 @@
   <sheetData>
     <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>408</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>409</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>410</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>242</v>
       </c>
       <c r="E1" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="G1" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>412</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="13" customFormat="1" ht="189.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="D2" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="F2" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>420</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="D3" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>429</v>
-      </c>
       <c r="H3" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" ht="129.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="D4" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>435</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" ht="89.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="D5" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>444</v>
-      </c>
       <c r="H5" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="D6" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="E6" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>449</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>451</v>
-      </c>
       <c r="H6" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" ht="118" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="D7" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="E7" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>458</v>
-      </c>
       <c r="H7" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>459</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="D8" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="E8" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="F8" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>464</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="13" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="E9" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>472</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>473</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="13" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="G10" s="13" t="s">
         <v>479</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>480</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="D11" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="E11" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="G11" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>489</v>
-      </c>
       <c r="H11" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>490</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="D12" s="14" t="s">
         <v>491</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="E12" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="F12" s="14" t="s">
         <v>493</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="G12" s="14" t="s">
         <v>494</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>496</v>
-      </c>
       <c r="H12" s="14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
@@ -5065,51 +5096,51 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E2" t="s">
         <v>508</v>
       </c>
-      <c r="B2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E2" t="s">
-        <v>510</v>
-      </c>
       <c r="F2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G2" s="5">
         <v>-1.1000000000000001E-3</v>
@@ -5124,21 +5155,21 @@
         <v>3300</v>
       </c>
       <c r="K2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" t="s">
         <v>512</v>
       </c>
-      <c r="B3" t="s">
-        <v>513</v>
-      </c>
-      <c r="E3" t="s">
-        <v>514</v>
-      </c>
       <c r="F3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G3" s="5">
         <v>-1.1000000000000001E-3</v>
@@ -5153,21 +5184,21 @@
         <v>3300</v>
       </c>
       <c r="K3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G4" s="5">
         <v>-1E-4</v>
@@ -5182,21 +5213,21 @@
         <v>300</v>
       </c>
       <c r="K4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G5" s="5">
         <v>-1E-4</v>
@@ -5211,21 +5242,21 @@
         <v>300</v>
       </c>
       <c r="K5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -5240,21 +5271,21 @@
         <v>200</v>
       </c>
       <c r="K6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>521</v>
+      </c>
+      <c r="B7" t="s">
+        <v>522</v>
+      </c>
+      <c r="E7" t="s">
         <v>523</v>
       </c>
-      <c r="B7" t="s">
-        <v>524</v>
-      </c>
-      <c r="E7" t="s">
-        <v>525</v>
-      </c>
       <c r="F7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G7" s="5">
         <v>2.6</v>
@@ -5269,21 +5300,21 @@
         <v>500000</v>
       </c>
       <c r="K7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B8" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G8" s="5">
         <v>34</v>
@@ -5298,21 +5329,21 @@
         <v>100000</v>
       </c>
       <c r="K8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B9" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E9" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G9" s="5">
         <v>56</v>
@@ -5327,27 +5358,27 @@
         <v>150000</v>
       </c>
       <c r="K9" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B10" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G10" s="5">
         <v>66</v>
@@ -5362,21 +5393,21 @@
         <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B11" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G11" s="5">
         <v>94</v>
@@ -5391,21 +5422,21 @@
         <v>500000</v>
       </c>
       <c r="K11" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B12" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G12" s="5">
         <v>120</v>
@@ -5420,21 +5451,21 @@
         <v>500000</v>
       </c>
       <c r="K12" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B13" t="s">
+        <v>540</v>
+      </c>
+      <c r="E13" t="s">
+        <v>541</v>
+      </c>
+      <c r="F13" t="s">
         <v>542</v>
-      </c>
-      <c r="E13" t="s">
-        <v>543</v>
-      </c>
-      <c r="F13" t="s">
-        <v>544</v>
       </c>
       <c r="G13" s="5">
         <v>140</v>
@@ -5449,21 +5480,21 @@
         <v>75000000</v>
       </c>
       <c r="K13" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B14" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E14" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G14" s="5">
         <v>143.1</v>
@@ -5478,21 +5509,21 @@
         <v>1000000</v>
       </c>
       <c r="K14" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B15" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E15" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G15" s="5">
         <v>183</v>
@@ -5507,24 +5538,24 @@
         <v>500000</v>
       </c>
       <c r="K15" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C16" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E16" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G16" s="5">
         <v>201</v>
@@ -5539,21 +5570,21 @@
         <v>85000</v>
       </c>
       <c r="K16" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B17" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E17" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F17" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G17" s="5">
         <v>234</v>
@@ -5568,21 +5599,21 @@
         <v>1090000</v>
       </c>
       <c r="K17" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B18" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E18" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G18" s="5">
         <v>248</v>
@@ -5597,27 +5628,27 @@
         <v>1000000</v>
       </c>
       <c r="K18" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B19" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C19" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D19" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E19" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G19" s="5">
         <v>252</v>
@@ -5632,21 +5663,21 @@
         <v>60000</v>
       </c>
       <c r="K19" t="s">
-        <v>561</v>
+        <v>712</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B20" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E20" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G20" s="5">
         <v>262</v>
@@ -5661,21 +5692,21 @@
         <v>1500000</v>
       </c>
       <c r="K20" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B21" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E21" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F21" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G21" s="5">
         <v>325</v>
@@ -5690,21 +5721,21 @@
         <v>4000000</v>
       </c>
       <c r="K21" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B22" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E22" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F22" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G22" s="5">
         <v>360</v>
@@ -5719,24 +5750,24 @@
         <v>100000</v>
       </c>
       <c r="K22" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B23" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C23" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E23" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G23" s="5">
         <v>371</v>
@@ -5751,21 +5782,21 @@
         <v>100000</v>
       </c>
       <c r="K23" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B24" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E24" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G24" s="5">
         <v>381</v>
@@ -5780,21 +5811,21 @@
         <v>1500000</v>
       </c>
       <c r="K24" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B25" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E25" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F25" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G25" s="5">
         <v>386</v>
@@ -5809,21 +5840,21 @@
         <v>100000</v>
       </c>
       <c r="K25" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B26" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E26" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G26" s="5">
         <v>423.5</v>
@@ -5838,21 +5869,21 @@
         <v>500000</v>
       </c>
       <c r="K26" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B27" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E27" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F27" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G27" s="5">
         <v>428</v>
@@ -5867,21 +5898,21 @@
         <v>1000000</v>
       </c>
       <c r="K27" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B28" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E28" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F28" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G28" s="5">
         <v>433</v>
@@ -5896,27 +5927,27 @@
         <v>1000000</v>
       </c>
       <c r="K28" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B29" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C29" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D29" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E29" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F29" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G29" s="5">
         <v>445</v>
@@ -5931,21 +5962,21 @@
         <v>500000</v>
       </c>
       <c r="K29" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B30" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E30" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F30" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G30" s="5">
         <v>475</v>
@@ -5960,21 +5991,21 @@
         <v>60000000</v>
       </c>
       <c r="K30" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B31" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E31" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F31" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="G31" s="5">
         <v>490</v>
@@ -5989,21 +6020,21 @@
         <v>30000000</v>
       </c>
       <c r="K31" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B32" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E32" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F32" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G32" s="5">
         <v>495</v>
@@ -6018,21 +6049,21 @@
         <v>2600000</v>
       </c>
       <c r="K32" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B33" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E33" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F33" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G33" s="5">
         <v>507</v>
@@ -6047,21 +6078,21 @@
         <v>500000</v>
       </c>
       <c r="K33" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B34" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E34" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F34" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G34" s="5">
         <v>513</v>
@@ -6076,21 +6107,21 @@
         <v>1000000</v>
       </c>
       <c r="K34" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B35" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E35" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F35" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G35" s="5">
         <v>545</v>
@@ -6105,21 +6136,21 @@
         <v>40000000</v>
       </c>
       <c r="K35" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B36" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E36" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F36" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G36" s="5">
         <v>2220</v>
@@ -6134,21 +6165,21 @@
         <v>100000000</v>
       </c>
       <c r="K36" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B37" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E37" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F37" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G37" s="5">
         <v>2400</v>
@@ -6163,7 +6194,7 @@
         <v>500000000</v>
       </c>
       <c r="K37" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -6194,27 +6225,27 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>502</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>504</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C2" s="2">
         <f>AVERAGEIF(table_s3_events!$E:$E, $A$2, table_s3_events!$H:$H)</f>
@@ -6231,10 +6262,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C3" s="2" cm="1">
         <f t="array" ref="C3">MEDIAN(IF(table_s3_events!$E:$E = $A$3, table_s3_events!$H:$H))</f>
@@ -6251,10 +6282,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B4" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" ref="C4">_xlfn.STDEV.P(IF(table_s3_events!$E:$E=$A$4, table_s3_events!$H:$H))</f>
@@ -6271,10 +6302,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B5" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C5" s="2" cm="1">
         <f t="array" ref="C5">MAX(IF(table_s3_events!$E:$E=$A$5,table_s3_events!$H:$H))</f>
@@ -6291,10 +6322,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C6" s="2" cm="1">
         <f t="array" ref="C6">MIN(IF(table_s3_events!$E:$E=$A$4, table_s3_events!$H:$H))</f>
@@ -6311,10 +6342,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C7" s="16" cm="1">
         <f t="array" ref="C7">COUNT(IF(table_s3_events!$E:$E=$A$7, table_s3_events!$H:$H))</f>
@@ -6331,10 +6362,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B8" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C8" s="2">
         <f>AVERAGEIF(table_s3_events!$E:$E, $A$8, table_s3_events!$H:$H)</f>
@@ -6351,10 +6382,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B9" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C9" s="2" cm="1">
         <f t="array" ref="C9">MEDIAN(IF(table_s3_events!$E:$E = $A$9, table_s3_events!$J:$J))</f>
@@ -6371,10 +6402,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B10" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C10" s="2" cm="1">
         <f t="array" ref="C10">_xlfn.STDEV.P(IF(table_s3_events!$E:$E=$A$10, table_s3_events!$H:$H))</f>
@@ -6391,10 +6422,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B11" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C11" s="2" cm="1">
         <f t="array" ref="C11">MAX(IF(table_s3_events!$E:$E=$A$11, table_s3_events!$H:$H))</f>
@@ -6411,10 +6442,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B12" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C12" s="2" cm="1">
         <f t="array" ref="C12">MIN(IF(table_s3_events!$E:$E=$A$12, table_s3_events!$H:$H))</f>
@@ -6431,10 +6462,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C13" s="16" cm="1">
         <f t="array" ref="C13">COUNT(IF(table_s3_events!$E:$E=$A$13, table_s3_events!$H:$H))</f>
@@ -6457,7 +6488,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582492E0-B1D4-4D01-BDC9-52F30A59C1EC}">
-  <dimension ref="A1:Z108"/>
+  <dimension ref="A1:Z107"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="49.1796875" customWidth="1"/>
@@ -6483,53 +6514,53 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>503</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="J1" s="4" t="str">
         <f>_xlfn.XLOOKUP(A1, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>event_duration_est_yr</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -6538,7 +6569,7 @@
         <v>3100 persistent - sustainable stewardship</v>
       </c>
       <c r="B2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C2" t="str">
         <f>_xlfn.XLOOKUP($B2, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6552,13 +6583,13 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -6568,24 +6599,24 @@
         <v>3300</v>
       </c>
       <c r="K2" s="7">
-        <f t="shared" ref="K2:K34" si="0">IF(OR(F2="species", F2="genus"), (I2*10^4)/J2,"NA")</f>
+        <f t="shared" ref="K2:K33" si="0">IF(OR(F2="species", F2="genus"), (I2*10^4)/J2,"NA")</f>
         <v>6.0606060606060606</v>
       </c>
       <c r="L2" s="7">
-        <f t="shared" ref="L2:L34" si="1">IF(H2="percent", I2/(J2/10^6), "NA")</f>
+        <f t="shared" ref="L2:L33" si="1">IF(H2="percent", I2/(J2/10^6), "NA")</f>
         <v>606.06060606060612</v>
       </c>
       <c r="M2" t="s">
+        <v>632</v>
+      </c>
+      <c r="O2" t="s">
+        <v>633</v>
+      </c>
+      <c r="P2" t="s">
+        <v>634</v>
+      </c>
+      <c r="Q2" t="s">
         <v>635</v>
-      </c>
-      <c r="O2" t="s">
-        <v>636</v>
-      </c>
-      <c r="P2" t="s">
-        <v>637</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -6594,7 +6625,7 @@
         <v>3100 persistent - sustainable stewardship</v>
       </c>
       <c r="B3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C3" t="str">
         <f>_xlfn.XLOOKUP($B3, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6608,13 +6639,13 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I3">
         <v>5</v>
@@ -6632,16 +6663,16 @@
         <v>1515.1515151515152</v>
       </c>
       <c r="M3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="O3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="P3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="Q3" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -6650,7 +6681,7 @@
         <v>3100 transient - business as usual</v>
       </c>
       <c r="B4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C4" t="str">
         <f>_xlfn.XLOOKUP($B4, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6664,13 +6695,13 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G4" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H4" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I4">
         <v>-28</v>
@@ -6688,16 +6719,16 @@
         <v>-8484.8484848484841</v>
       </c>
       <c r="M4" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="O4" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="P4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="Q4" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
@@ -6706,7 +6737,7 @@
         <v>3100 transient - business as usual</v>
       </c>
       <c r="B5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C5" t="str">
         <f>_xlfn.XLOOKUP($B5, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6720,13 +6751,13 @@
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G5" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I5">
         <v>-10</v>
@@ -6744,16 +6775,16 @@
         <v>-3030.3030303030305</v>
       </c>
       <c r="M5" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="O5" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="P5" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="Q5" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -6762,7 +6793,7 @@
         <v>3100 transient - business as usual</v>
       </c>
       <c r="B6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C6" t="str">
         <f>_xlfn.XLOOKUP($B6, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6776,13 +6807,13 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G6" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I6">
         <v>-5</v>
@@ -6800,16 +6831,16 @@
         <v>-1515.1515151515152</v>
       </c>
       <c r="M6" t="s">
+        <v>641</v>
+      </c>
+      <c r="O6" t="s">
+        <v>642</v>
+      </c>
+      <c r="P6" t="s">
+        <v>643</v>
+      </c>
+      <c r="Q6" t="s">
         <v>644</v>
-      </c>
-      <c r="O6" t="s">
-        <v>645</v>
-      </c>
-      <c r="P6" t="s">
-        <v>646</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -6818,7 +6849,7 @@
         <v>2100 persistent - sustainable stewardship</v>
       </c>
       <c r="B7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C7" t="str">
         <f>_xlfn.XLOOKUP($B7, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6832,13 +6863,13 @@
         <v>130</v>
       </c>
       <c r="F7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6856,16 +6887,16 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
+        <v>645</v>
+      </c>
+      <c r="O7" t="s">
+        <v>646</v>
+      </c>
+      <c r="P7" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q7" t="s">
         <v>648</v>
-      </c>
-      <c r="O7" t="s">
-        <v>649</v>
-      </c>
-      <c r="P7" t="s">
-        <v>650</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -6874,7 +6905,7 @@
         <v>2100 persistent - sustainable stewardship</v>
       </c>
       <c r="B8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C8" t="str">
         <f>_xlfn.XLOOKUP($B8, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6888,13 +6919,13 @@
         <v>130</v>
       </c>
       <c r="F8" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G8" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H8" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6912,10 +6943,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="O8" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -6924,7 +6955,7 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B9" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C9" t="str">
         <f>_xlfn.XLOOKUP($B9, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6935,16 +6966,16 @@
         <v>-1E-4</v>
       </c>
       <c r="E9" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F9" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G9" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H9" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I9">
         <v>-32</v>
@@ -6962,7 +6993,7 @@
         <v>-106666.66666666667</v>
       </c>
       <c r="O9" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -6971,7 +7002,7 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B10" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C10" t="str">
         <f>_xlfn.XLOOKUP($B10, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -6985,13 +7016,13 @@
         <v>206</v>
       </c>
       <c r="F10" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G10" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H10" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I10">
         <v>-27</v>
@@ -7009,10 +7040,10 @@
         <v>-90000.000000000015</v>
       </c>
       <c r="M10" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="O10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
@@ -7021,7 +7052,7 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B11" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C11" t="str">
         <f>_xlfn.XLOOKUP($B11, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7035,13 +7066,13 @@
         <v>206</v>
       </c>
       <c r="F11" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G11" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H11" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I11">
         <v>-17.600000000000001</v>
@@ -7059,10 +7090,10 @@
         <v>-58666.666666666679</v>
       </c>
       <c r="M11" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="O11" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -7071,7 +7102,7 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C12" t="str">
         <f>_xlfn.XLOOKUP($B12, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7082,16 +7113,16 @@
         <v>-1E-4</v>
       </c>
       <c r="E12" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F12" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G12" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H12" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I12">
         <v>-14</v>
@@ -7109,7 +7140,7 @@
         <v>-46666.666666666672</v>
       </c>
       <c r="O12" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -7118,7 +7149,7 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.XLOOKUP($B13, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7132,13 +7163,13 @@
         <v>206</v>
       </c>
       <c r="F13" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G13" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H13" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I13">
         <v>-13</v>
@@ -7156,10 +7187,10 @@
         <v>-43333.333333333336</v>
       </c>
       <c r="M13" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="O13" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -7168,7 +7199,7 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B14" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.XLOOKUP($B14, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7182,13 +7213,13 @@
         <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G14" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="H14" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I14">
         <v>-7.8</v>
@@ -7206,10 +7237,10 @@
         <v>-26000</v>
       </c>
       <c r="M14" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="O14" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
@@ -7218,7 +7249,7 @@
         <v>2100 transient - business as usual</v>
       </c>
       <c r="B15" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.XLOOKUP($B15, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7232,13 +7263,13 @@
         <v>130</v>
       </c>
       <c r="F15" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G15" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H15" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I15">
         <v>-3.8</v>
@@ -7256,10 +7287,10 @@
         <v>-12666.666666666668</v>
       </c>
       <c r="M15" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="O15" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -7268,7 +7299,7 @@
         <v>Recent past</v>
       </c>
       <c r="B16" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C16" t="str">
         <f>_xlfn.XLOOKUP($B16, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7279,22 +7310,23 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>707</v>
       </c>
       <c r="F16" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="G16" t="s">
-        <v>659</v>
+        <v>708</v>
       </c>
       <c r="H16" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I16">
-        <v>-83</v>
+        <v>-60</v>
       </c>
       <c r="J16" s="2">
-        <v>47000</v>
+        <f>_xlfn.XLOOKUP(A16, table_s3_events!A:A, table_s3_events!J:J)</f>
+        <v>200</v>
       </c>
       <c r="K16" s="7" t="str">
         <f t="shared" si="0"/>
@@ -7302,13 +7334,13 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" si="1"/>
-        <v>-1765.9574468085107</v>
+        <v>-300000</v>
       </c>
       <c r="M16" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O16" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
@@ -7317,7 +7349,7 @@
         <v>Recent past</v>
       </c>
       <c r="B17" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C17" t="str">
         <f>_xlfn.XLOOKUP($B17, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7328,36 +7360,37 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="F17" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="G17" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="H17" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I17">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="J17" s="2">
-        <v>47000</v>
-      </c>
-      <c r="K17" s="7">
+        <f>_xlfn.XLOOKUP(A17, table_s3_events!A:A, table_s3_events!J:J)</f>
+        <v>200</v>
+      </c>
+      <c r="K17" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>-10.638297872340425</v>
+        <v>NA</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="1"/>
-        <v>-1063.8297872340424</v>
+        <v>-150000</v>
       </c>
       <c r="M17" t="s">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="O17" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
@@ -7366,7 +7399,7 @@
         <v>Recent past</v>
       </c>
       <c r="B18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C18" t="str">
         <f>_xlfn.XLOOKUP($B18, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7377,37 +7410,37 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>702</v>
       </c>
       <c r="F18" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="G18" t="s">
-        <v>663</v>
+        <v>703</v>
       </c>
       <c r="H18" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I18">
-        <v>-30</v>
+        <v>-60</v>
       </c>
       <c r="J18" s="2">
         <f>_xlfn.XLOOKUP(A18, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>200</v>
       </c>
       <c r="K18" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K18" si="2">IF(OR(F18="species", F18="genus"), (I18*10^4)/J18,"NA")</f>
         <v>NA</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="1"/>
-        <v>-150000</v>
+        <f t="shared" ref="L18" si="3">IF(H18="percent", I18/(J18/10^6), "NA")</f>
+        <v>-300000</v>
       </c>
       <c r="M18" t="s">
-        <v>669</v>
+        <v>710</v>
       </c>
       <c r="O18" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
@@ -7416,7 +7449,7 @@
         <v>Recent past</v>
       </c>
       <c r="B19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C19" t="str">
         <f>_xlfn.XLOOKUP($B19, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7427,37 +7460,37 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>706</v>
+        <v>220</v>
       </c>
       <c r="F19" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="G19" t="s">
-        <v>707</v>
+        <v>656</v>
       </c>
       <c r="H19" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I19">
-        <v>-60</v>
+        <v>-1.61</v>
       </c>
       <c r="J19" s="2">
         <f>_xlfn.XLOOKUP(A19, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>200</v>
       </c>
-      <c r="K19" s="7" t="str">
-        <f t="shared" ref="K19" si="2">IF(OR(F19="species", F19="genus"), (I19*10^4)/J19,"NA")</f>
-        <v>NA</v>
+      <c r="K19" s="7">
+        <f t="shared" si="0"/>
+        <v>-80.500000000000014</v>
       </c>
       <c r="L19" s="7">
-        <f t="shared" ref="L19" si="3">IF(H19="percent", I19/(J19/10^6), "NA")</f>
-        <v>-300000</v>
+        <f t="shared" si="1"/>
+        <v>-8050</v>
       </c>
       <c r="M19" t="s">
-        <v>708</v>
+        <v>668</v>
       </c>
       <c r="O19" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -7466,7 +7499,7 @@
         <v>Recent past</v>
       </c>
       <c r="B20" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C20" t="str">
         <f>_xlfn.XLOOKUP($B20, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7480,16 +7513,16 @@
         <v>220</v>
       </c>
       <c r="F20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G20" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="H20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I20">
-        <v>-1.61</v>
+        <v>-1.54</v>
       </c>
       <c r="J20" s="2">
         <f>_xlfn.XLOOKUP(A20, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7497,17 +7530,17 @@
       </c>
       <c r="K20" s="7">
         <f t="shared" si="0"/>
-        <v>-80.500000000000014</v>
+        <v>-77</v>
       </c>
       <c r="L20" s="7">
         <f t="shared" si="1"/>
-        <v>-8050</v>
+        <v>-7700</v>
       </c>
       <c r="M20" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="O20" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -7516,7 +7549,7 @@
         <v>Recent past</v>
       </c>
       <c r="B21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C21" t="str">
         <f>_xlfn.XLOOKUP($B21, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7530,16 +7563,16 @@
         <v>220</v>
       </c>
       <c r="F21" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G21" t="s">
-        <v>668</v>
+        <v>630</v>
       </c>
       <c r="H21" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I21">
-        <v>-1.54</v>
+        <v>-0.88</v>
       </c>
       <c r="J21" s="2">
         <f>_xlfn.XLOOKUP(A21, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7547,17 +7580,17 @@
       </c>
       <c r="K21" s="7">
         <f t="shared" si="0"/>
-        <v>-77</v>
+        <v>-44</v>
       </c>
       <c r="L21" s="7">
         <f t="shared" si="1"/>
-        <v>-7700</v>
+        <v>-4400</v>
       </c>
       <c r="M21" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="O21" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -7566,7 +7599,7 @@
         <v>Recent past</v>
       </c>
       <c r="B22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C22" t="str">
         <f>_xlfn.XLOOKUP($B22, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7580,16 +7613,16 @@
         <v>220</v>
       </c>
       <c r="F22" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G22" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="H22" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I22">
-        <v>-0.88</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="J22" s="2">
         <f>_xlfn.XLOOKUP(A22, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7597,17 +7630,17 @@
       </c>
       <c r="K22" s="7">
         <f t="shared" si="0"/>
-        <v>-44</v>
+        <v>-29</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="1"/>
-        <v>-4400</v>
+        <v>-2899.9999999999995</v>
       </c>
       <c r="M22" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="O22" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -7616,7 +7649,7 @@
         <v>Recent past</v>
       </c>
       <c r="B23" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C23" t="str">
         <f>_xlfn.XLOOKUP($B23, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7627,19 +7660,19 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="F23" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G23" t="s">
-        <v>666</v>
+        <v>630</v>
       </c>
       <c r="H23" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I23">
-        <v>-0.57999999999999996</v>
+        <v>-0.5</v>
       </c>
       <c r="J23" s="2">
         <f>_xlfn.XLOOKUP(A23, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7647,17 +7680,14 @@
       </c>
       <c r="K23" s="7">
         <f t="shared" si="0"/>
-        <v>-29</v>
+        <v>-25</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="1"/>
-        <v>-2899.9999999999995</v>
-      </c>
-      <c r="M23" t="s">
-        <v>675</v>
+        <v>-2500</v>
       </c>
       <c r="O23" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
@@ -7666,7 +7696,7 @@
         <v>Recent past</v>
       </c>
       <c r="B24" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C24" t="str">
         <f>_xlfn.XLOOKUP($B24, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7677,19 +7707,19 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="F24" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G24" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H24" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I24">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="J24" s="2">
         <f>_xlfn.XLOOKUP(A24, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7697,14 +7727,17 @@
       </c>
       <c r="K24" s="7">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>-22.5</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="1"/>
-        <v>-2500</v>
+        <v>-2250</v>
+      </c>
+      <c r="M24" t="s">
+        <v>675</v>
       </c>
       <c r="O24" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -7713,7 +7746,7 @@
         <v>Recent past</v>
       </c>
       <c r="B25" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C25" t="str">
         <f>_xlfn.XLOOKUP($B25, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7727,16 +7760,16 @@
         <v>220</v>
       </c>
       <c r="F25" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G25" t="s">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="H25" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I25">
-        <v>-0.45</v>
+        <v>-0.17</v>
       </c>
       <c r="J25" s="2">
         <f>_xlfn.XLOOKUP(A25, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7744,14 +7777,17 @@
       </c>
       <c r="K25" s="7">
         <f t="shared" si="0"/>
-        <v>-22.5</v>
+        <v>-8.5000000000000018</v>
       </c>
       <c r="L25" s="7">
         <f t="shared" si="1"/>
-        <v>-2250</v>
+        <v>-850</v>
       </c>
       <c r="M25" t="s">
-        <v>678</v>
+        <v>676</v>
+      </c>
+      <c r="O25" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
@@ -7760,7 +7796,7 @@
         <v>Recent past</v>
       </c>
       <c r="B26" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C26" t="str">
         <f>_xlfn.XLOOKUP($B26, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7771,19 +7807,19 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="F26" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G26" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
       <c r="H26" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I26">
-        <v>-0.17</v>
+        <v>-0.01</v>
       </c>
       <c r="J26" s="2">
         <f>_xlfn.XLOOKUP(A26, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7791,14 +7827,11 @@
       </c>
       <c r="K26" s="7">
         <f t="shared" si="0"/>
-        <v>-8.5000000000000018</v>
+        <v>-0.5</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="1"/>
-        <v>-850</v>
-      </c>
-      <c r="M26" t="s">
-        <v>679</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
@@ -7807,7 +7840,7 @@
         <v>Recent past</v>
       </c>
       <c r="B27" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C27" t="str">
         <f>_xlfn.XLOOKUP($B27, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7818,19 +7851,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>186</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G27" t="s">
-        <v>633</v>
+        <v>674</v>
       </c>
       <c r="H27" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I27">
-        <v>-0.01</v>
+        <v>-1</v>
       </c>
       <c r="J27" s="2">
         <f>_xlfn.XLOOKUP(A27, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7838,58 +7871,61 @@
       </c>
       <c r="K27" s="7">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="1"/>
-        <v>-50</v>
+        <v>-5000</v>
+      </c>
+      <c r="M27" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>_xlfn.XLOOKUP($B28, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Recent past</v>
+        <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B28" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C28" t="str">
         <f>_xlfn.XLOOKUP($B28, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>humans so far</v>
+        <v>transient</v>
       </c>
       <c r="D28" s="5">
         <f>_xlfn.XLOOKUP($B28, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G28" t="s">
-        <v>677</v>
+        <v>640</v>
       </c>
       <c r="H28" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="J28" s="2">
         <f>_xlfn.XLOOKUP(A28, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>200</v>
+        <v>500000</v>
       </c>
       <c r="K28" s="7">
         <f t="shared" si="0"/>
-        <v>-50</v>
+        <v>-0.01</v>
       </c>
       <c r="L28" s="7">
         <f t="shared" si="1"/>
-        <v>-5000</v>
+        <v>-1</v>
       </c>
       <c r="M28" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
@@ -7898,7 +7934,7 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B29" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C29" t="str">
         <f>_xlfn.XLOOKUP($B29, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7912,16 +7948,16 @@
         <v>98</v>
       </c>
       <c r="F29" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G29" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H29" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I29">
-        <v>-0.5</v>
+        <v>-11</v>
       </c>
       <c r="J29" s="2">
         <f>_xlfn.XLOOKUP(A29, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7929,14 +7965,14 @@
       </c>
       <c r="K29" s="7">
         <f t="shared" si="0"/>
-        <v>-0.01</v>
+        <v>-0.22</v>
       </c>
       <c r="L29" s="7">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-22</v>
       </c>
       <c r="M29" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
@@ -7945,7 +7981,7 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B30" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C30" t="str">
         <f>_xlfn.XLOOKUP($B30, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -7959,16 +7995,16 @@
         <v>98</v>
       </c>
       <c r="F30" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G30" t="s">
-        <v>643</v>
+        <v>669</v>
       </c>
       <c r="H30" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I30">
-        <v>-11</v>
+        <v>-36</v>
       </c>
       <c r="J30" s="2">
         <f>_xlfn.XLOOKUP(A30, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -7976,14 +8012,14 @@
       </c>
       <c r="K30" s="7">
         <f t="shared" si="0"/>
-        <v>-0.22</v>
+        <v>-0.72</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="1"/>
-        <v>-22</v>
+        <v>-72</v>
       </c>
       <c r="M30" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
@@ -7992,7 +8028,7 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B31" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C31" t="str">
         <f>_xlfn.XLOOKUP($B31, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8006,16 +8042,16 @@
         <v>98</v>
       </c>
       <c r="F31" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G31" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H31" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I31">
-        <v>-36</v>
+        <v>-49</v>
       </c>
       <c r="J31" s="2">
         <f>_xlfn.XLOOKUP(A31, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8023,14 +8059,14 @@
       </c>
       <c r="K31" s="7">
         <f t="shared" si="0"/>
-        <v>-0.72</v>
+        <v>-0.98</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="1"/>
-        <v>-72</v>
+        <v>-98</v>
       </c>
       <c r="M31" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -8039,7 +8075,7 @@
         <v>Pliocene-Pleistocene transition</v>
       </c>
       <c r="B32" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C32" t="str">
         <f>_xlfn.XLOOKUP($B32, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8053,16 +8089,16 @@
         <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G32" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H32" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I32">
-        <v>-49</v>
+        <v>-42</v>
       </c>
       <c r="J32" s="2">
         <f>_xlfn.XLOOKUP(A32, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8070,23 +8106,23 @@
       </c>
       <c r="K32" s="7">
         <f t="shared" si="0"/>
-        <v>-0.98</v>
+        <v>-0.84</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="1"/>
-        <v>-98</v>
+        <v>-84</v>
       </c>
       <c r="M32" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>_xlfn.XLOOKUP($B33, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Pliocene-Pleistocene transition</v>
+        <v>Eocene-Oligocene transition</v>
       </c>
       <c r="B33" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C33" t="str">
         <f>_xlfn.XLOOKUP($B33, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8094,37 +8130,34 @@
       </c>
       <c r="D33" s="5">
         <f>_xlfn.XLOOKUP($B33, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>2.6</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>216</v>
       </c>
       <c r="F33" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G33" t="s">
-        <v>676</v>
+        <v>656</v>
       </c>
       <c r="H33" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I33">
-        <v>-42</v>
+        <v>-77</v>
       </c>
       <c r="J33" s="2">
         <f>_xlfn.XLOOKUP(A33, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="K33" s="7">
         <f t="shared" si="0"/>
-        <v>-0.84</v>
+        <v>-7.7</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="1"/>
-        <v>-84</v>
-      </c>
-      <c r="M33" t="s">
-        <v>685</v>
+        <v>-770</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -8133,7 +8166,7 @@
         <v>Eocene-Oligocene transition</v>
       </c>
       <c r="B34" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C34" t="str">
         <f>_xlfn.XLOOKUP($B34, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8144,31 +8177,31 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G34" t="s">
-        <v>659</v>
+        <v>640</v>
       </c>
       <c r="H34" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I34">
-        <v>-77</v>
+        <v>-16</v>
       </c>
       <c r="J34" s="2">
         <f>_xlfn.XLOOKUP(A34, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>100000</v>
       </c>
       <c r="K34" s="7">
-        <f t="shared" si="0"/>
-        <v>-7.7</v>
+        <f t="shared" ref="K34:K65" si="4">IF(OR(F34="species", F34="genus"), (I34*10^4)/J34,"NA")</f>
+        <v>-1.6</v>
       </c>
       <c r="L34" s="7">
-        <f t="shared" si="1"/>
-        <v>-770</v>
+        <f t="shared" ref="L34:L65" si="5">IF(H34="percent", I34/(J34/10^6), "NA")</f>
+        <v>-160</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -8177,7 +8210,7 @@
         <v>Eocene-Oligocene transition</v>
       </c>
       <c r="B35" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C35" t="str">
         <f>_xlfn.XLOOKUP($B35, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8188,40 +8221,40 @@
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G35" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="H35" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I35">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="J35" s="2">
         <f>_xlfn.XLOOKUP(A35, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>100000</v>
       </c>
       <c r="K35" s="7">
-        <f t="shared" ref="K35:K66" si="4">IF(OR(F35="species", F35="genus"), (I35*10^4)/J35,"NA")</f>
-        <v>-1.6</v>
+        <f t="shared" si="4"/>
+        <v>-1.5</v>
       </c>
       <c r="L35" s="7">
-        <f t="shared" ref="L35:L66" si="5">IF(H35="percent", I35/(J35/10^6), "NA")</f>
-        <v>-160</v>
+        <f t="shared" si="5"/>
+        <v>-150</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>_xlfn.XLOOKUP($B36, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Eocene-Oligocene transition</v>
+        <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B36" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C36" t="str">
         <f>_xlfn.XLOOKUP($B36, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8229,34 +8262,34 @@
       </c>
       <c r="D36" s="5">
         <f>_xlfn.XLOOKUP($B36, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="F36" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G36" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="H36" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I36">
-        <v>-15</v>
+        <v>-65</v>
       </c>
       <c r="J36" s="2">
         <f>_xlfn.XLOOKUP(A36, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="K36" s="7">
         <f t="shared" si="4"/>
-        <v>-1.5</v>
+        <v>-4.333333333333333</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="5"/>
-        <v>-150</v>
+        <v>-433.33333333333337</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
@@ -8265,7 +8298,7 @@
         <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B37" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C37" t="str">
         <f>_xlfn.XLOOKUP($B37, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8279,16 +8312,16 @@
         <v>198</v>
       </c>
       <c r="F37" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G37" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H37" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I37">
-        <v>-65</v>
+        <v>-33</v>
       </c>
       <c r="J37" s="2">
         <f>_xlfn.XLOOKUP(A37, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8296,11 +8329,11 @@
       </c>
       <c r="K37" s="7">
         <f t="shared" si="4"/>
-        <v>-4.333333333333333</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="5"/>
-        <v>-433.33333333333337</v>
+        <v>-220</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
@@ -8309,7 +8342,7 @@
         <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B38" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.XLOOKUP($B38, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8320,19 +8353,19 @@
         <v>56</v>
       </c>
       <c r="E38" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="F38" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G38" t="s">
-        <v>656</v>
+        <v>633</v>
       </c>
       <c r="H38" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I38">
-        <v>-33</v>
+        <v>-20</v>
       </c>
       <c r="J38" s="2">
         <f>_xlfn.XLOOKUP(A38, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8340,11 +8373,11 @@
       </c>
       <c r="K38" s="7">
         <f t="shared" si="4"/>
-        <v>-2.2000000000000002</v>
+        <v>-1.3333333333333333</v>
       </c>
       <c r="L38" s="7">
         <f t="shared" si="5"/>
-        <v>-220</v>
+        <v>-133.33333333333334</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
@@ -8353,7 +8386,7 @@
         <v>Palaeocene-Eocene Thermal Maximum</v>
       </c>
       <c r="B39" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.XLOOKUP($B39, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8367,16 +8400,16 @@
         <v>80</v>
       </c>
       <c r="F39" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G39" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="H39" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I39">
-        <v>-20</v>
+        <v>-1</v>
       </c>
       <c r="J39" s="2">
         <f>_xlfn.XLOOKUP(A39, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8384,17 +8417,17 @@
       </c>
       <c r="K39" s="7">
         <f t="shared" si="4"/>
-        <v>-1.3333333333333333</v>
+        <v>-6.6666666666666666E-2</v>
       </c>
       <c r="L39" s="7">
         <f t="shared" si="5"/>
-        <v>-133.33333333333334</v>
+        <v>-6.666666666666667</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>_xlfn.XLOOKUP($B40, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Palaeocene-Eocene Thermal Maximum</v>
+        <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B40" t="s">
         <v>531</v>
@@ -8405,34 +8438,34 @@
       </c>
       <c r="D40" s="5">
         <f>_xlfn.XLOOKUP($B40, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G40" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H40" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>-40</v>
       </c>
       <c r="J40" s="2">
         <f>_xlfn.XLOOKUP(A40, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>150000</v>
+        <v>30</v>
       </c>
       <c r="K40" s="7">
         <f t="shared" si="4"/>
-        <v>-6.6666666666666666E-2</v>
+        <v>-13333.333333333334</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="5"/>
-        <v>-6.666666666666667</v>
+        <v>-1333333.3333333333</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -8441,7 +8474,7 @@
         <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B41" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C41" t="str">
         <f>_xlfn.XLOOKUP($B41, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8452,16 +8485,16 @@
         <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="F41" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G41" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H41" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I41">
         <v>-40</v>
@@ -8485,7 +8518,7 @@
         <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B42" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.XLOOKUP($B42, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8496,19 +8529,19 @@
         <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="F42" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G42" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H42" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I42">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="J42" s="2">
         <f>_xlfn.XLOOKUP(A42, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8516,11 +8549,11 @@
       </c>
       <c r="K42" s="7">
         <f t="shared" si="4"/>
-        <v>-13333.333333333334</v>
+        <v>-13000</v>
       </c>
       <c r="L42" s="7">
         <f t="shared" si="5"/>
-        <v>-1333333.3333333333</v>
+        <v>-1300000</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
@@ -8529,7 +8562,7 @@
         <v>Cretaceous-Palaeogene boundary</v>
       </c>
       <c r="B43" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.XLOOKUP($B43, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8540,19 +8573,19 @@
         <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F43" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G43" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H43" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I43">
-        <v>-39</v>
+        <v>-75</v>
       </c>
       <c r="J43" s="2">
         <f>_xlfn.XLOOKUP(A43, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8560,20 +8593,23 @@
       </c>
       <c r="K43" s="7">
         <f t="shared" si="4"/>
-        <v>-13000</v>
+        <v>-25000</v>
       </c>
       <c r="L43" s="7">
         <f t="shared" si="5"/>
-        <v>-1300000</v>
+        <v>-2500000</v>
+      </c>
+      <c r="M43" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="str">
         <f>_xlfn.XLOOKUP($B44, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Cretaceous-Palaeogene boundary</v>
+        <v>OAE2 (Cenomanian-Turonian)</v>
       </c>
       <c r="B44" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C44" t="str">
         <f>_xlfn.XLOOKUP($B44, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8581,46 +8617,43 @@
       </c>
       <c r="D44" s="5">
         <f>_xlfn.XLOOKUP($B44, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="F44" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G44" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="H44" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I44">
-        <v>-75</v>
+        <v>-20</v>
       </c>
       <c r="J44" s="2">
         <f>_xlfn.XLOOKUP(A44, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>30</v>
+        <v>500000</v>
       </c>
       <c r="K44" s="7">
         <f t="shared" si="4"/>
-        <v>-25000</v>
+        <v>-0.4</v>
       </c>
       <c r="L44" s="7">
         <f t="shared" si="5"/>
-        <v>-2500000</v>
-      </c>
-      <c r="M44" t="s">
-        <v>686</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>_xlfn.XLOOKUP($B45, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>OAE2 (Cenomanian-Turonian)</v>
+        <v>OAE1a (Aptian)</v>
       </c>
       <c r="B45" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C45" t="str">
         <f>_xlfn.XLOOKUP($B45, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8628,22 +8661,22 @@
       </c>
       <c r="D45" s="5">
         <f>_xlfn.XLOOKUP($B45, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
         <v>80</v>
       </c>
       <c r="F45" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G45" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="H45" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I45">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="J45" s="2">
         <f>_xlfn.XLOOKUP(A45, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8651,55 +8684,58 @@
       </c>
       <c r="K45" s="7">
         <f t="shared" si="4"/>
-        <v>-0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="L45" s="7">
         <f t="shared" si="5"/>
-        <v>-40</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>_xlfn.XLOOKUP($B46, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>OAE1a (Aptian)</v>
+        <v>Angiosperm Terrestrial Revolution</v>
       </c>
       <c r="B46" t="s">
         <v>540</v>
       </c>
       <c r="C46" t="str">
         <f>_xlfn.XLOOKUP($B46, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>transient</v>
+        <v>persistent</v>
       </c>
       <c r="D46" s="5">
         <f>_xlfn.XLOOKUP($B46, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F46" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G46" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="H46" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I46">
-        <v>-22</v>
+        <v>150</v>
       </c>
       <c r="J46" s="2">
         <f>_xlfn.XLOOKUP(A46, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>500000</v>
+        <v>75000000</v>
       </c>
       <c r="K46" s="7">
         <f t="shared" si="4"/>
-        <v>-0.44</v>
+        <v>0.02</v>
       </c>
       <c r="L46" s="7">
         <f t="shared" si="5"/>
-        <v>-44</v>
+        <v>2</v>
+      </c>
+      <c r="M46" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
@@ -8708,7 +8744,7 @@
         <v>Angiosperm Terrestrial Revolution</v>
       </c>
       <c r="B47" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C47" t="str">
         <f>_xlfn.XLOOKUP($B47, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8719,90 +8755,87 @@
         <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="G47" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H47" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I47">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J47" s="2">
         <f>_xlfn.XLOOKUP(A47, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>75000000</v>
       </c>
-      <c r="K47" s="7">
+      <c r="K47" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>0.02</v>
+        <v>NA</v>
       </c>
       <c r="L47" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>2.1466666666666665</v>
       </c>
       <c r="M47" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="str">
         <f>_xlfn.XLOOKUP($B48, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Angiosperm Terrestrial Revolution</v>
+        <v>Jurassic-Cretaceous extinction (Tithonian)</v>
       </c>
       <c r="B48" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C48" t="str">
         <f>_xlfn.XLOOKUP($B48, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>persistent</v>
+        <v>transient</v>
       </c>
       <c r="D48" s="5">
         <f>_xlfn.XLOOKUP($B48, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>140</v>
+        <v>143.1</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="G48" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="H48" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I48">
-        <v>161</v>
+        <v>-20</v>
       </c>
       <c r="J48" s="2">
         <f>_xlfn.XLOOKUP(A48, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>75000000</v>
-      </c>
-      <c r="K48" s="7" t="str">
+        <v>1000000</v>
+      </c>
+      <c r="K48" s="7">
         <f t="shared" si="4"/>
-        <v>NA</v>
+        <v>-0.2</v>
       </c>
       <c r="L48" s="7">
         <f t="shared" si="5"/>
-        <v>2.1466666666666665</v>
-      </c>
-      <c r="M48" t="s">
-        <v>688</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="str">
         <f>_xlfn.XLOOKUP($B49, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Jurassic-Cretaceous extinction (Tithonian)</v>
+        <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B49" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C49" t="str">
         <f>_xlfn.XLOOKUP($B49, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8810,34 +8843,34 @@
       </c>
       <c r="D49" s="5">
         <f>_xlfn.XLOOKUP($B49, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>143.1</v>
+        <v>183</v>
       </c>
       <c r="E49" t="s">
         <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G49" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H49" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I49">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="J49" s="2">
         <f>_xlfn.XLOOKUP(A49, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="K49" s="7">
         <f t="shared" si="4"/>
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="L49" s="7">
         <f t="shared" si="5"/>
-        <v>-20</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
@@ -8846,7 +8879,7 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B50" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C50" t="str">
         <f>_xlfn.XLOOKUP($B50, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8860,16 +8893,16 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G50" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H50" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I50">
-        <v>-25</v>
+        <v>-22</v>
       </c>
       <c r="J50" s="2">
         <f>_xlfn.XLOOKUP(A50, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8877,11 +8910,11 @@
       </c>
       <c r="K50" s="7">
         <f t="shared" si="4"/>
-        <v>-0.5</v>
+        <v>-0.44</v>
       </c>
       <c r="L50" s="7">
         <f t="shared" si="5"/>
-        <v>-50</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -8890,7 +8923,7 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B51" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C51" t="str">
         <f>_xlfn.XLOOKUP($B51, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8901,19 +8934,19 @@
         <v>183</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="F51" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G51" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="H51" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I51">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="J51" s="2">
         <f>_xlfn.XLOOKUP(A51, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8921,11 +8954,11 @@
       </c>
       <c r="K51" s="7">
         <f t="shared" si="4"/>
-        <v>-0.44</v>
+        <v>-0.4</v>
       </c>
       <c r="L51" s="7">
         <f t="shared" si="5"/>
-        <v>-44</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
@@ -8934,7 +8967,7 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B52" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C52" t="str">
         <f>_xlfn.XLOOKUP($B52, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -8948,16 +8981,16 @@
         <v>80</v>
       </c>
       <c r="F52" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G52" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="H52" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I52">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="J52" s="2">
         <f>_xlfn.XLOOKUP(A52, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -8965,11 +8998,11 @@
       </c>
       <c r="K52" s="7">
         <f t="shared" si="4"/>
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="L52" s="7">
         <f t="shared" si="5"/>
-        <v>-40</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
@@ -8978,30 +9011,29 @@
         <v>T-OAE (Toarcian)</v>
       </c>
       <c r="B53" t="s">
-        <v>550</v>
-      </c>
-      <c r="C53" t="str">
-        <f>_xlfn.XLOOKUP($B53, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>transient</v>
+        <v>548</v>
+      </c>
+      <c r="C53" t="s">
+        <v>523</v>
       </c>
       <c r="D53" s="5">
         <f>_xlfn.XLOOKUP($B53, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
         <v>183</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F53" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G53" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H53" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I53">
-        <v>-15</v>
+        <v>-26</v>
       </c>
       <c r="J53" s="2">
         <f>_xlfn.XLOOKUP(A53, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9009,54 +9041,55 @@
       </c>
       <c r="K53" s="7">
         <f t="shared" si="4"/>
-        <v>-0.3</v>
+        <v>-0.52</v>
       </c>
       <c r="L53" s="7">
         <f t="shared" si="5"/>
-        <v>-30</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" t="str">
         <f>_xlfn.XLOOKUP($B54, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>T-OAE (Toarcian)</v>
+        <v>End-Triassic</v>
       </c>
       <c r="B54" t="s">
         <v>550</v>
       </c>
-      <c r="C54" t="s">
-        <v>525</v>
+      <c r="C54" t="str">
+        <f>_xlfn.XLOOKUP($B54, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
+        <v>transient</v>
       </c>
       <c r="D54" s="5">
         <f>_xlfn.XLOOKUP($B54, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E54" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F54" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G54" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="H54" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I54">
-        <v>-26</v>
+        <v>-80</v>
       </c>
       <c r="J54" s="2">
         <f>_xlfn.XLOOKUP(A54, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>500000</v>
+        <v>85000</v>
       </c>
       <c r="K54" s="7">
         <f t="shared" si="4"/>
-        <v>-0.52</v>
+        <v>-9.4117647058823533</v>
       </c>
       <c r="L54" s="7">
         <f t="shared" si="5"/>
-        <v>-52</v>
+        <v>-941.17647058823525</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
@@ -9065,7 +9098,7 @@
         <v>End-Triassic</v>
       </c>
       <c r="B55" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C55" t="str">
         <f>_xlfn.XLOOKUP($B55, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9076,19 +9109,19 @@
         <v>201</v>
       </c>
       <c r="E55" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="F55" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G55" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H55" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I55">
-        <v>-80</v>
+        <v>-73</v>
       </c>
       <c r="J55" s="2">
         <f>_xlfn.XLOOKUP(A55, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9096,11 +9129,11 @@
       </c>
       <c r="K55" s="7">
         <f t="shared" si="4"/>
-        <v>-9.4117647058823533</v>
+        <v>-8.5882352941176467</v>
       </c>
       <c r="L55" s="7">
         <f t="shared" si="5"/>
-        <v>-941.17647058823525</v>
+        <v>-858.82352941176464</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
@@ -9109,7 +9142,7 @@
         <v>End-Triassic</v>
       </c>
       <c r="B56" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C56" t="str">
         <f>_xlfn.XLOOKUP($B56, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9120,19 +9153,19 @@
         <v>201</v>
       </c>
       <c r="E56" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="F56" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G56" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H56" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I56">
-        <v>-73</v>
+        <v>-47</v>
       </c>
       <c r="J56" s="2">
         <f>_xlfn.XLOOKUP(A56, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9140,17 +9173,17 @@
       </c>
       <c r="K56" s="7">
         <f t="shared" si="4"/>
-        <v>-8.5882352941176467</v>
+        <v>-5.5294117647058822</v>
       </c>
       <c r="L56" s="7">
         <f t="shared" si="5"/>
-        <v>-858.82352941176464</v>
+        <v>-552.94117647058818</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" t="str">
         <f>_xlfn.XLOOKUP($B57, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>End-Triassic</v>
+        <v>Carnian (Triassic)</v>
       </c>
       <c r="B57" t="s">
         <v>552</v>
@@ -9161,34 +9194,37 @@
       </c>
       <c r="D57" s="5">
         <f>_xlfn.XLOOKUP($B57, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="E57" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="F57" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G57" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="H57" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I57">
-        <v>-47</v>
+        <v>-62</v>
       </c>
       <c r="J57" s="2">
         <f>_xlfn.XLOOKUP(A57, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>85000</v>
+        <v>1090000</v>
       </c>
       <c r="K57" s="7">
         <f t="shared" si="4"/>
-        <v>-5.5294117647058822</v>
+        <v>-0.56880733944954132</v>
       </c>
       <c r="L57" s="7">
         <f t="shared" si="5"/>
-        <v>-552.94117647058818</v>
+        <v>-56.880733944954123</v>
+      </c>
+      <c r="M57" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
@@ -9197,7 +9233,7 @@
         <v>Carnian (Triassic)</v>
       </c>
       <c r="B58" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C58" t="str">
         <f>_xlfn.XLOOKUP($B58, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9211,16 +9247,16 @@
         <v>182</v>
       </c>
       <c r="F58" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G58" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="H58" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I58">
-        <v>-62</v>
+        <v>-51</v>
       </c>
       <c r="J58" s="2">
         <f>_xlfn.XLOOKUP(A58, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9228,14 +9264,14 @@
       </c>
       <c r="K58" s="7">
         <f t="shared" si="4"/>
-        <v>-0.56880733944954132</v>
+        <v>-0.46788990825688076</v>
       </c>
       <c r="L58" s="7">
         <f t="shared" si="5"/>
-        <v>-56.880733944954123</v>
+        <v>-46.788990825688067</v>
       </c>
       <c r="M58" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
@@ -9244,7 +9280,7 @@
         <v>Carnian (Triassic)</v>
       </c>
       <c r="B59" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C59" t="str">
         <f>_xlfn.XLOOKUP($B59, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9255,19 +9291,19 @@
         <v>234</v>
       </c>
       <c r="E59" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="F59" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G59" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="H59" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I59">
-        <v>-51</v>
+        <v>-33</v>
       </c>
       <c r="J59" s="2">
         <f>_xlfn.XLOOKUP(A59, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9275,23 +9311,23 @@
       </c>
       <c r="K59" s="7">
         <f t="shared" si="4"/>
-        <v>-0.46788990825688076</v>
+        <v>-0.30275229357798167</v>
       </c>
       <c r="L59" s="7">
         <f t="shared" si="5"/>
-        <v>-46.788990825688067</v>
+        <v>-30.275229357798164</v>
       </c>
       <c r="M59" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" t="str">
         <f>_xlfn.XLOOKUP($B60, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Carnian (Triassic)</v>
+        <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B60" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C60" t="str">
         <f>_xlfn.XLOOKUP($B60, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9299,37 +9335,34 @@
       </c>
       <c r="D60" s="5">
         <f>_xlfn.XLOOKUP($B60, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="E60" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F60" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G60" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="H60" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I60">
-        <v>-33</v>
+        <v>-95</v>
       </c>
       <c r="J60" s="2">
         <f>_xlfn.XLOOKUP(A60, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>1090000</v>
+        <v>60000</v>
       </c>
       <c r="K60" s="7">
         <f t="shared" si="4"/>
-        <v>-0.30275229357798167</v>
+        <v>-15.833333333333334</v>
       </c>
       <c r="L60" s="7">
         <f t="shared" si="5"/>
-        <v>-30.275229357798164</v>
-      </c>
-      <c r="M60" t="s">
-        <v>690</v>
+        <v>-1583.3333333333335</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
@@ -9338,7 +9371,7 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B61" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C61" t="str">
         <f>_xlfn.XLOOKUP($B61, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9349,19 +9382,19 @@
         <v>252</v>
       </c>
       <c r="E61" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="F61" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G61" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H61" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I61">
-        <v>-95</v>
+        <v>-83</v>
       </c>
       <c r="J61" s="2">
         <f>_xlfn.XLOOKUP(A61, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9369,11 +9402,11 @@
       </c>
       <c r="K61" s="7">
         <f t="shared" si="4"/>
-        <v>-15.833333333333334</v>
+        <v>-13.833333333333334</v>
       </c>
       <c r="L61" s="7">
         <f t="shared" si="5"/>
-        <v>-1583.3333333333335</v>
+        <v>-1383.3333333333335</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
@@ -9382,7 +9415,7 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B62" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C62" t="str">
         <f>_xlfn.XLOOKUP($B62, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9393,31 +9426,31 @@
         <v>252</v>
       </c>
       <c r="E62" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
       <c r="F62" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="G62" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
       <c r="H62" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I62">
-        <v>-83</v>
+        <v>-70</v>
       </c>
       <c r="J62" s="2">
         <f>_xlfn.XLOOKUP(A62, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>60000</v>
       </c>
-      <c r="K62" s="7">
+      <c r="K62" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>-13.833333333333334</v>
+        <v>NA</v>
       </c>
       <c r="L62" s="7">
         <f t="shared" si="5"/>
-        <v>-1383.3333333333335</v>
+        <v>-1166.6666666666667</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
@@ -9426,7 +9459,7 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B63" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C63" t="str">
         <f>_xlfn.XLOOKUP($B63, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9437,31 +9470,31 @@
         <v>252</v>
       </c>
       <c r="E63" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="F63" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="G63" t="s">
-        <v>663</v>
+        <v>640</v>
       </c>
       <c r="H63" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I63">
-        <v>-70</v>
+        <v>-62</v>
       </c>
       <c r="J63" s="2">
         <f>_xlfn.XLOOKUP(A63, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>60000</v>
       </c>
-      <c r="K63" s="7" t="str">
+      <c r="K63" s="7">
         <f t="shared" si="4"/>
-        <v>NA</v>
+        <v>-10.333333333333334</v>
       </c>
       <c r="L63" s="7">
         <f t="shared" si="5"/>
-        <v>-1166.6666666666667</v>
+        <v>-1033.3333333333335</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
@@ -9470,7 +9503,7 @@
         <v>Permo-Triassic mass extinction</v>
       </c>
       <c r="B64" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C64" t="str">
         <f>_xlfn.XLOOKUP($B64, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9481,19 +9514,19 @@
         <v>252</v>
       </c>
       <c r="E64" t="s">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G64" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H64" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I64">
-        <v>-62</v>
+        <v>-56</v>
       </c>
       <c r="J64" s="2">
         <f>_xlfn.XLOOKUP(A64, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9501,17 +9534,17 @@
       </c>
       <c r="K64" s="7">
         <f t="shared" si="4"/>
-        <v>-10.333333333333334</v>
+        <v>-9.3333333333333339</v>
       </c>
       <c r="L64" s="7">
         <f t="shared" si="5"/>
-        <v>-1033.3333333333335</v>
+        <v>-933.33333333333337</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A65" t="str">
         <f>_xlfn.XLOOKUP($B65, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Permo-Triassic mass extinction</v>
+        <v>End-Guadalupian (Capitanian; Permian)</v>
       </c>
       <c r="B65" t="s">
         <v>560</v>
@@ -9522,34 +9555,34 @@
       </c>
       <c r="D65" s="5">
         <f>_xlfn.XLOOKUP($B65, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G65" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H65" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I65">
-        <v>-56</v>
+        <v>-48</v>
       </c>
       <c r="J65" s="2">
         <f>_xlfn.XLOOKUP(A65, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>60000</v>
+        <v>1500000</v>
       </c>
       <c r="K65" s="7">
         <f t="shared" si="4"/>
-        <v>-9.3333333333333339</v>
+        <v>-0.32</v>
       </c>
       <c r="L65" s="7">
         <f t="shared" si="5"/>
-        <v>-933.33333333333337</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.35">
@@ -9558,7 +9591,7 @@
         <v>End-Guadalupian (Capitanian; Permian)</v>
       </c>
       <c r="B66" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C66" t="str">
         <f>_xlfn.XLOOKUP($B66, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9569,31 +9602,31 @@
         <v>262</v>
       </c>
       <c r="E66" t="s">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="F66" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G66" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H66" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I66">
-        <v>-48</v>
+        <v>-34</v>
       </c>
       <c r="J66" s="2">
         <f>_xlfn.XLOOKUP(A66, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>1500000</v>
       </c>
       <c r="K66" s="7">
-        <f t="shared" si="4"/>
-        <v>-0.32</v>
+        <f t="shared" ref="K66:K97" si="6">IF(OR(F66="species", F66="genus"), (I66*10^4)/J66,"NA")</f>
+        <v>-0.22666666666666666</v>
       </c>
       <c r="L66" s="7">
-        <f t="shared" si="5"/>
-        <v>-32</v>
+        <f t="shared" ref="L66:L97" si="7">IF(H66="percent", I66/(J66/10^6), "NA")</f>
+        <v>-22.666666666666668</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.35">
@@ -9602,7 +9635,7 @@
         <v>End-Guadalupian (Capitanian; Permian)</v>
       </c>
       <c r="B67" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C67" t="str">
         <f>_xlfn.XLOOKUP($B67, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9613,40 +9646,40 @@
         <v>262</v>
       </c>
       <c r="E67" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="F67" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G67" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H67" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I67">
-        <v>-34</v>
+        <v>-25</v>
       </c>
       <c r="J67" s="2">
         <f>_xlfn.XLOOKUP(A67, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>1500000</v>
       </c>
       <c r="K67" s="7">
-        <f t="shared" ref="K67:K98" si="6">IF(OR(F67="species", F67="genus"), (I67*10^4)/J67,"NA")</f>
-        <v>-0.22666666666666666</v>
+        <f t="shared" si="6"/>
+        <v>-0.16666666666666666</v>
       </c>
       <c r="L67" s="7">
-        <f t="shared" ref="L67:L98" si="7">IF(H67="percent", I67/(J67/10^6), "NA")</f>
-        <v>-22.666666666666668</v>
+        <f t="shared" si="7"/>
+        <v>-16.666666666666668</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A68" t="str">
         <f>_xlfn.XLOOKUP($B68, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>End-Guadalupian (Capitanian; Permian)</v>
+        <v>Serpukhovian (late Mississippian; Carboniferous)</v>
       </c>
       <c r="B68" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C68" t="str">
         <f>_xlfn.XLOOKUP($B68, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9654,34 +9687,34 @@
       </c>
       <c r="D68" s="5">
         <f>_xlfn.XLOOKUP($B68, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>262</v>
+        <v>325</v>
       </c>
       <c r="E68" t="s">
         <v>142</v>
       </c>
       <c r="F68" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G68" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H68" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I68">
-        <v>-25</v>
+        <v>-39</v>
       </c>
       <c r="J68" s="2">
         <f>_xlfn.XLOOKUP(A68, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>1500000</v>
+        <v>4000000</v>
       </c>
       <c r="K68" s="7">
         <f t="shared" si="6"/>
-        <v>-0.16666666666666666</v>
+        <v>-9.7500000000000003E-2</v>
       </c>
       <c r="L68" s="7">
         <f t="shared" si="7"/>
-        <v>-16.666666666666668</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.35">
@@ -9690,7 +9723,7 @@
         <v>Serpukhovian (late Mississippian; Carboniferous)</v>
       </c>
       <c r="B69" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C69" t="str">
         <f>_xlfn.XLOOKUP($B69, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9701,19 +9734,19 @@
         <v>325</v>
       </c>
       <c r="E69" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="F69" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G69" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H69" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I69">
-        <v>-39</v>
+        <v>-31</v>
       </c>
       <c r="J69" s="2">
         <f>_xlfn.XLOOKUP(A69, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9721,11 +9754,11 @@
       </c>
       <c r="K69" s="7">
         <f t="shared" si="6"/>
-        <v>-9.7500000000000003E-2</v>
+        <v>-7.7499999999999999E-2</v>
       </c>
       <c r="L69" s="7">
         <f t="shared" si="7"/>
-        <v>-9.75</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.35">
@@ -9734,7 +9767,7 @@
         <v>Serpukhovian (late Mississippian; Carboniferous)</v>
       </c>
       <c r="B70" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C70" t="str">
         <f>_xlfn.XLOOKUP($B70, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9745,19 +9778,19 @@
         <v>325</v>
       </c>
       <c r="E70" t="s">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="F70" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G70" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H70" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I70">
-        <v>-31</v>
+        <v>-14</v>
       </c>
       <c r="J70" s="2">
         <f>_xlfn.XLOOKUP(A70, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9765,18 +9798,18 @@
       </c>
       <c r="K70" s="7">
         <f t="shared" si="6"/>
-        <v>-7.7499999999999999E-2</v>
+        <v>-3.5000000000000003E-2</v>
       </c>
       <c r="L70" s="7">
         <f t="shared" si="7"/>
-        <v>-7.75</v>
+        <v>-3.5</v>
       </c>
       <c r="Z70" s="8"/>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A71" t="str">
         <f>_xlfn.XLOOKUP($B71, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Serpukhovian (late Mississippian; Carboniferous)</v>
+        <v>Hangenberg Event (end-Devonian)</v>
       </c>
       <c r="B71" t="s">
         <v>565</v>
@@ -9787,34 +9820,34 @@
       </c>
       <c r="D71" s="5">
         <f>_xlfn.XLOOKUP($B71, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="E71" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="F71" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G71" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H71" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I71">
-        <v>-14</v>
+        <v>-50</v>
       </c>
       <c r="J71" s="2">
         <f>_xlfn.XLOOKUP(A71, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>4000000</v>
+        <v>100000</v>
       </c>
       <c r="K71" s="7">
         <f t="shared" si="6"/>
-        <v>-3.5000000000000003E-2</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="7">
         <f t="shared" si="7"/>
-        <v>-3.5</v>
+        <v>-500</v>
       </c>
       <c r="Z71" s="8"/>
     </row>
@@ -9824,7 +9857,7 @@
         <v>Hangenberg Event (end-Devonian)</v>
       </c>
       <c r="B72" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C72" t="str">
         <f>_xlfn.XLOOKUP($B72, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9835,19 +9868,19 @@
         <v>360</v>
       </c>
       <c r="E72" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G72" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H72" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I72">
-        <v>-50</v>
+        <v>-31</v>
       </c>
       <c r="J72" s="2">
         <f>_xlfn.XLOOKUP(A72, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9855,18 +9888,18 @@
       </c>
       <c r="K72" s="7">
         <f t="shared" si="6"/>
-        <v>-5</v>
+        <v>-3.1</v>
       </c>
       <c r="L72" s="7">
         <f t="shared" si="7"/>
-        <v>-500</v>
+        <v>-310</v>
       </c>
       <c r="Z72" s="8"/>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A73" t="str">
         <f>_xlfn.XLOOKUP($B73, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Hangenberg Event (end-Devonian)</v>
+        <v>Frasnian-Famenian (Late Devonian)</v>
       </c>
       <c r="B73" t="s">
         <v>568</v>
@@ -9877,22 +9910,22 @@
       </c>
       <c r="D73" s="5">
         <f>_xlfn.XLOOKUP($B73, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E73" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="F73" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G73" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H73" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I73">
-        <v>-31</v>
+        <v>-40</v>
       </c>
       <c r="J73" s="2">
         <f>_xlfn.XLOOKUP(A73, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9900,11 +9933,11 @@
       </c>
       <c r="K73" s="7">
         <f t="shared" si="6"/>
-        <v>-3.1</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="7">
         <f t="shared" si="7"/>
-        <v>-310</v>
+        <v>-400</v>
       </c>
       <c r="Y73" s="8"/>
       <c r="Z73" s="8"/>
@@ -9915,7 +9948,7 @@
         <v>Frasnian-Famenian (Late Devonian)</v>
       </c>
       <c r="B74" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C74" t="str">
         <f>_xlfn.XLOOKUP($B74, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9926,19 +9959,19 @@
         <v>371</v>
       </c>
       <c r="E74" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="F74" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G74" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H74" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I74">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="J74" s="2">
         <f>_xlfn.XLOOKUP(A74, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9946,11 +9979,11 @@
       </c>
       <c r="K74" s="7">
         <f t="shared" si="6"/>
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="L74" s="7">
         <f t="shared" si="7"/>
-        <v>-400</v>
+        <v>-350</v>
       </c>
       <c r="Z74" s="8"/>
     </row>
@@ -9960,7 +9993,7 @@
         <v>Frasnian-Famenian (Late Devonian)</v>
       </c>
       <c r="B75" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C75" t="str">
         <f>_xlfn.XLOOKUP($B75, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -9971,19 +10004,19 @@
         <v>371</v>
       </c>
       <c r="E75" t="s">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="F75" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G75" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H75" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I75">
-        <v>-35</v>
+        <v>-18</v>
       </c>
       <c r="J75" s="2">
         <f>_xlfn.XLOOKUP(A75, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -9991,11 +10024,11 @@
       </c>
       <c r="K75" s="7">
         <f t="shared" si="6"/>
-        <v>-3.5</v>
+        <v>-1.8</v>
       </c>
       <c r="L75" s="7">
         <f t="shared" si="7"/>
-        <v>-350</v>
+        <v>-180</v>
       </c>
       <c r="Y75" s="8"/>
       <c r="Z75" s="8"/>
@@ -10003,10 +10036,10 @@
     <row r="76" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A76" t="str">
         <f>_xlfn.XLOOKUP($B76, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Frasnian-Famenian (Late Devonian)</v>
+        <v>Taghanic Event (Giventian, Middle Devonian)</v>
       </c>
       <c r="B76" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C76" t="str">
         <f>_xlfn.XLOOKUP($B76, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10014,34 +10047,34 @@
       </c>
       <c r="D76" s="5">
         <f>_xlfn.XLOOKUP($B76, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="E76" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="F76" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G76" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H76" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I76">
-        <v>-18</v>
+        <v>-36</v>
       </c>
       <c r="J76" s="2">
         <f>_xlfn.XLOOKUP(A76, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="K76" s="7">
         <f t="shared" si="6"/>
-        <v>-1.8</v>
+        <v>-0.24</v>
       </c>
       <c r="L76" s="7">
         <f t="shared" si="7"/>
-        <v>-180</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.35">
@@ -10050,7 +10083,7 @@
         <v>Taghanic Event (Giventian, Middle Devonian)</v>
       </c>
       <c r="B77" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C77" t="str">
         <f>_xlfn.XLOOKUP($B77, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10061,19 +10094,19 @@
         <v>381</v>
       </c>
       <c r="E77" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G77" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H77" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I77">
-        <v>-36</v>
+        <v>-29</v>
       </c>
       <c r="J77" s="2">
         <f>_xlfn.XLOOKUP(A77, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10081,17 +10114,17 @@
       </c>
       <c r="K77" s="7">
         <f t="shared" si="6"/>
-        <v>-0.24</v>
+        <v>-0.19333333333333333</v>
       </c>
       <c r="L77" s="7">
         <f t="shared" si="7"/>
-        <v>-24</v>
+        <v>-19.333333333333332</v>
       </c>
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A78" t="str">
         <f>_xlfn.XLOOKUP($B78, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Taghanic Event (Giventian, Middle Devonian)</v>
+        <v>Kačák Event (Eifelian, Middle Devonian)</v>
       </c>
       <c r="B78" t="s">
         <v>573</v>
@@ -10102,40 +10135,40 @@
       </c>
       <c r="D78" s="5">
         <f>_xlfn.XLOOKUP($B78, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E78" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="F78" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G78" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H78" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I78">
-        <v>-29</v>
+        <v>-32</v>
       </c>
       <c r="J78" s="2">
         <f>_xlfn.XLOOKUP(A78, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>1500000</v>
+        <v>100000</v>
       </c>
       <c r="K78" s="7">
         <f t="shared" si="6"/>
-        <v>-0.19333333333333333</v>
+        <v>-3.2</v>
       </c>
       <c r="L78" s="7">
         <f t="shared" si="7"/>
-        <v>-19.333333333333332</v>
+        <v>-320</v>
       </c>
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A79" t="str">
         <f>_xlfn.XLOOKUP($B79, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Kačák Event (Eifelian, Middle Devonian)</v>
+        <v>Lau Event (Ludfordian, Ludlow, Silurian)</v>
       </c>
       <c r="B79" t="s">
         <v>576</v>
@@ -10146,34 +10179,34 @@
       </c>
       <c r="D79" s="5">
         <f>_xlfn.XLOOKUP($B79, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>386</v>
+        <v>423.5</v>
       </c>
       <c r="E79" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="F79" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G79" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H79" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I79">
-        <v>-32</v>
+        <v>-21</v>
       </c>
       <c r="J79" s="2">
         <f>_xlfn.XLOOKUP(A79, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="K79" s="7">
         <f t="shared" si="6"/>
-        <v>-3.2</v>
+        <v>-0.42</v>
       </c>
       <c r="L79" s="7">
         <f t="shared" si="7"/>
-        <v>-320</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.35">
@@ -10182,7 +10215,7 @@
         <v>Lau Event (Ludfordian, Ludlow, Silurian)</v>
       </c>
       <c r="B80" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C80" t="str">
         <f>_xlfn.XLOOKUP($B80, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10193,19 +10226,19 @@
         <v>423.5</v>
       </c>
       <c r="E80" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="F80" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G80" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H80" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I80">
-        <v>-21</v>
+        <v>-9</v>
       </c>
       <c r="J80" s="2">
         <f>_xlfn.XLOOKUP(A80, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10213,17 +10246,17 @@
       </c>
       <c r="K80" s="7">
         <f t="shared" si="6"/>
-        <v>-0.42</v>
+        <v>-0.18</v>
       </c>
       <c r="L80" s="7">
         <f t="shared" si="7"/>
-        <v>-42</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" t="str">
         <f>_xlfn.XLOOKUP($B81, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Lau Event (Ludfordian, Ludlow, Silurian)</v>
+        <v>Mulde Event (Homerian, Wenlock, Silurian)</v>
       </c>
       <c r="B81" t="s">
         <v>579</v>
@@ -10234,40 +10267,40 @@
       </c>
       <c r="D81" s="5">
         <f>_xlfn.XLOOKUP($B81, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>423.5</v>
+        <v>428</v>
       </c>
       <c r="E81" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="F81" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G81" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H81" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I81">
-        <v>-9</v>
+        <v>-25</v>
       </c>
       <c r="J81" s="2">
         <f>_xlfn.XLOOKUP(A81, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="K81" s="7">
         <f t="shared" si="6"/>
-        <v>-0.18</v>
+        <v>-0.25</v>
       </c>
       <c r="L81" s="7">
         <f t="shared" si="7"/>
-        <v>-18</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" t="str">
         <f>_xlfn.XLOOKUP($B82, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Mulde Event (Homerian, Wenlock, Silurian)</v>
+        <v>Ireviken Event (Sheinwoodian, Wenlock, Silurian)</v>
       </c>
       <c r="B82" t="s">
         <v>582</v>
@@ -10278,22 +10311,22 @@
       </c>
       <c r="D82" s="5">
         <f>_xlfn.XLOOKUP($B82, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E82" t="s">
         <v>34</v>
       </c>
       <c r="F82" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G82" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H82" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I82">
-        <v>-25</v>
+        <v>-22</v>
       </c>
       <c r="J82" s="2">
         <f>_xlfn.XLOOKUP(A82, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10301,55 +10334,54 @@
       </c>
       <c r="K82" s="7">
         <f t="shared" si="6"/>
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="L82" s="7">
         <f t="shared" si="7"/>
-        <v>-25</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" t="str">
         <f>_xlfn.XLOOKUP($B83, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Ireviken Event (Sheinwoodian, Wenlock, Silurian)</v>
+        <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B83" t="s">
         <v>585</v>
       </c>
-      <c r="C83" t="str">
-        <f>_xlfn.XLOOKUP($B83, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>transient</v>
+      <c r="C83" t="s">
+        <v>523</v>
       </c>
       <c r="D83" s="5">
         <f>_xlfn.XLOOKUP($B83, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="E83" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="F83" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G83" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H83" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I83">
-        <v>-22</v>
+        <v>-85</v>
       </c>
       <c r="J83" s="2">
         <f>_xlfn.XLOOKUP(A83, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="K83" s="7">
         <f t="shared" si="6"/>
-        <v>-0.22</v>
+        <v>-1.7</v>
       </c>
       <c r="L83" s="7">
         <f t="shared" si="7"/>
-        <v>-22</v>
+        <v>-170</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.35">
@@ -10358,10 +10390,10 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B84" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C84" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D84" s="5">
         <f>_xlfn.XLOOKUP($B84, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
@@ -10371,16 +10403,16 @@
         <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G84" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H84" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I84">
-        <v>-85</v>
+        <v>-49</v>
       </c>
       <c r="J84" s="2">
         <f>_xlfn.XLOOKUP(A84, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10388,11 +10420,11 @@
       </c>
       <c r="K84" s="7">
         <f t="shared" si="6"/>
-        <v>-1.7</v>
+        <v>-0.98</v>
       </c>
       <c r="L84" s="7">
         <f t="shared" si="7"/>
-        <v>-170</v>
+        <v>-98</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.35">
@@ -10401,29 +10433,30 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B85" t="s">
-        <v>588</v>
-      </c>
-      <c r="C85" t="s">
-        <v>525</v>
+        <v>585</v>
+      </c>
+      <c r="C85" t="str">
+        <f>_xlfn.XLOOKUP($B85, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
+        <v>transient</v>
       </c>
       <c r="D85" s="5">
         <f>_xlfn.XLOOKUP($B85, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
         <v>445</v>
       </c>
       <c r="E85" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G85" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H85" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I85">
-        <v>-49</v>
+        <v>-57</v>
       </c>
       <c r="J85" s="2">
         <f>_xlfn.XLOOKUP(A85, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10431,11 +10464,11 @@
       </c>
       <c r="K85" s="7">
         <f t="shared" si="6"/>
-        <v>-0.98</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="L85" s="7">
         <f t="shared" si="7"/>
-        <v>-98</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.35">
@@ -10444,7 +10477,7 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B86" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C86" t="str">
         <f>_xlfn.XLOOKUP($B86, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10455,19 +10488,19 @@
         <v>445</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="F86" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G86" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H86" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I86">
-        <v>-57</v>
+        <v>-52</v>
       </c>
       <c r="J86" s="2">
         <f>_xlfn.XLOOKUP(A86, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10475,11 +10508,11 @@
       </c>
       <c r="K86" s="7">
         <f t="shared" si="6"/>
-        <v>-1.1399999999999999</v>
+        <v>-1.04</v>
       </c>
       <c r="L86" s="7">
         <f t="shared" si="7"/>
-        <v>-114</v>
+        <v>-104</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.35">
@@ -10488,7 +10521,7 @@
         <v>Late Ordovician Mass Extinction</v>
       </c>
       <c r="B87" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C87" t="str">
         <f>_xlfn.XLOOKUP($B87, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10499,19 +10532,19 @@
         <v>445</v>
       </c>
       <c r="E87" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="F87" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G87" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H87" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I87">
-        <v>-52</v>
+        <v>-46</v>
       </c>
       <c r="J87" s="2">
         <f>_xlfn.XLOOKUP(A87, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10519,55 +10552,58 @@
       </c>
       <c r="K87" s="7">
         <f t="shared" si="6"/>
-        <v>-1.04</v>
+        <v>-0.92</v>
       </c>
       <c r="L87" s="7">
         <f t="shared" si="7"/>
-        <v>-104</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" t="str">
         <f>_xlfn.XLOOKUP($B88, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Late Ordovician Mass Extinction</v>
+        <v>Land plant evolution</v>
       </c>
       <c r="B88" t="s">
         <v>588</v>
       </c>
       <c r="C88" t="str">
         <f>_xlfn.XLOOKUP($B88, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>transient</v>
+        <v>persistent</v>
       </c>
       <c r="D88" s="5">
         <f>_xlfn.XLOOKUP($B88, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="E88" t="s">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="F88" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="G88" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="H88" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I88">
-        <v>-46</v>
+        <v>35</v>
       </c>
       <c r="J88" s="2">
         <f>_xlfn.XLOOKUP(A88, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>500000</v>
-      </c>
-      <c r="K88" s="7">
+        <v>60000000</v>
+      </c>
+      <c r="K88" s="7" t="str">
         <f t="shared" si="6"/>
-        <v>-0.92</v>
+        <v>NA</v>
       </c>
       <c r="L88" s="7">
         <f t="shared" si="7"/>
-        <v>-92</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="M88" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.35">
@@ -10576,7 +10612,7 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B89" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C89" t="str">
         <f>_xlfn.XLOOKUP($B89, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10590,16 +10626,16 @@
         <v>132</v>
       </c>
       <c r="F89" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="G89" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H89" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I89">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="J89" s="2">
         <f>_xlfn.XLOOKUP(A89, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10611,10 +10647,10 @@
       </c>
       <c r="L89" s="7">
         <f t="shared" si="7"/>
-        <v>0.58333333333333337</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="M89" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.35">
@@ -10623,7 +10659,7 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B90" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C90" t="str">
         <f>_xlfn.XLOOKUP($B90, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10634,19 +10670,19 @@
         <v>475</v>
       </c>
       <c r="E90" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="F90" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="G90" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H90" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I90">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="J90" s="2">
         <f>_xlfn.XLOOKUP(A90, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10658,10 +10694,10 @@
       </c>
       <c r="L90" s="7">
         <f t="shared" si="7"/>
-        <v>1.3333333333333333</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="M90" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.35">
@@ -10670,7 +10706,7 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B91" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C91" t="str">
         <f>_xlfn.XLOOKUP($B91, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10681,19 +10717,19 @@
         <v>475</v>
       </c>
       <c r="E91" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F91" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="G91" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H91" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I91">
-        <v>147</v>
+        <v>900</v>
       </c>
       <c r="J91" s="2">
         <f>_xlfn.XLOOKUP(A91, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10705,10 +10741,10 @@
       </c>
       <c r="L91" s="7">
         <f t="shared" si="7"/>
-        <v>2.4500000000000002</v>
+        <v>15</v>
       </c>
       <c r="M91" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.35">
@@ -10717,7 +10753,7 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B92" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C92" t="str">
         <f>_xlfn.XLOOKUP($B92, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10728,34 +10764,34 @@
         <v>475</v>
       </c>
       <c r="E92" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F92" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="G92" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H92" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I92">
-        <v>900</v>
+        <v>12000</v>
       </c>
       <c r="J92" s="2">
         <f>_xlfn.XLOOKUP(A92, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>60000000</v>
       </c>
-      <c r="K92" s="7" t="str">
+      <c r="K92" s="7">
         <f t="shared" si="6"/>
-        <v>NA</v>
+        <v>2</v>
       </c>
       <c r="L92" s="7">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="M92" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.35">
@@ -10764,7 +10800,7 @@
         <v>Land plant evolution</v>
       </c>
       <c r="B93" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C93" t="str">
         <f>_xlfn.XLOOKUP($B93, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10775,19 +10811,19 @@
         <v>475</v>
       </c>
       <c r="E93" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F93" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G93" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H93" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I93">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="J93" s="2">
         <f>_xlfn.XLOOKUP(A93, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10795,107 +10831,104 @@
       </c>
       <c r="K93" s="7">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L93" s="7">
         <f t="shared" si="7"/>
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M93" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" t="str">
         <f>_xlfn.XLOOKUP($B94, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Land plant evolution</v>
+        <v>Great Ordovician Biodiversification Event</v>
       </c>
       <c r="B94" t="s">
         <v>591</v>
       </c>
-      <c r="C94" t="str">
-        <f>_xlfn.XLOOKUP($B94, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>persistent</v>
+      <c r="C94" t="s">
+        <v>541</v>
       </c>
       <c r="D94" s="5">
         <f>_xlfn.XLOOKUP($B94, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="E94" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="F94" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G94" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="H94" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I94">
-        <v>18000</v>
+        <v>800</v>
       </c>
       <c r="J94" s="2">
         <f>_xlfn.XLOOKUP(A94, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>60000000</v>
+        <v>30000000</v>
       </c>
       <c r="K94" s="7">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="L94" s="7">
         <f t="shared" si="7"/>
-        <v>300</v>
+        <v>26.666666666666668</v>
       </c>
       <c r="M94" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" t="str">
         <f>_xlfn.XLOOKUP($B95, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Great Ordovician Biodiversification Event</v>
+        <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B95" t="s">
         <v>594</v>
       </c>
-      <c r="C95" t="s">
-        <v>543</v>
+      <c r="C95" t="str">
+        <f>_xlfn.XLOOKUP($B95, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
+        <v>transient</v>
       </c>
       <c r="D95" s="5">
         <f>_xlfn.XLOOKUP($B95, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E95" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F95" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G95" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H95" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I95">
-        <v>800</v>
+        <v>-65</v>
       </c>
       <c r="J95" s="2">
         <f>_xlfn.XLOOKUP(A95, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>30000000</v>
+        <v>2600000</v>
       </c>
       <c r="K95" s="7">
         <f t="shared" si="6"/>
-        <v>0.26666666666666666</v>
+        <v>-0.25</v>
       </c>
       <c r="L95" s="7">
         <f t="shared" si="7"/>
-        <v>26.666666666666668</v>
-      </c>
-      <c r="M95" t="s">
-        <v>696</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.35">
@@ -10904,7 +10937,7 @@
         <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B96" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C96" t="str">
         <f>_xlfn.XLOOKUP($B96, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10915,19 +10948,19 @@
         <v>495</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F96" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G96" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H96" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I96">
-        <v>-65</v>
+        <v>-60</v>
       </c>
       <c r="J96" s="2">
         <f>_xlfn.XLOOKUP(A96, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10935,11 +10968,14 @@
       </c>
       <c r="K96" s="7">
         <f t="shared" si="6"/>
-        <v>-0.25</v>
+        <v>-0.23076923076923078</v>
       </c>
       <c r="L96" s="7">
         <f t="shared" si="7"/>
-        <v>-25</v>
+        <v>-23.076923076923077</v>
+      </c>
+      <c r="M96" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.35">
@@ -10948,7 +10984,7 @@
         <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B97" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C97" t="str">
         <f>_xlfn.XLOOKUP($B97, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -10959,19 +10995,19 @@
         <v>495</v>
       </c>
       <c r="E97" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F97" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G97" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H97" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I97">
-        <v>-60</v>
+        <v>-59</v>
       </c>
       <c r="J97" s="2">
         <f>_xlfn.XLOOKUP(A97, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -10979,14 +11015,11 @@
       </c>
       <c r="K97" s="7">
         <f t="shared" si="6"/>
-        <v>-0.23076923076923078</v>
+        <v>-0.22692307692307692</v>
       </c>
       <c r="L97" s="7">
         <f t="shared" si="7"/>
-        <v>-23.076923076923077</v>
-      </c>
-      <c r="M97" t="s">
-        <v>697</v>
+        <v>-22.69230769230769</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
@@ -10995,7 +11028,7 @@
         <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
       </c>
       <c r="B98" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C98" t="str">
         <f>_xlfn.XLOOKUP($B98, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -11009,37 +11042,37 @@
         <v>18</v>
       </c>
       <c r="F98" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G98" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H98" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I98">
-        <v>-59</v>
+        <v>-58</v>
       </c>
       <c r="J98" s="2">
         <f>_xlfn.XLOOKUP(A98, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>2600000</v>
       </c>
       <c r="K98" s="7">
-        <f t="shared" si="6"/>
-        <v>-0.22692307692307692</v>
+        <f t="shared" ref="K98:K107" si="8">IF(OR(F98="species", F98="genus"), (I98*10^4)/J98,"NA")</f>
+        <v>-0.22307692307692309</v>
       </c>
       <c r="L98" s="7">
-        <f t="shared" si="7"/>
-        <v>-22.69230769230769</v>
+        <f t="shared" ref="L98:L107" si="9">IF(H98="percent", I98/(J98/10^6), "NA")</f>
+        <v>-22.307692307692307</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="str">
         <f>_xlfn.XLOOKUP($B99, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Steptoean Positive Carbon Isotope Excursion (SPICE) / End-Marjuman Biomere Extinction (EMBE; Paibian, Cambrian)</v>
+        <v>Redlichiid-Olenellid trilobite Extinction Carbon isotope Excursion (ROECE; Cambrian Stage 4–Miaolingian boundary)</v>
       </c>
       <c r="B99" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C99" t="str">
         <f>_xlfn.XLOOKUP($B99, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -11047,40 +11080,43 @@
       </c>
       <c r="D99" s="5">
         <f>_xlfn.XLOOKUP($B99, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="E99" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F99" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G99" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H99" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I99">
-        <v>-58</v>
+        <v>-50</v>
       </c>
       <c r="J99" s="2">
         <f>_xlfn.XLOOKUP(A99, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>2600000</v>
+        <v>500000</v>
       </c>
       <c r="K99" s="7">
-        <f t="shared" ref="K99:K108" si="8">IF(OR(F99="species", F99="genus"), (I99*10^4)/J99,"NA")</f>
-        <v>-0.22307692307692309</v>
+        <f t="shared" si="8"/>
+        <v>-1</v>
       </c>
       <c r="L99" s="7">
-        <f t="shared" ref="L99:L108" si="9">IF(H99="percent", I99/(J99/10^6), "NA")</f>
-        <v>-22.307692307692307</v>
+        <f t="shared" si="9"/>
+        <v>-100</v>
+      </c>
+      <c r="M99" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="str">
         <f>_xlfn.XLOOKUP($B100, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Redlichiid-Olenellid trilobite Extinction Carbon isotope Excursion (ROECE; Cambrian Stage 4–Miaolingian boundary)</v>
+        <v>Sinsk Event / Archaeocyath Extinction Carbon isotope Excursion (AECE; Cambrian Stage 4)</v>
       </c>
       <c r="B100" t="s">
         <v>601</v>
@@ -11091,37 +11127,37 @@
       </c>
       <c r="D100" s="5">
         <f>_xlfn.XLOOKUP($B100, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E100" t="s">
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G100" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H100" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I100">
         <v>-50</v>
       </c>
       <c r="J100" s="2">
         <f>_xlfn.XLOOKUP(A100, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="K100" s="7">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="L100" s="7">
         <f t="shared" si="9"/>
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M100" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
@@ -11130,7 +11166,7 @@
         <v>Sinsk Event / Archaeocyath Extinction Carbon isotope Excursion (AECE; Cambrian Stage 4)</v>
       </c>
       <c r="B101" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C101" t="str">
         <f>_xlfn.XLOOKUP($B101, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -11141,19 +11177,19 @@
         <v>513</v>
       </c>
       <c r="E101" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F101" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G101" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H101" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I101">
-        <v>-50</v>
+        <v>-49</v>
       </c>
       <c r="J101" s="2">
         <f>_xlfn.XLOOKUP(A101, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -11161,58 +11197,58 @@
       </c>
       <c r="K101" s="7">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="L101" s="7">
         <f t="shared" si="9"/>
-        <v>-50</v>
-      </c>
-      <c r="M101" t="s">
-        <v>698</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" t="str">
         <f>_xlfn.XLOOKUP($B102, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Sinsk Event / Archaeocyath Extinction Carbon isotope Excursion (AECE; Cambrian Stage 4)</v>
+        <v>Cambrian Agronomic Revolution</v>
       </c>
       <c r="B102" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C102" t="str">
         <f>_xlfn.XLOOKUP($B102, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>transient</v>
+        <v>persistent</v>
       </c>
       <c r="D102" s="5">
         <f>_xlfn.XLOOKUP($B102, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="E102" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="F102" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="G102" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="H102" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I102">
-        <v>-49</v>
+        <v>243</v>
       </c>
       <c r="J102" s="2">
         <f>_xlfn.XLOOKUP(A102, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>1000000</v>
-      </c>
-      <c r="K102" s="7">
+        <v>40000000</v>
+      </c>
+      <c r="K102" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>-0.49</v>
+        <v>NA</v>
       </c>
       <c r="L102" s="7">
         <f t="shared" si="9"/>
-        <v>-49</v>
+        <v>6.0750000000000002</v>
+      </c>
+      <c r="M102" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.35">
@@ -11221,7 +11257,7 @@
         <v>Cambrian Agronomic Revolution</v>
       </c>
       <c r="B103" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C103" t="str">
         <f>_xlfn.XLOOKUP($B103, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -11232,34 +11268,34 @@
         <v>545</v>
       </c>
       <c r="E103" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="G103" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="H103" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I103">
-        <v>243</v>
+        <v>946</v>
       </c>
       <c r="J103" s="2">
         <f>_xlfn.XLOOKUP(A103, table_s3_events!A:A, table_s3_events!J:J)</f>
         <v>40000000</v>
       </c>
-      <c r="K103" s="7" t="str">
+      <c r="K103" s="7">
         <f t="shared" si="8"/>
-        <v>NA</v>
+        <v>0.23649999999999999</v>
       </c>
       <c r="L103" s="7">
         <f t="shared" si="9"/>
-        <v>6.0750000000000002</v>
+        <v>23.65</v>
       </c>
       <c r="M103" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
@@ -11268,7 +11304,7 @@
         <v>Cambrian Agronomic Revolution</v>
       </c>
       <c r="B104" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C104" t="str">
         <f>_xlfn.XLOOKUP($B104, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -11282,16 +11318,16 @@
         <v>16</v>
       </c>
       <c r="F104" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G104" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="H104" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I104">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="J104" s="2">
         <f>_xlfn.XLOOKUP(A104, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -11299,20 +11335,20 @@
       </c>
       <c r="K104" s="7">
         <f t="shared" si="8"/>
-        <v>0.23649999999999999</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="L104" s="7">
         <f t="shared" si="9"/>
-        <v>23.65</v>
+        <v>23.75</v>
       </c>
       <c r="M104" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" t="str">
         <f>_xlfn.XLOOKUP($B105, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Cambrian Agronomic Revolution</v>
+        <v>Eukaryogenesis</v>
       </c>
       <c r="B105" t="s">
         <v>606</v>
@@ -11323,46 +11359,46 @@
       </c>
       <c r="D105" s="5">
         <f>_xlfn.XLOOKUP($B105, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>545</v>
+        <v>2220</v>
       </c>
       <c r="E105" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F105" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="G105" t="s">
-        <v>666</v>
+        <v>630</v>
       </c>
       <c r="H105" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I105">
-        <v>950</v>
+        <v>600</v>
       </c>
       <c r="J105" s="2">
         <f>_xlfn.XLOOKUP(A105, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>40000000</v>
-      </c>
-      <c r="K105" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="K105" s="7" t="str">
         <f t="shared" si="8"/>
-        <v>0.23749999999999999</v>
+        <v>NA</v>
       </c>
       <c r="L105" s="7">
         <f t="shared" si="9"/>
-        <v>23.75</v>
+        <v>6</v>
       </c>
       <c r="M105" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" t="str">
         <f>_xlfn.XLOOKUP($B106, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Eukaryogenesis</v>
+        <v>Great Oxygenation Event</v>
       </c>
       <c r="B106" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C106" t="str">
         <f>_xlfn.XLOOKUP($B106, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -11370,26 +11406,26 @@
       </c>
       <c r="D106" s="5">
         <f>_xlfn.XLOOKUP($B106, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>2220</v>
+        <v>2400</v>
       </c>
       <c r="E106" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F106" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G106" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H106" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I106">
-        <v>600</v>
+        <v>458</v>
       </c>
       <c r="J106" s="2">
         <f>_xlfn.XLOOKUP(A106, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>100000000</v>
+        <v>500000000</v>
       </c>
       <c r="K106" s="7" t="str">
         <f t="shared" si="8"/>
@@ -11397,10 +11433,10 @@
       </c>
       <c r="L106" s="7">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>0.91600000000000004</v>
       </c>
       <c r="M106" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
@@ -11409,7 +11445,7 @@
         <v>Great Oxygenation Event</v>
       </c>
       <c r="B107" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C107" t="str">
         <f>_xlfn.XLOOKUP($B107, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
@@ -11423,16 +11459,16 @@
         <v>62</v>
       </c>
       <c r="F107" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="G107" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H107" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="I107">
-        <v>458</v>
+        <v>188000</v>
       </c>
       <c r="J107" s="2">
         <f>_xlfn.XLOOKUP(A107, table_s3_events!A:A, table_s3_events!J:J)</f>
@@ -11444,63 +11480,16 @@
       </c>
       <c r="L107" s="7">
         <f t="shared" si="9"/>
-        <v>0.91600000000000004</v>
+        <v>376</v>
       </c>
       <c r="M107" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A108" t="str">
-        <f>_xlfn.XLOOKUP($B108, table_s3_events!$B:$B, table_s3_events!$A:$A)</f>
-        <v>Great Oxygenation Event</v>
-      </c>
-      <c r="B108" t="s">
-        <v>613</v>
-      </c>
-      <c r="C108" t="str">
-        <f>_xlfn.XLOOKUP($B108, table_s3_events!$B:$B, table_s3_events!$E:$E)</f>
-        <v>persistent</v>
-      </c>
-      <c r="D108" s="5">
-        <f>_xlfn.XLOOKUP($B108, table_s3_events!$B:$B, table_s3_events!$G:$G)</f>
-        <v>2400</v>
-      </c>
-      <c r="E108" t="s">
-        <v>62</v>
-      </c>
-      <c r="F108" t="s">
-        <v>650</v>
-      </c>
-      <c r="G108" t="s">
-        <v>633</v>
-      </c>
-      <c r="H108" t="s">
-        <v>634</v>
-      </c>
-      <c r="I108">
-        <v>188000</v>
-      </c>
-      <c r="J108" s="2">
-        <f>_xlfn.XLOOKUP(A108, table_s3_events!A:A, table_s3_events!J:J)</f>
-        <v>500000000</v>
-      </c>
-      <c r="K108" s="7" t="str">
-        <f t="shared" si="8"/>
-        <v>NA</v>
-      </c>
-      <c r="L108" s="7">
-        <f t="shared" si="9"/>
-        <v>376</v>
-      </c>
-      <c r="M108" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M106" xr:uid="{582492E0-B1D4-4D01-BDC9-52F30A59C1EC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M108">
-      <sortCondition ref="D1:D106"/>
+  <autoFilter ref="A1:M105" xr:uid="{582492E0-B1D4-4D01-BDC9-52F30A59C1EC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M107">
+      <sortCondition ref="D1:D105"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -11525,17 +11514,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FAB42693-32D4-4C10-802D-AF303937A480}">
+          <x14:formula1>
+            <xm:f>table_s3_events!$B:$B</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1:B1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CCD39283-F4E1-4D52-B7DE-3097070FAE2B}">
           <x14:formula1>
             <xm:f>references!$A:$A</xm:f>
           </x14:formula1>
           <xm:sqref>E1:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FAB42693-32D4-4C10-802D-AF303937A480}">
-          <x14:formula1>
-            <xm:f>table_s3_events!$B:$B</xm:f>
-          </x14:formula1>
-          <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11544,26 +11533,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EE3B5FF1D6D93545B0A9BE76E04A5739" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b213452e5774ccb18cdbac914376359f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af" xmlns:ns3="d7940701-fd28-48c6-89b6-2769869457dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94bb0651eba29840b02d7d9879aff2b0" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
@@ -11758,10 +11727,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7940701-fd28-48c6-89b6-2769869457dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D4D638-0E0C-48CA-BE88-3BE2B56E957A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
+    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11778,20 +11778,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D4D638-0E0C-48CA-BE88-3BE2B56E957A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C242F3B7-E13F-47B3-89BF-DC7F2A584373}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f4d1a5f8-cfe9-4a60-92ce-29fb37cf63af"/>
-    <ds:schemaRef ds:uri="d7940701-fd28-48c6-89b6-2769869457dd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>